--- a/database/event/7250/event_7250_evp_summary.xlsx
+++ b/database/event/7250/event_7250_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7826</v>
+        <v>6.0183</v>
       </c>
       <c r="C2" t="n">
-        <v>1.73478</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.621536866965887</v>
+        <v>2.0099</v>
       </c>
       <c r="E2" t="n">
-        <v>57.3159</v>
+        <v>6.0183</v>
       </c>
       <c r="F2" t="n">
-        <v>23.48690954840057</v>
+        <v>2.7032</v>
       </c>
       <c r="G2" t="n">
-        <v>33.82897920093157</v>
+        <v>3.3152</v>
       </c>
       <c r="H2" t="n">
-        <v>23.48690954840057</v>
+        <v>2.7032</v>
       </c>
       <c r="I2" t="n">
-        <v>15.95761318599464</v>
+        <v>2.191</v>
       </c>
       <c r="J2" t="n">
-        <v>33.82897920093157</v>
+        <v>3.3152</v>
       </c>
       <c r="K2" t="n">
         <v>71</v>
@@ -541,7 +529,7 @@
         <v>130</v>
       </c>
       <c r="M2" t="n">
-        <v>49.7866</v>
+        <v>5.5062</v>
       </c>
       <c r="N2" t="n">
         <v>201</v>
@@ -550,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.0348</v>
+        <v>5.6078</v>
       </c>
       <c r="C3" t="n">
-        <v>1.21044</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.959066495430915</v>
+        <v>1.8441</v>
       </c>
       <c r="E3" t="n">
-        <v>28.4906</v>
+        <v>5.6078</v>
       </c>
       <c r="F3" t="n">
-        <v>-12.35463847482454</v>
+        <v>1.0072</v>
       </c>
       <c r="G3" t="n">
-        <v>40.84525251454492</v>
+        <v>4.6006</v>
       </c>
       <c r="H3" t="n">
-        <v>-12.35463847482454</v>
+        <v>1.0072</v>
       </c>
       <c r="I3" t="n">
-        <v>-11.94084675557205</v>
+        <v>0.8164</v>
       </c>
       <c r="J3" t="n">
-        <v>40.84525251454492</v>
+        <v>4.6006</v>
       </c>
       <c r="K3" t="n">
         <v>101</v>
@@ -587,7 +575,7 @@
         <v>120</v>
       </c>
       <c r="M3" t="n">
-        <v>28.9044</v>
+        <v>5.417</v>
       </c>
       <c r="N3" t="n">
         <v>221</v>
@@ -596,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7378</v>
+        <v>4.3074</v>
       </c>
       <c r="C4" t="n">
-        <v>1.12134</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8644612042647601</v>
+        <v>1.3187</v>
       </c>
       <c r="E4" t="n">
-        <v>24.3742</v>
+        <v>4.3074</v>
       </c>
       <c r="F4" t="n">
-        <v>3.594988700421291</v>
+        <v>2.7396</v>
       </c>
       <c r="G4" t="n">
-        <v>20.77917934560341</v>
+        <v>1.5678</v>
       </c>
       <c r="H4" t="n">
-        <v>3.594988700421291</v>
+        <v>2.7396</v>
       </c>
       <c r="I4" t="n">
-        <v>3.474582380311487</v>
+        <v>2.2205</v>
       </c>
       <c r="J4" t="n">
-        <v>20.77917934560341</v>
+        <v>1.5678</v>
       </c>
       <c r="K4" t="n">
         <v>101</v>
@@ -633,7 +621,7 @@
         <v>120</v>
       </c>
       <c r="M4" t="n">
-        <v>24.2538</v>
+        <v>3.7883</v>
       </c>
       <c r="N4" t="n">
         <v>221</v>
@@ -642,173 +630,173 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6886</v>
+        <v>4.2119</v>
       </c>
       <c r="C5" t="n">
-        <v>1.10658</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8492353059896343</v>
+        <v>1.2802</v>
       </c>
       <c r="E5" t="n">
-        <v>23.7117</v>
+        <v>4.2119</v>
       </c>
       <c r="F5" t="n">
-        <v>23.7116618882562</v>
+        <v>4.4362</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0.2243</v>
       </c>
       <c r="H5" t="n">
-        <v>23.7116618882562</v>
+        <v>5.2872</v>
       </c>
       <c r="I5" t="n">
-        <v>19.96771527432101</v>
+        <v>4.2854</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0.2243</v>
       </c>
       <c r="K5" t="n">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>19.9677</v>
+        <v>4.0611</v>
       </c>
       <c r="N5" t="n">
-        <v>88</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3934</v>
+        <v>3.617</v>
       </c>
       <c r="C6" t="n">
-        <v>1.01802</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7604551591752985</v>
+        <v>1.0398</v>
       </c>
       <c r="E6" t="n">
-        <v>19.8487</v>
+        <v>3.617</v>
       </c>
       <c r="F6" t="n">
-        <v>19.84867837889061</v>
+        <v>-0.3969</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4.0139</v>
       </c>
       <c r="H6" t="n">
-        <v>19.84867837889061</v>
+        <v>-0.3969</v>
       </c>
       <c r="I6" t="n">
-        <v>27.16134936058715</v>
+        <v>-0.3217</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>4.0139</v>
       </c>
       <c r="K6" t="n">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M6" t="n">
-        <v>27.1613</v>
+        <v>3.6922</v>
       </c>
       <c r="N6" t="n">
-        <v>143</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0592</v>
+        <v>3.4974</v>
       </c>
       <c r="C7" t="n">
-        <v>0.91776</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6650646005544091</v>
+        <v>0.9915</v>
       </c>
       <c r="E7" t="n">
-        <v>15.6981</v>
+        <v>3.4974</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.308038125354063</v>
+        <v>3.4974</v>
       </c>
       <c r="G7" t="n">
-        <v>18.0061021143824</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.308038125354063</v>
+        <v>3.4974</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.23073541302163</v>
+        <v>3.4974</v>
       </c>
       <c r="J7" t="n">
-        <v>18.0061021143824</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="L7" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>15.7754</v>
+        <v>3.4974</v>
       </c>
       <c r="N7" t="n">
-        <v>221</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6613</v>
+        <v>2.8223</v>
       </c>
       <c r="C8" t="n">
-        <v>0.79839</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5582370924490236</v>
+        <v>0.7188</v>
       </c>
       <c r="E8" t="n">
-        <v>11.0498</v>
+        <v>2.8223</v>
       </c>
       <c r="F8" t="n">
-        <v>29.14050071994565</v>
+        <v>2.7508</v>
       </c>
       <c r="G8" t="n">
-        <v>-18.09069331716443</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>29.14050071994565</v>
+        <v>2.7508</v>
       </c>
       <c r="I8" t="n">
-        <v>19.79880910158986</v>
+        <v>2.2296</v>
       </c>
       <c r="J8" t="n">
-        <v>-18.09069331716443</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>71</v>
@@ -817,7 +805,7 @@
         <v>130</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7081</v>
+        <v>2.3011</v>
       </c>
       <c r="N8" t="n">
         <v>201</v>
@@ -826,231 +814,231 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4679</v>
+        <v>2.6741</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7403700000000001</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5088023031323367</v>
+        <v>0.6589</v>
       </c>
       <c r="E9" t="n">
-        <v>8.8988</v>
+        <v>2.6741</v>
       </c>
       <c r="F9" t="n">
-        <v>8.898811005819999</v>
+        <v>3.9432</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-1.2691</v>
       </c>
       <c r="H9" t="n">
-        <v>8.898811005819999</v>
+        <v>3.9432</v>
       </c>
       <c r="I9" t="n">
-        <v>7.493735583848419</v>
+        <v>3.1961</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-1.2691</v>
       </c>
       <c r="K9" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M9" t="n">
-        <v>7.4937</v>
+        <v>1.927</v>
       </c>
       <c r="N9" t="n">
-        <v>88</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2657</v>
+        <v>2.62</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6797099999999999</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4588139558155443</v>
+        <v>0.6371</v>
       </c>
       <c r="E10" t="n">
-        <v>6.7237</v>
+        <v>2.62</v>
       </c>
       <c r="F10" t="n">
-        <v>6.72372830688007</v>
+        <v>0.4215</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.1985</v>
       </c>
       <c r="H10" t="n">
-        <v>6.72372830688007</v>
+        <v>0.4215</v>
       </c>
       <c r="I10" t="n">
-        <v>9.39391706033005</v>
+        <v>0.3416</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2.1985</v>
       </c>
       <c r="K10" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M10" t="n">
-        <v>9.3939</v>
+        <v>2.5401</v>
       </c>
       <c r="N10" t="n">
-        <v>146</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5732</v>
+        <v>2.3805</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4719599999999999</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2997942184581306</v>
+        <v>0.5403</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1955</v>
+        <v>2.3805</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1955058363117737</v>
+        <v>3.153</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.7725</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1955058363117737</v>
+        <v>3.153</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2731469100623825</v>
+        <v>2.5556</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.7725</v>
       </c>
       <c r="K11" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2731</v>
+        <v>1.7831</v>
       </c>
       <c r="N11" t="n">
-        <v>146</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.4428</v>
+        <v>2.0099</v>
       </c>
       <c r="C12" t="n">
-        <v>0.43284</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.271844399487309</v>
+        <v>0.3906</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4117</v>
+        <v>2.0099</v>
       </c>
       <c r="F12" t="n">
-        <v>16.58975246370698</v>
+        <v>2.0099</v>
       </c>
       <c r="G12" t="n">
-        <v>-18.00140508112097</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>16.58975246370698</v>
+        <v>2.0099</v>
       </c>
       <c r="I12" t="n">
-        <v>20.63796957207567</v>
+        <v>2.0099</v>
       </c>
       <c r="J12" t="n">
-        <v>-18.00140508112097</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="L12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6366</v>
+        <v>2.0099</v>
       </c>
       <c r="N12" t="n">
-        <v>174</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4417</v>
+        <v>1.8636</v>
       </c>
       <c r="C13" t="n">
-        <v>0.43251</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2716065640526684</v>
+        <v>0.3315</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.422</v>
+        <v>1.8636</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.422001263985635</v>
+        <v>1.3813</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.4823</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.422001263985635</v>
+        <v>1.3813</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.945896466506658</v>
+        <v>1.1196</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.4823</v>
       </c>
       <c r="K13" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9459</v>
+        <v>1.6019</v>
       </c>
       <c r="N13" t="n">
-        <v>143</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -1060,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4267</v>
+        <v>1.8418</v>
       </c>
       <c r="C14" t="n">
-        <v>0.42801</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2684261224819934</v>
+        <v>0.3227</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.5604</v>
+        <v>1.8418</v>
       </c>
       <c r="F14" t="n">
-        <v>15.07930416544326</v>
+        <v>1.5957</v>
       </c>
       <c r="G14" t="n">
-        <v>-16.63969214966841</v>
+        <v>0.2461</v>
       </c>
       <c r="H14" t="n">
-        <v>15.07930416544326</v>
+        <v>1.5957</v>
       </c>
       <c r="I14" t="n">
-        <v>11.97686359551953</v>
+        <v>1.2933</v>
       </c>
       <c r="J14" t="n">
-        <v>-16.63969214966841</v>
+        <v>0.2461</v>
       </c>
       <c r="K14" t="n">
         <v>83</v>
@@ -1093,7 +1081,7 @@
         <v>34</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.6628</v>
+        <v>1.5394</v>
       </c>
       <c r="N14" t="n">
         <v>117</v>
@@ -1102,78 +1090,78 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1736</v>
+        <v>1.5344</v>
       </c>
       <c r="C15" t="n">
-        <v>0.35208</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2160306753161226</v>
+        <v>0.1985</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.8402</v>
+        <v>1.5344</v>
       </c>
       <c r="F15" t="n">
-        <v>20.76920232247582</v>
+        <v>1.3403</v>
       </c>
       <c r="G15" t="n">
-        <v>-24.60941023976411</v>
+        <v>0.1941</v>
       </c>
       <c r="H15" t="n">
-        <v>20.76920232247582</v>
+        <v>1.3403</v>
       </c>
       <c r="I15" t="n">
-        <v>20.07358310593357</v>
+        <v>1.0864</v>
       </c>
       <c r="J15" t="n">
-        <v>-24.60941023976411</v>
+        <v>0.1941</v>
       </c>
       <c r="K15" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="L15" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.5358</v>
+        <v>1.2805</v>
       </c>
       <c r="N15" t="n">
-        <v>221</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1153</v>
+        <v>1.525</v>
       </c>
       <c r="C16" t="n">
-        <v>0.33459</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2042725496629938</v>
+        <v>0.1947</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.3518</v>
+        <v>1.525</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.351825065140882</v>
+        <v>1.525</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.351825065140882</v>
+        <v>1.525</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.664694791697585</v>
+        <v>1.525</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1185,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.6647</v>
+        <v>1.525</v>
       </c>
       <c r="N16" t="n">
         <v>88</v>
@@ -1194,722 +1182,722 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2564</v>
+        <v>1.4871</v>
       </c>
       <c r="C17" t="n">
-        <v>0.07692</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04365728996653854</v>
+        <v>0.1794</v>
       </c>
       <c r="E17" t="n">
-        <v>-11.3405</v>
+        <v>1.4871</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.34048324856811</v>
+        <v>0.4135</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.0736</v>
       </c>
       <c r="H17" t="n">
-        <v>-11.34048324856811</v>
+        <v>0.4135</v>
       </c>
       <c r="I17" t="n">
-        <v>-8.030581439177418</v>
+        <v>0.3352</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.0736</v>
       </c>
       <c r="K17" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M17" t="n">
-        <v>-8.0306</v>
+        <v>1.4088</v>
       </c>
       <c r="N17" t="n">
-        <v>74</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0502</v>
+        <v>1.4082</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01506</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.008402356551956891</v>
+        <v>0.1475</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.8745</v>
+        <v>1.4082</v>
       </c>
       <c r="F18" t="n">
-        <v>-12.87448866859879</v>
+        <v>1.4082</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-12.87448866859879</v>
+        <v>1.4082</v>
       </c>
       <c r="I18" t="n">
-        <v>-17.98732388148731</v>
+        <v>1.4082</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-17.9873</v>
+        <v>1.4082</v>
       </c>
       <c r="N18" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.1422</v>
+        <v>1.215</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.04266</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.02398089489295362</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-14.2835</v>
+        <v>1.215</v>
       </c>
       <c r="F19" t="n">
-        <v>-14.28354205271787</v>
+        <v>1.215</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-14.28354205271787</v>
+        <v>1.215</v>
       </c>
       <c r="I19" t="n">
-        <v>-19.54589965108762</v>
+        <v>1.215</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-19.5459</v>
+        <v>1.215</v>
       </c>
       <c r="N19" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Airax</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1703</v>
+        <v>0.9323</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.05109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.02878514467898662</v>
+        <v>-0.0447</v>
       </c>
       <c r="E20" t="n">
-        <v>-14.4926</v>
+        <v>0.9323</v>
       </c>
       <c r="F20" t="n">
-        <v>-14.49258358243206</v>
+        <v>1.806</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.8737</v>
       </c>
       <c r="H20" t="n">
-        <v>-14.49258358243206</v>
+        <v>1.806</v>
       </c>
       <c r="I20" t="n">
-        <v>-10.26269076650691</v>
+        <v>1.4638</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.8737</v>
       </c>
       <c r="K20" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M20" t="n">
-        <v>-10.2627</v>
+        <v>0.5901</v>
       </c>
       <c r="N20" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.6064000000000001</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.18192</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1063554407691467</v>
+        <v>-0.1581</v>
       </c>
       <c r="E21" t="n">
-        <v>-17.8678</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-17.86780637001713</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-17.86780637001713</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-12.65280068307433</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-12.6528</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.869</v>
+        <v>0.4581</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.2607</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1558385168767923</v>
+        <v>-0.2363</v>
       </c>
       <c r="E22" t="n">
-        <v>-20.0209</v>
+        <v>0.4581</v>
       </c>
       <c r="F22" t="n">
-        <v>30.3655530807973</v>
+        <v>-0.3724</v>
       </c>
       <c r="G22" t="n">
-        <v>-50.3864568927039</v>
+        <v>0.8305</v>
       </c>
       <c r="H22" t="n">
-        <v>30.40430119919955</v>
+        <v>-0.3724</v>
       </c>
       <c r="I22" t="n">
-        <v>20.65746780041309</v>
+        <v>-0.3018</v>
       </c>
       <c r="J22" t="n">
-        <v>-50.3864568927039</v>
+        <v>0.8305</v>
       </c>
       <c r="K22" t="n">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="L22" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="M22" t="n">
-        <v>-29.729</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>ottoNd</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.9012</v>
+        <v>0.3859</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.27036</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1620642890232767</v>
+        <v>-0.2655</v>
       </c>
       <c r="E23" t="n">
-        <v>-20.2918</v>
+        <v>0.3859</v>
       </c>
       <c r="F23" t="n">
-        <v>-20.29179833053396</v>
+        <v>1.3859</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>-20.29179833053396</v>
+        <v>1.3859</v>
       </c>
       <c r="I23" t="n">
-        <v>-27.767724031257</v>
+        <v>1.1233</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K23" t="n">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M23" t="n">
-        <v>-27.7677</v>
+        <v>0.1233</v>
       </c>
       <c r="N23" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Airax</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.0479</v>
+        <v>0.3314</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.31437</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1908207356305164</v>
+        <v>-0.2875</v>
       </c>
       <c r="E24" t="n">
-        <v>-21.543</v>
+        <v>0.3314</v>
       </c>
       <c r="F24" t="n">
-        <v>13.29064276400461</v>
+        <v>0.3314</v>
       </c>
       <c r="G24" t="n">
-        <v>-34.83368569164462</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>13.29064276400461</v>
+        <v>0.3314</v>
       </c>
       <c r="I24" t="n">
-        <v>10.55620430059696</v>
+        <v>0.3314</v>
       </c>
       <c r="J24" t="n">
-        <v>-34.83368569164462</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="L24" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-24.2775</v>
+        <v>0.3314</v>
       </c>
       <c r="N24" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.2665</v>
+        <v>0.1621</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.37995</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2350103366039638</v>
+        <v>-0.3559</v>
       </c>
       <c r="E25" t="n">
-        <v>-23.4658</v>
+        <v>0.1621</v>
       </c>
       <c r="F25" t="n">
-        <v>-23.46581176697143</v>
+        <v>0.1621</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-23.46581176697143</v>
+        <v>0.1621</v>
       </c>
       <c r="I25" t="n">
-        <v>-32.11111083901353</v>
+        <v>0.1621</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-32.1111</v>
+        <v>0.1621</v>
       </c>
       <c r="N25" t="n">
-        <v>143</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Banjo</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.3094</v>
+        <v>0.1414</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3928199999999999</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2438870767802724</v>
+        <v>-0.3642</v>
       </c>
       <c r="E26" t="n">
-        <v>-23.8521</v>
+        <v>0.1414</v>
       </c>
       <c r="F26" t="n">
-        <v>1.53593146054101</v>
+        <v>0.1414</v>
       </c>
       <c r="G26" t="n">
-        <v>-25.38798612244383</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.53593146054101</v>
+        <v>0.1414</v>
       </c>
       <c r="I26" t="n">
-        <v>1.219926423204821</v>
+        <v>0.1414</v>
       </c>
       <c r="J26" t="n">
-        <v>-25.38798612244383</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="L26" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-24.1681</v>
+        <v>0.1414</v>
       </c>
       <c r="N26" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.3558</v>
+        <v>0.1089</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.4067399999999999</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2535410410508954</v>
+        <v>-0.3774</v>
       </c>
       <c r="E27" t="n">
-        <v>-24.2721</v>
+        <v>0.1089</v>
       </c>
       <c r="F27" t="n">
-        <v>-24.27211597195462</v>
+        <v>0.1089</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-24.27211597195462</v>
+        <v>0.1089</v>
       </c>
       <c r="I27" t="n">
-        <v>-20.43967660796178</v>
+        <v>0.1089</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-20.4397</v>
+        <v>0.1089</v>
       </c>
       <c r="N27" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Banjo</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.4599</v>
+        <v>-0.1208</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.43797</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2754726648196563</v>
+        <v>-0.4702</v>
       </c>
       <c r="E28" t="n">
-        <v>-25.2264</v>
+        <v>-0.1208</v>
       </c>
       <c r="F28" t="n">
-        <v>47.85683066814427</v>
+        <v>0.4975</v>
       </c>
       <c r="G28" t="n">
-        <v>-73.08323094793531</v>
+        <v>-0.6183</v>
       </c>
       <c r="H28" t="n">
-        <v>57.69219151259572</v>
+        <v>0.4975</v>
       </c>
       <c r="I28" t="n">
-        <v>39.19756552530427</v>
+        <v>0.4032</v>
       </c>
       <c r="J28" t="n">
-        <v>-73.08323094793531</v>
+        <v>-0.6183</v>
       </c>
       <c r="K28" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="L28" t="n">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="M28" t="n">
-        <v>-33.8857</v>
+        <v>-0.2151</v>
       </c>
       <c r="N28" t="n">
-        <v>201</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.5032</v>
+        <v>-0.1429</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.45096</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2847003983698596</v>
+        <v>-0.4791</v>
       </c>
       <c r="E29" t="n">
-        <v>-25.6279</v>
+        <v>-0.1429</v>
       </c>
       <c r="F29" t="n">
-        <v>-25.62791552629994</v>
+        <v>-0.1429</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-25.62791552629994</v>
+        <v>-0.1429</v>
       </c>
       <c r="I29" t="n">
-        <v>-35.80550877358652</v>
+        <v>-0.1429</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-35.8055</v>
+        <v>-0.1429</v>
       </c>
       <c r="N29" t="n">
-        <v>146</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.5716</v>
+        <v>-0.1792</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.47148</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.299434261950766</v>
+        <v>-0.4938</v>
       </c>
       <c r="E30" t="n">
-        <v>-26.269</v>
+        <v>-0.1792</v>
       </c>
       <c r="F30" t="n">
-        <v>-26.26901237153621</v>
+        <v>-0.1792</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-26.26901237153621</v>
+        <v>-0.1792</v>
       </c>
       <c r="I30" t="n">
-        <v>-22.12127357603049</v>
+        <v>-0.1792</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-22.1213</v>
+        <v>-0.1792</v>
       </c>
       <c r="N30" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.6491</v>
+        <v>-0.5576</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.49473</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3163273802753453</v>
+        <v>-0.6466</v>
       </c>
       <c r="E31" t="n">
-        <v>-27.0041</v>
+        <v>-0.5576</v>
       </c>
       <c r="F31" t="n">
-        <v>-21.31726223370675</v>
+        <v>-0.5576</v>
       </c>
       <c r="G31" t="n">
-        <v>-5.686800031879361</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-21.31726223370675</v>
+        <v>-0.5576</v>
       </c>
       <c r="I31" t="n">
-        <v>-26.51908220461127</v>
+        <v>-0.5576</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.686800031879361</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="L31" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-32.2059</v>
+        <v>-0.5576</v>
       </c>
       <c r="N31" t="n">
-        <v>174</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.7088</v>
+        <v>-0.712</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.51264</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3294947722678919</v>
+        <v>-0.709</v>
       </c>
       <c r="E32" t="n">
-        <v>-27.577</v>
+        <v>-0.712</v>
       </c>
       <c r="F32" t="n">
-        <v>-27.57699912088253</v>
+        <v>-0.712</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-27.57699912088253</v>
+        <v>-0.712</v>
       </c>
       <c r="I32" t="n">
-        <v>-19.52820990378284</v>
+        <v>-0.712</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1921,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-19.5282</v>
+        <v>-0.712</v>
       </c>
       <c r="N32" t="n">
         <v>74</v>
@@ -1930,369 +1918,369 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-2.1769</v>
+        <v>-0.7257</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.6530699999999999</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.437376934644382</v>
+        <v>-0.7145</v>
       </c>
       <c r="E33" t="n">
-        <v>-32.2711</v>
+        <v>-0.7257</v>
       </c>
       <c r="F33" t="n">
-        <v>-33.1924252778952</v>
+        <v>-0.7257</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9212796707873505</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-33.1924252778952</v>
+        <v>-0.7257</v>
       </c>
       <c r="I33" t="n">
-        <v>-41.29201230742943</v>
+        <v>-0.7257</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9212796707873505</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="L33" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-40.3707</v>
+        <v>-0.7257</v>
       </c>
       <c r="N33" t="n">
-        <v>174</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>uli</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-2.1847</v>
+        <v>-0.8663</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.6554099999999999</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.4392467946143883</v>
+        <v>-0.7713</v>
       </c>
       <c r="E34" t="n">
-        <v>-32.3525</v>
+        <v>-0.8663</v>
       </c>
       <c r="F34" t="n">
-        <v>-9.688463632568089</v>
+        <v>-0.8663</v>
       </c>
       <c r="G34" t="n">
-        <v>-22.66404293741429</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-9.688463632568089</v>
+        <v>-0.8663</v>
       </c>
       <c r="I34" t="n">
-        <v>-7.695143363666521</v>
+        <v>-0.8663</v>
       </c>
       <c r="J34" t="n">
-        <v>-22.66404293741429</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L34" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-30.3592</v>
+        <v>-0.8663</v>
       </c>
       <c r="N34" t="n">
-        <v>117</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-2.3888</v>
+        <v>-0.9525</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.7166399999999999</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4890461864145157</v>
+        <v>-0.8062</v>
       </c>
       <c r="E35" t="n">
-        <v>-34.5194</v>
+        <v>-0.9525</v>
       </c>
       <c r="F35" t="n">
-        <v>-10.96000247926831</v>
+        <v>-0.9525</v>
       </c>
       <c r="G35" t="n">
-        <v>-23.55936499603153</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-10.96000247926831</v>
+        <v>-0.9525</v>
       </c>
       <c r="I35" t="n">
-        <v>-10.59292105651769</v>
+        <v>-0.9525</v>
       </c>
       <c r="J35" t="n">
-        <v>-23.55936499603153</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="L35" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-34.1523</v>
+        <v>-0.9525</v>
       </c>
       <c r="N35" t="n">
-        <v>221</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ottoNd</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-2.4585</v>
+        <v>-1.0808</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.7375499999999999</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.5064420473648575</v>
+        <v>-0.858</v>
       </c>
       <c r="E36" t="n">
-        <v>-35.2763</v>
+        <v>-1.0808</v>
       </c>
       <c r="F36" t="n">
-        <v>12.26998397077969</v>
+        <v>-1.0808</v>
       </c>
       <c r="G36" t="n">
-        <v>-47.54627657397914</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>12.26998397077969</v>
+        <v>-1.0808</v>
       </c>
       <c r="I36" t="n">
-        <v>9.745537507892006</v>
+        <v>-1.0808</v>
       </c>
       <c r="J36" t="n">
-        <v>-47.54627657397914</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L36" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-37.8007</v>
+        <v>-1.0808</v>
       </c>
       <c r="N36" t="n">
-        <v>117</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>uli</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2.5761</v>
+        <v>-1.3785</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.7728299999999999</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.5362656644545341</v>
+        <v>-0.9782</v>
       </c>
       <c r="E37" t="n">
-        <v>-36.574</v>
+        <v>-1.3785</v>
       </c>
       <c r="F37" t="n">
-        <v>-36.57397170309986</v>
+        <v>-0.8591</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.5194</v>
       </c>
       <c r="H37" t="n">
-        <v>-36.57397170309986</v>
+        <v>-0.8591</v>
       </c>
       <c r="I37" t="n">
-        <v>-51.09856333638832</v>
+        <v>-0.6963</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.5194</v>
       </c>
       <c r="K37" t="n">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M37" t="n">
-        <v>-51.0986</v>
+        <v>-1.2157</v>
       </c>
       <c r="N37" t="n">
-        <v>146</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>kyuubii</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.9587</v>
+        <v>-1.5674</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.8876099999999999</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.6373985833792841</v>
+        <v>-1.0546</v>
       </c>
       <c r="E38" t="n">
-        <v>-40.9744</v>
+        <v>-1.5674</v>
       </c>
       <c r="F38" t="n">
-        <v>-3.861531045286196</v>
+        <v>-1.5674</v>
       </c>
       <c r="G38" t="n">
-        <v>-37.11291544951826</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-3.861531045286196</v>
+        <v>-1.5674</v>
       </c>
       <c r="I38" t="n">
-        <v>-4.803818525236416</v>
+        <v>-1.5674</v>
       </c>
       <c r="J38" t="n">
-        <v>-37.11291544951826</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="L38" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-41.9167</v>
+        <v>-1.5674</v>
       </c>
       <c r="N38" t="n">
-        <v>174</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kyuubii</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-3.1139</v>
+        <v>-1.7361</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.9341699999999999</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.6803304800466536</v>
+        <v>-1.1227</v>
       </c>
       <c r="E39" t="n">
-        <v>-42.8425</v>
+        <v>-1.7361</v>
       </c>
       <c r="F39" t="n">
-        <v>-42.84249036275012</v>
+        <v>-1.2541</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.482</v>
       </c>
       <c r="H39" t="n">
-        <v>-42.84249036275012</v>
+        <v>-1.2541</v>
       </c>
       <c r="I39" t="n">
-        <v>-30.33822284060774</v>
+        <v>-1.0165</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.482</v>
       </c>
       <c r="K39" t="n">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>-30.3382</v>
+        <v>-1.4985</v>
       </c>
       <c r="N39" t="n">
-        <v>74</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-4.3192</v>
+        <v>-2.0927</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.29576</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.054148508941651</v>
+        <v>-1.2668</v>
       </c>
       <c r="E40" t="n">
-        <v>-59.108</v>
+        <v>-2.0927</v>
       </c>
       <c r="F40" t="n">
-        <v>-31.83880064154563</v>
+        <v>-2.0927</v>
       </c>
       <c r="G40" t="n">
-        <v>-27.26918299803862</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-31.83880064154563</v>
+        <v>-2.0927</v>
       </c>
       <c r="I40" t="n">
-        <v>-39.60807735311896</v>
+        <v>-2.0927</v>
       </c>
       <c r="J40" t="n">
-        <v>-27.26918299803862</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-66.87730000000001</v>
+        <v>-2.0927</v>
       </c>
       <c r="N40" t="n">
-        <v>174</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41">
@@ -2302,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.611</v>
+        <v>-2.8198</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.6833</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.547619182549951</v>
+        <v>-1.5605</v>
       </c>
       <c r="E41" t="n">
-        <v>-80.57980000000001</v>
+        <v>-2.8198</v>
       </c>
       <c r="F41" t="n">
-        <v>-18.47386915824732</v>
+        <v>-1.3206</v>
       </c>
       <c r="G41" t="n">
-        <v>-62.10590905373084</v>
+        <v>-1.4992</v>
       </c>
       <c r="H41" t="n">
-        <v>-18.47386915824732</v>
+        <v>-1.3206</v>
       </c>
       <c r="I41" t="n">
-        <v>-12.55162402139292</v>
+        <v>-1.0704</v>
       </c>
       <c r="J41" t="n">
-        <v>-62.10590905373084</v>
+        <v>-1.4992</v>
       </c>
       <c r="K41" t="n">
         <v>71</v>
@@ -2335,7 +2323,7 @@
         <v>130</v>
       </c>
       <c r="M41" t="n">
-        <v>-74.6575</v>
+        <v>-2.5696</v>
       </c>
       <c r="N41" t="n">
         <v>201</v>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04001709812308497</v>
+        <v>0.2996</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8803761587078692</v>
+        <v>6.5912</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>0.88</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6690860970196856</v>
+        <v>-0.1857</v>
       </c>
       <c r="J3" t="n">
-        <v>-14.71989413443308</v>
+        <v>-4.0854</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9774594268085415</v>
+        <v>-0.3058</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.50410738978791</v>
+        <v>-6.7276</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>0.77</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.149568747986293</v>
+        <v>-0.386</v>
       </c>
       <c r="J5" t="n">
-        <v>-25.29051245569846</v>
+        <v>-8.492000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.350371610758341</v>
+        <v>-0.4877</v>
       </c>
       <c r="J6" t="n">
-        <v>-29.7081754366835</v>
+        <v>-10.7294</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.57</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8913507614285662</v>
+        <v>1.3414</v>
       </c>
       <c r="J7" t="n">
-        <v>19.60971675142845</v>
+        <v>29.5108</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.52</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8381413120608007</v>
+        <v>1.2435</v>
       </c>
       <c r="J8" t="n">
-        <v>18.43910886533762</v>
+        <v>27.357</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3107097691561213</v>
+        <v>0.4904</v>
       </c>
       <c r="J9" t="n">
-        <v>6.835614921434668</v>
+        <v>10.7888</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04670179621289033</v>
+        <v>0.0353</v>
       </c>
       <c r="J10" t="n">
-        <v>1.027439516683587</v>
+        <v>0.7766</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.86</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5171957869352962</v>
+        <v>-0.5924</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.37830731257652</v>
+        <v>-13.0328</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.78</v>
       </c>
       <c r="I12" t="n">
-        <v>1.233036171950769</v>
+        <v>0.9954</v>
       </c>
       <c r="J12" t="n">
-        <v>24.66072343901538</v>
+        <v>19.908</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6287028184731344</v>
+        <v>0.4014</v>
       </c>
       <c r="J13" t="n">
-        <v>12.57405636946269</v>
+        <v>8.028</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>1.16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.369548013916674</v>
+        <v>0.2222</v>
       </c>
       <c r="J14" t="n">
-        <v>7.39096027833348</v>
+        <v>4.444</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1772755646840723</v>
+        <v>0.0216</v>
       </c>
       <c r="J15" t="n">
-        <v>3.545511293681447</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.02623444323390317</v>
+        <v>-0.263</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5246888646780633</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.06</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04791112374308132</v>
+        <v>0.2513</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9582224748616264</v>
+        <v>5.026</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.549507054529825</v>
+        <v>-0.1219</v>
       </c>
       <c r="J18" t="n">
-        <v>-10.9901410905965</v>
+        <v>-2.438</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8229230286005121</v>
+        <v>-0.2572</v>
       </c>
       <c r="J19" t="n">
-        <v>-16.45846057201024</v>
+        <v>-5.144</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.54</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.786308401349345</v>
+        <v>-0.6767</v>
       </c>
       <c r="J20" t="n">
-        <v>-35.7261680269869</v>
+        <v>-13.534</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.52</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.833841625800685</v>
+        <v>-0.7022</v>
       </c>
       <c r="J21" t="n">
-        <v>-36.6768325160137</v>
+        <v>-14.044</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.92</v>
       </c>
       <c r="I22" t="n">
-        <v>1.019521829996627</v>
+        <v>1.2116</v>
       </c>
       <c r="J22" t="n">
-        <v>22.4294802599258</v>
+        <v>26.6552</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>0.85</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.088051105478708</v>
+        <v>-0.3063</v>
       </c>
       <c r="J23" t="n">
-        <v>-23.93712432053157</v>
+        <v>-6.7386</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.285150735929683</v>
+        <v>-0.4098</v>
       </c>
       <c r="J24" t="n">
-        <v>-28.27331619045303</v>
+        <v>-9.015599999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.362348491943064</v>
+        <v>-0.4516</v>
       </c>
       <c r="J25" t="n">
-        <v>-29.97166682274741</v>
+        <v>-9.9352</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.65</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.596000439881706</v>
+        <v>-0.5825</v>
       </c>
       <c r="J26" t="n">
-        <v>-35.11200967739754</v>
+        <v>-12.815</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5493287604211459</v>
+        <v>0.7603</v>
       </c>
       <c r="J27" t="n">
-        <v>12.08523272926521</v>
+        <v>16.7266</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.25</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5178281469918697</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>11.39221923382113</v>
+        <v>15.6684</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3256395934538632</v>
+        <v>0.4461</v>
       </c>
       <c r="J29" t="n">
-        <v>7.164071055984991</v>
+        <v>9.8142</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>1.08</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1323486543700044</v>
+        <v>0.2138</v>
       </c>
       <c r="J30" t="n">
-        <v>2.911670396140098</v>
+        <v>4.7036</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5000587460468939</v>
+        <v>-0.4258</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.00129241303167</v>
+        <v>-9.367599999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3784605278759253</v>
+        <v>0.5206</v>
       </c>
       <c r="J32" t="n">
-        <v>8.326131613270356</v>
+        <v>11.4532</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>0.86</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.868174829554342</v>
+        <v>-0.2523</v>
       </c>
       <c r="J33" t="n">
-        <v>-19.09984625019552</v>
+        <v>-5.5506</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.051393839771338</v>
+        <v>-0.3359</v>
       </c>
       <c r="J34" t="n">
-        <v>-23.13066447496943</v>
+        <v>-7.3898</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.083899102035212</v>
+        <v>-0.3516</v>
       </c>
       <c r="J35" t="n">
-        <v>-23.84578024477467</v>
+        <v>-7.7352</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.368342296031994</v>
+        <v>-0.4963</v>
       </c>
       <c r="J36" t="n">
-        <v>-30.10353051270387</v>
+        <v>-10.9186</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.78</v>
       </c>
       <c r="I37" t="n">
-        <v>1.101813196998787</v>
+        <v>1.7533</v>
       </c>
       <c r="J37" t="n">
-        <v>24.23989033397332</v>
+        <v>38.5726</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.36</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6735614185403258</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>14.81835120788717</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1912975832798365</v>
+        <v>0.2714</v>
       </c>
       <c r="J39" t="n">
-        <v>4.208546832156403</v>
+        <v>5.9708</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1648720508138636</v>
+        <v>-0.3245</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.627185117905</v>
+        <v>-7.139</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9358774773974918</v>
+        <v>-0.865</v>
       </c>
       <c r="J41" t="n">
-        <v>-20.58930450274482</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1126551129300277</v>
+        <v>0.4817</v>
       </c>
       <c r="J42" t="n">
-        <v>2.253102258600554</v>
+        <v>9.634</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.07</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1328914424791209</v>
+        <v>0.2344</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.657828849582418</v>
+        <v>4.688</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>0.85</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.6411186486653299</v>
+        <v>-0.24</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.8223729733066</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.63</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.130450929633825</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>-22.6090185926765</v>
+        <v>-11.602</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.46</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.373254983947757</v>
+        <v>-0.7907</v>
       </c>
       <c r="J46" t="n">
-        <v>-27.46509967895515</v>
+        <v>-15.814</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5441727815150449</v>
+        <v>1.4968</v>
       </c>
       <c r="J47" t="n">
-        <v>10.8834556303009</v>
+        <v>29.936</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>0.241054717544202</v>
+        <v>0.6294</v>
       </c>
       <c r="J48" t="n">
-        <v>4.82109435088404</v>
+        <v>12.588</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>1.26</v>
       </c>
       <c r="I49" t="n">
-        <v>0.241054717544202</v>
+        <v>0.6294</v>
       </c>
       <c r="J49" t="n">
-        <v>4.82109435088404</v>
+        <v>12.588</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>1.11</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1011525463523294</v>
+        <v>0.2337</v>
       </c>
       <c r="J50" t="n">
-        <v>2.023050927046589</v>
+        <v>4.674</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>1.06</v>
       </c>
       <c r="I51" t="n">
-        <v>0.06186308174043344</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>1.237261634808669</v>
+        <v>1.768</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.15</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.272665655454415</v>
+        <v>0.4861</v>
       </c>
       <c r="J52" t="n">
-        <v>-3.81731917636181</v>
+        <v>6.8054</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>0.73</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.8731905070691512</v>
+        <v>-0.2936</v>
       </c>
       <c r="J53" t="n">
-        <v>-12.22466709896812</v>
+        <v>-4.1104</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>0.49</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.434369778215999</v>
+        <v>-0.6919</v>
       </c>
       <c r="J54" t="n">
-        <v>-20.08117689502399</v>
+        <v>-9.6866</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.37</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.623582662347244</v>
+        <v>-0.8527</v>
       </c>
       <c r="J55" t="n">
-        <v>-22.73015727286141</v>
+        <v>-11.9378</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.25</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.779796085429632</v>
+        <v>-1.0011</v>
       </c>
       <c r="J56" t="n">
-        <v>-24.91714519601485</v>
+        <v>-14.0154</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.87</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6585709750995787</v>
+        <v>1.7175</v>
       </c>
       <c r="J57" t="n">
-        <v>9.219993651394102</v>
+        <v>24.045</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.65</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5115445868108908</v>
+        <v>1.3206</v>
       </c>
       <c r="J58" t="n">
-        <v>7.161624215352471</v>
+        <v>18.4884</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>1.6</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4463610084676037</v>
+        <v>1.2011</v>
       </c>
       <c r="J59" t="n">
-        <v>6.249054118546452</v>
+        <v>16.8154</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>1.58</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4248894759490592</v>
+        <v>1.1567</v>
       </c>
       <c r="J60" t="n">
-        <v>5.948452663286829</v>
+        <v>16.1938</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>1.36</v>
       </c>
       <c r="I61" t="n">
-        <v>0.269337812774666</v>
+        <v>0.7058</v>
       </c>
       <c r="J61" t="n">
-        <v>3.770729378845323</v>
+        <v>9.8812</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.62</v>
       </c>
       <c r="I62" t="n">
-        <v>1.167959644750983</v>
+        <v>1.4552</v>
       </c>
       <c r="J62" t="n">
-        <v>23.35919289501966</v>
+        <v>29.104</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.49</v>
       </c>
       <c r="I63" t="n">
-        <v>1.01334462273015</v>
+        <v>1.2021</v>
       </c>
       <c r="J63" t="n">
-        <v>20.266892454603</v>
+        <v>24.042</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3282802516522294</v>
+        <v>0.3499</v>
       </c>
       <c r="J64" t="n">
-        <v>6.565605033044588</v>
+        <v>6.998</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>1.03</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1084604975086446</v>
+        <v>0.0149</v>
       </c>
       <c r="J65" t="n">
-        <v>2.169209950172893</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.72</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4767271779607546</v>
+        <v>-0.9119</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.534543559215091</v>
+        <v>-18.238</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0948932552101437</v>
+        <v>0.2475</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.897865104202874</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>0.92</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5301527466983494</v>
+        <v>-0.1368</v>
       </c>
       <c r="J68" t="n">
-        <v>-10.60305493396699</v>
+        <v>-2.736</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>0.87</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.7238301749180645</v>
+        <v>-0.2425</v>
       </c>
       <c r="J69" t="n">
-        <v>-14.47660349836129</v>
+        <v>-4.85</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7517357257156021</v>
+        <v>-0.2601</v>
       </c>
       <c r="J70" t="n">
-        <v>-15.03471451431204</v>
+        <v>-5.202</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.78</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9394568654723354</v>
+        <v>-0.3872</v>
       </c>
       <c r="J71" t="n">
-        <v>-18.78913730944671</v>
+        <v>-7.744</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.45</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8855541419848362</v>
+        <v>1.1872</v>
       </c>
       <c r="J72" t="n">
-        <v>21.25329940763607</v>
+        <v>28.4928</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.37</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7805932508868769</v>
+        <v>1.0191</v>
       </c>
       <c r="J73" t="n">
-        <v>18.73423802128504</v>
+        <v>24.4584</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>0.91</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2688100618577114</v>
+        <v>-0.4021</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.451441484585073</v>
+        <v>-9.650399999999999</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3447490209667127</v>
+        <v>-0.5145</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.273976503201105</v>
+        <v>-12.348</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5213212442794103</v>
+        <v>-0.7893</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.51170986270585</v>
+        <v>-18.9432</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.16</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2048439542536512</v>
+        <v>0.3309</v>
       </c>
       <c r="J77" t="n">
-        <v>4.916254902087628</v>
+        <v>7.9416</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1174643656245927</v>
+        <v>0.2348</v>
       </c>
       <c r="J78" t="n">
-        <v>2.819144774990225</v>
+        <v>5.6352</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0328221761802391</v>
+        <v>0.1629</v>
       </c>
       <c r="J79" t="n">
-        <v>0.7877322283257383</v>
+        <v>3.9096</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.509769520155274</v>
+        <v>-0.2219</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.23446848372658</v>
+        <v>-5.3256</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.9431796646315406</v>
+        <v>-0.53</v>
       </c>
       <c r="J81" t="n">
-        <v>-22.63631195115697</v>
+        <v>-12.72</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.45</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5941831399104579</v>
+        <v>1.1286</v>
       </c>
       <c r="J82" t="n">
-        <v>14.26039535785099</v>
+        <v>27.0864</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.27</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3946423847777166</v>
+        <v>0.7297</v>
       </c>
       <c r="J83" t="n">
-        <v>9.4714172346652</v>
+        <v>17.5128</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>1.19</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2637880293728459</v>
+        <v>0.5167</v>
       </c>
       <c r="J84" t="n">
-        <v>6.330912704948302</v>
+        <v>12.4008</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.009156820025604143</v>
+        <v>0.0568</v>
       </c>
       <c r="J85" t="n">
-        <v>0.2197636806144994</v>
+        <v>1.3632</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.06812130516553183</v>
+        <v>-0.2553</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.634911323972764</v>
+        <v>-6.1272</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.06112296359360654</v>
+        <v>0.2863</v>
       </c>
       <c r="J87" t="n">
-        <v>1.466951126246557</v>
+        <v>6.8712</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.09531667756161592</v>
+        <v>-0.0262</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.287600261478782</v>
+        <v>-0.6288</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2610545739323977</v>
+        <v>-0.2156</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.265309774377544</v>
+        <v>-5.1744</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2973632514310723</v>
+        <v>-0.2534</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.136718034345735</v>
+        <v>-6.0816</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5628968037160986</v>
+        <v>-0.5894</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.50952328918637</v>
+        <v>-14.1456</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.63</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8284255483467898</v>
+        <v>1.4624</v>
       </c>
       <c r="J92" t="n">
-        <v>16.5685109669358</v>
+        <v>29.248</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>1.47</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6898510449442554</v>
+        <v>1.1497</v>
       </c>
       <c r="J93" t="n">
-        <v>13.79702089888511</v>
+        <v>22.994</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>1.15</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2298616321191506</v>
+        <v>0.3639</v>
       </c>
       <c r="J94" t="n">
-        <v>4.597232642383013</v>
+        <v>7.278</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1068994185663305</v>
+        <v>0.1056</v>
       </c>
       <c r="J95" t="n">
-        <v>2.13798837132661</v>
+        <v>2.112</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2032677543170247</v>
+        <v>-0.7119</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.065355086340493</v>
+        <v>-14.238</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.1</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.04478368294677464</v>
+        <v>0.2698</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.8956736589354929</v>
+        <v>5.396</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.06975330621518455</v>
+        <v>0.2356</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.395066124303691</v>
+        <v>4.712</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>0.88</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3748180433102039</v>
+        <v>-0.2156</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.496360866204077</v>
+        <v>-4.312</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>0.8</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4947413271439107</v>
+        <v>-0.3523</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.894826542878214</v>
+        <v>-7.046</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.707651124061635</v>
+        <v>-0.6401</v>
       </c>
       <c r="J101" t="n">
-        <v>-14.1530224812327</v>
+        <v>-12.802</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.33</v>
       </c>
       <c r="I102" t="n">
-        <v>0.300298431979837</v>
+        <v>0.5847</v>
       </c>
       <c r="J102" t="n">
-        <v>6.306267071576578</v>
+        <v>12.2787</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.14</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0326085461956054</v>
+        <v>0.3206</v>
       </c>
       <c r="J103" t="n">
-        <v>0.6847794701077135</v>
+        <v>6.7326</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>0.78</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.417992561628463</v>
+        <v>-0.3936</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.777843794197723</v>
+        <v>-8.265599999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>0.74</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4532773328485108</v>
+        <v>-0.4507</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.518823989818726</v>
+        <v>-9.464700000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5317324736609153</v>
+        <v>-0.5838</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.16638194687922</v>
+        <v>-12.2598</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.64</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5697224417340584</v>
+        <v>1.4986</v>
       </c>
       <c r="J107" t="n">
-        <v>11.96417127641523</v>
+        <v>31.4706</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>1.36</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3922055457980954</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>8.236316461760003</v>
+        <v>19.635</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.08237875744534776</v>
+        <v>0.1829</v>
       </c>
       <c r="J109" t="n">
-        <v>1.729953906352303</v>
+        <v>3.8409</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.03593430168027703</v>
+        <v>-0.2568</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.7546203352858176</v>
+        <v>-5.3928</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1641799494465936</v>
+        <v>-0.5</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.447778938378466</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.91</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9884313287713998</v>
+        <v>1.0773</v>
       </c>
       <c r="J112" t="n">
-        <v>16.8033325891138</v>
+        <v>18.3141</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>1.73</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8653280248834128</v>
+        <v>0.8961</v>
       </c>
       <c r="J113" t="n">
-        <v>14.71057642301802</v>
+        <v>15.2337</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>1.27</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3337259841144525</v>
+        <v>0.3293</v>
       </c>
       <c r="J114" t="n">
-        <v>5.673341729945692</v>
+        <v>5.5981</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>1.16</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2265241463822231</v>
+        <v>0.1797</v>
       </c>
       <c r="J115" t="n">
-        <v>3.850910488497792</v>
+        <v>3.0549</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>1.03</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1093481968520244</v>
+        <v>-0.0299</v>
       </c>
       <c r="J116" t="n">
-        <v>1.858919346484416</v>
+        <v>-0.5083</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.2228529906428</v>
+        <v>0.0161</v>
       </c>
       <c r="J117" t="n">
-        <v>-3.7885008409276</v>
+        <v>0.2737</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>0.79</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3765037925232536</v>
+        <v>-0.2565</v>
       </c>
       <c r="J118" t="n">
-        <v>-6.400564472895311</v>
+        <v>-4.3605</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>0.73</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4496063403609415</v>
+        <v>-0.355</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.643307786136005</v>
+        <v>-6.035</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.58</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6574928947056803</v>
+        <v>-0.6052</v>
       </c>
       <c r="J120" t="n">
-        <v>-11.17737920999656</v>
+        <v>-10.2884</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.46</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7608209681516072</v>
+        <v>-0.7637</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.93395645857732</v>
+        <v>-12.9829</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.39</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2915237319549437</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="J122" t="n">
-        <v>5.830474639098874</v>
+        <v>13.336</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.36</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2586814210575764</v>
+        <v>0.6298</v>
       </c>
       <c r="J123" t="n">
-        <v>5.173628421151529</v>
+        <v>12.596</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>0.8</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.4334171351695963</v>
+        <v>-0.3577</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.668342703391927</v>
+        <v>-7.154</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>0.53</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.639288792476795</v>
+        <v>-0.7163</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.7857758495359</v>
+        <v>-14.326</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.45</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6873646435653091</v>
+        <v>-0.8102</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.74729287130618</v>
+        <v>-16.204</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.97</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7161209414755599</v>
+        <v>1.9858</v>
       </c>
       <c r="J127" t="n">
-        <v>14.3224188295112</v>
+        <v>39.716</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>1.31</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3038054722551159</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J128" t="n">
-        <v>6.076109445102318</v>
+        <v>15.212</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2260974979966318</v>
+        <v>0.6161</v>
       </c>
       <c r="J129" t="n">
-        <v>4.521949959932636</v>
+        <v>12.322</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.01921965590602695</v>
+        <v>-0.1518</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.384393118120539</v>
+        <v>-3.036</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.89</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1725550963457934</v>
+        <v>-0.5263</v>
       </c>
       <c r="J131" t="n">
-        <v>-3.451101926915868</v>
+        <v>-10.526</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.2049318021114834</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>-4.098636042229669</v>
+        <v>-1.624</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>0.91</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2410946300716842</v>
+        <v>-0.1391</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.821892601433683</v>
+        <v>-2.782</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>0.89</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2687303617006344</v>
+        <v>-0.1778</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.374607234012688</v>
+        <v>-3.556</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>0.85</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3417811562870054</v>
+        <v>-0.2627</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.835623125740109</v>
+        <v>-5.254</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4216467867961892</v>
+        <v>-0.3773</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.432935735923783</v>
+        <v>-7.546</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>1.69</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8634287718629079</v>
+        <v>0.8963</v>
       </c>
       <c r="J137" t="n">
-        <v>17.26857543725816</v>
+        <v>17.926</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>1.54</v>
       </c>
       <c r="I138" t="n">
-        <v>0.7406439067272844</v>
+        <v>0.733</v>
       </c>
       <c r="J138" t="n">
-        <v>14.81287813454569</v>
+        <v>14.66</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>1.28</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4402068636153801</v>
+        <v>0.4069</v>
       </c>
       <c r="J139" t="n">
-        <v>8.804137272307601</v>
+        <v>8.138</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.97</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.01507913540908518</v>
+        <v>-0.16</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.3015827081817035</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2249317697316048</v>
+        <v>-0.44</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.498635394632097</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.84</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7903267441812272</v>
+        <v>1.8989</v>
       </c>
       <c r="J142" t="n">
-        <v>18.96784186034945</v>
+        <v>45.5736</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>1.11</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1354553569033807</v>
+        <v>0.3539</v>
       </c>
       <c r="J143" t="n">
-        <v>3.250928565681136</v>
+        <v>8.493600000000001</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>1.02</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.06383627516190535</v>
+        <v>0.0259</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.532070603885728</v>
+        <v>0.6216</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.78</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3200097010969629</v>
+        <v>-0.7494</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.680232826327108</v>
+        <v>-17.9856</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3593890634189529</v>
+        <v>-0.8651</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.62533752205487</v>
+        <v>-20.7624</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.43</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4821394236878913</v>
+        <v>0.6688</v>
       </c>
       <c r="J147" t="n">
-        <v>11.57134616850939</v>
+        <v>16.0512</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.11</v>
       </c>
       <c r="I148" t="n">
-        <v>0.06893395626263484</v>
+        <v>0.2292</v>
       </c>
       <c r="J148" t="n">
-        <v>1.654414950303236</v>
+        <v>5.5008</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1116607452985286</v>
+        <v>0.0625</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.679857887164686</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>0.86</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3216711832857582</v>
+        <v>-0.3037</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.720108398858198</v>
+        <v>-7.2888</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.77</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4008696544862447</v>
+        <v>-0.4342</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.620871707669874</v>
+        <v>-10.4208</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4885972028630827</v>
+        <v>0.966</v>
       </c>
       <c r="J152" t="n">
-        <v>11.2377356658509</v>
+        <v>22.218</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.09</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1202059847570782</v>
+        <v>0.2467</v>
       </c>
       <c r="J153" t="n">
-        <v>2.764737649412798</v>
+        <v>5.6741</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1.07</v>
       </c>
       <c r="I154" t="n">
-        <v>0.08973806610953766</v>
+        <v>0.1831</v>
       </c>
       <c r="J154" t="n">
-        <v>2.063975520519366</v>
+        <v>4.2113</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>1.07</v>
       </c>
       <c r="I155" t="n">
-        <v>0.08973806610953766</v>
+        <v>0.1831</v>
       </c>
       <c r="J155" t="n">
-        <v>2.063975520519366</v>
+        <v>4.2113</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>1.06</v>
       </c>
       <c r="I156" t="n">
-        <v>0.07506752317229431</v>
+        <v>0.1505</v>
       </c>
       <c r="J156" t="n">
-        <v>1.726553032962769</v>
+        <v>3.4615</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.5</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5533286551473191</v>
+        <v>0.7855</v>
       </c>
       <c r="J157" t="n">
-        <v>12.72655906838834</v>
+        <v>18.0665</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1243986277817287</v>
+        <v>0.3004</v>
       </c>
       <c r="J158" t="n">
-        <v>2.861168438979759</v>
+        <v>6.9092</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>0.95</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1480525543523351</v>
+        <v>-0.0944</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.405208750103707</v>
+        <v>-2.1712</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.59</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5180149125161011</v>
+        <v>-0.6485</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.91434298787033</v>
+        <v>-14.9155</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.52</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5642751941265145</v>
+        <v>-0.7328</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.97832946490983</v>
+        <v>-16.8544</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.73</v>
       </c>
       <c r="I162" t="n">
-        <v>0.565845870938283</v>
+        <v>1.6203</v>
       </c>
       <c r="J162" t="n">
-        <v>11.31691741876566</v>
+        <v>32.406</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.54</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4664200548637772</v>
+        <v>1.263</v>
       </c>
       <c r="J163" t="n">
-        <v>9.328401097275545</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>1.42</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3886578233317933</v>
+        <v>1.017</v>
       </c>
       <c r="J164" t="n">
-        <v>7.773156466635865</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.03640986676076015</v>
+        <v>-0.3201</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.7281973352152029</v>
+        <v>-6.402</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3209020106110455</v>
+        <v>-0.8616</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.418040212220909</v>
+        <v>-17.232</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.14</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.01069553577539033</v>
+        <v>0.3456</v>
       </c>
       <c r="J167" t="n">
-        <v>-0.2139107155078067</v>
+        <v>6.912</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2059991316338683</v>
+        <v>0.0097</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.119982632677365</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4263137440765177</v>
+        <v>-0.2538</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.526274881530355</v>
+        <v>-5.076</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.609007985277739</v>
+        <v>-0.4607</v>
       </c>
       <c r="J170" t="n">
-        <v>-12.18015970555478</v>
+        <v>-9.214</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.61</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7215755079215407</v>
+        <v>-0.6088</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.43151015843081</v>
+        <v>-12.176</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.98</v>
       </c>
       <c r="I172" t="n">
-        <v>0.696630072526325</v>
+        <v>1.9358</v>
       </c>
       <c r="J172" t="n">
-        <v>11.1460811604212</v>
+        <v>30.9728</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.81</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6175393248040393</v>
+        <v>1.6636</v>
       </c>
       <c r="J173" t="n">
-        <v>9.880629196864628</v>
+        <v>26.6176</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>1.54</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4377417334800199</v>
+        <v>1.1448</v>
       </c>
       <c r="J174" t="n">
-        <v>7.003867735680318</v>
+        <v>18.3168</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>1.24</v>
       </c>
       <c r="I175" t="n">
-        <v>0.19135094768851</v>
+        <v>0.4743</v>
       </c>
       <c r="J175" t="n">
-        <v>3.061615163016159</v>
+        <v>7.5888</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>1</v>
       </c>
       <c r="I176" t="n">
-        <v>0.05563732032818524</v>
+        <v>-0.2057</v>
       </c>
       <c r="J176" t="n">
-        <v>0.8901971252509638</v>
+        <v>-3.2912</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1933216006472236</v>
+        <v>0.2828</v>
       </c>
       <c r="J177" t="n">
-        <v>-3.093145610355578</v>
+        <v>4.5248</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>0.75</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.4883660882940276</v>
+        <v>-0.2963</v>
       </c>
       <c r="J178" t="n">
-        <v>-7.813857412704441</v>
+        <v>-4.7408</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>0.68</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.5843439640461781</v>
+        <v>-0.4105</v>
       </c>
       <c r="J179" t="n">
-        <v>-9.349503424738849</v>
+        <v>-6.568</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>0.49</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.8546749236444569</v>
+        <v>-0.7131</v>
       </c>
       <c r="J180" t="n">
-        <v>-13.67479877831131</v>
+        <v>-11.4096</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.32</v>
       </c>
       <c r="I181" t="n">
-        <v>-1.000531936308041</v>
+        <v>-0.9268</v>
       </c>
       <c r="J181" t="n">
-        <v>-16.00851098092865</v>
+        <v>-14.8288</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.03</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1098719444032043</v>
+        <v>0.1469</v>
       </c>
       <c r="J182" t="n">
-        <v>-2.307310832467291</v>
+        <v>3.0849</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1342564559127977</v>
+        <v>0.0994</v>
       </c>
       <c r="J183" t="n">
-        <v>-2.819385574168752</v>
+        <v>2.0874</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>0.87</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3506052449443479</v>
+        <v>-0.2215</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.362710143831306</v>
+        <v>-4.6515</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4512637669935651</v>
+        <v>-0.3296</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.476539106864866</v>
+        <v>-6.9216</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.64</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6370662205280936</v>
+        <v>-0.5725</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.37839063108997</v>
+        <v>-12.0225</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>2.01</v>
       </c>
       <c r="I187" t="n">
-        <v>0.9298230754214368</v>
+        <v>2.0303</v>
       </c>
       <c r="J187" t="n">
-        <v>19.52628458385017</v>
+        <v>42.6363</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.47</v>
       </c>
       <c r="I188" t="n">
-        <v>0.5766195322822324</v>
+        <v>1.1338</v>
       </c>
       <c r="J188" t="n">
-        <v>12.10901017792688</v>
+        <v>23.8098</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.02</v>
       </c>
       <c r="I189" t="n">
-        <v>0.01587938661386537</v>
+        <v>-0.0429</v>
       </c>
       <c r="J189" t="n">
-        <v>0.3334671188911728</v>
+        <v>-0.9009</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.01523705953115496</v>
+        <v>-0.2006</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.3199782501542542</v>
+        <v>-4.2126</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.79</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2445925007588857</v>
+        <v>-0.7661</v>
       </c>
       <c r="J191" t="n">
-        <v>-5.1364425159366</v>
+        <v>-16.0881</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.03659450010043285</v>
+        <v>0.2501</v>
       </c>
       <c r="J192" t="n">
-        <v>1.28080750351515</v>
+        <v>8.753500000000001</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.02375396507356176</v>
+        <v>0.2333</v>
       </c>
       <c r="J193" t="n">
-        <v>0.8313887775746615</v>
+        <v>8.1655</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.03</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.08952403809493174</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.133341333322611</v>
+        <v>3.4685</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>0.97</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.230950281581579</v>
+        <v>-0.0849</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.083259855355266</v>
+        <v>-2.9715</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5649566614456719</v>
+        <v>-0.4913</v>
       </c>
       <c r="J196" t="n">
-        <v>-19.77348315059852</v>
+        <v>-17.1955</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.39</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5711010066046885</v>
+        <v>1.0382</v>
       </c>
       <c r="J197" t="n">
-        <v>19.9885352311641</v>
+        <v>36.337</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>1.38</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5610516946158315</v>
+        <v>1.0168</v>
       </c>
       <c r="J198" t="n">
-        <v>19.6368093115541</v>
+        <v>35.588</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>1.11</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1680126742313403</v>
+        <v>0.3241</v>
       </c>
       <c r="J199" t="n">
-        <v>5.880443598096909</v>
+        <v>11.3435</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1858681540912062</v>
+        <v>-0.4764</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.505385393192215</v>
+        <v>-16.674</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2627199706339476</v>
+        <v>-0.6831</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.195198972188168</v>
+        <v>-23.9085</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.64</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2300354218240384</v>
+        <v>0.944</v>
       </c>
       <c r="J202" t="n">
-        <v>4.600708436480767</v>
+        <v>18.88</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.29</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1065149776130623</v>
+        <v>0.5308</v>
       </c>
       <c r="J203" t="n">
-        <v>2.130299552261246</v>
+        <v>10.616</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.999826551997834</v>
+        <v>-0.52</v>
       </c>
       <c r="J204" t="n">
-        <v>-19.99653103995668</v>
+        <v>-10.4</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>0.62</v>
       </c>
       <c r="I205" t="n">
-        <v>-1.103353820510556</v>
+        <v>-0.6102</v>
       </c>
       <c r="J205" t="n">
-        <v>-22.06707641021111</v>
+        <v>-12.204</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.42</v>
       </c>
       <c r="I206" t="n">
-        <v>-1.354320034086789</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="J206" t="n">
-        <v>-27.08640068173578</v>
+        <v>-16.946</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.29</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5029418933241003</v>
+        <v>0.4581</v>
       </c>
       <c r="J207" t="n">
-        <v>10.05883786648201</v>
+        <v>9.162000000000001</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.25</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4553655456417602</v>
+        <v>0.4031</v>
       </c>
       <c r="J208" t="n">
-        <v>9.107310912835203</v>
+        <v>8.061999999999999</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>1.11</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2124379579130982</v>
+        <v>0.1693</v>
       </c>
       <c r="J209" t="n">
-        <v>4.248759158261964</v>
+        <v>3.386</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>1.06</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1363426169522794</v>
+        <v>0.0801</v>
       </c>
       <c r="J210" t="n">
-        <v>2.726852339045589</v>
+        <v>1.602</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>1.04</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1075445436767967</v>
+        <v>0.0416</v>
       </c>
       <c r="J211" t="n">
-        <v>2.150890873535935</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>2.08</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4637256985832856</v>
+        <v>2.0249</v>
       </c>
       <c r="J212" t="n">
-        <v>6.955885478749284</v>
+        <v>30.3735</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.87</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4065322095493928</v>
+        <v>1.7535</v>
       </c>
       <c r="J213" t="n">
-        <v>6.097983143240892</v>
+        <v>26.3025</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>1.55</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2655080774516457</v>
+        <v>1.1328</v>
       </c>
       <c r="J214" t="n">
-        <v>3.982621161774685</v>
+        <v>16.992</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>1.51</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2377344249761595</v>
+        <v>1.0398</v>
       </c>
       <c r="J215" t="n">
-        <v>3.566016374642393</v>
+        <v>15.597</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.75</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1511096097962754</v>
+        <v>-0.9026</v>
       </c>
       <c r="J216" t="n">
-        <v>-2.266644146944131</v>
+        <v>-13.539</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>0.65</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.4667252533506515</v>
+        <v>-0.4243</v>
       </c>
       <c r="J217" t="n">
-        <v>-7.000878800259772</v>
+        <v>-6.3645</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>0.64</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.4780432495268069</v>
+        <v>-0.4409</v>
       </c>
       <c r="J218" t="n">
-        <v>-7.170648742902103</v>
+        <v>-6.6135</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>0.62</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.5035559121265405</v>
+        <v>-0.4761</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.553338681898108</v>
+        <v>-7.1415</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>0.59</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5583490616640742</v>
+        <v>-0.5413</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.375235924961112</v>
+        <v>-8.1195</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.53</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6244913980202865</v>
+        <v>-0.6374</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.367370970304298</v>
+        <v>-9.561</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.66</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3247347414649693</v>
+        <v>1.4309</v>
       </c>
       <c r="J222" t="n">
-        <v>5.845225346369448</v>
+        <v>25.7562</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>1.63</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3138104133304225</v>
+        <v>1.3741</v>
       </c>
       <c r="J223" t="n">
-        <v>5.648587439947605</v>
+        <v>24.7338</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>1.48</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2485469445955238</v>
+        <v>1.0719</v>
       </c>
       <c r="J224" t="n">
-        <v>4.473845002719428</v>
+        <v>19.2942</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>1.43</v>
       </c>
       <c r="I225" t="n">
-        <v>0.2177888438273963</v>
+        <v>0.9571</v>
       </c>
       <c r="J225" t="n">
-        <v>3.920199188893133</v>
+        <v>17.2278</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.89</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1393413406258277</v>
+        <v>-0.5544</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.508144131264899</v>
+        <v>-9.979200000000001</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.12</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.08516117977687762</v>
+        <v>0.3443</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.532901235983797</v>
+        <v>6.1974</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>0.86</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.308112787227356</v>
+        <v>-0.1839</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.546030170092409</v>
+        <v>-3.3102</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>0.84</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3294261982862651</v>
+        <v>-0.2181</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.929671569152771</v>
+        <v>-3.9258</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>0.58</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.6145656910047499</v>
+        <v>-0.6303</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.0621824380855</v>
+        <v>-11.3454</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.53</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6502772576624686</v>
+        <v>-0.6944</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.70499063792443</v>
+        <v>-12.4992</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.48</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4477601328118451</v>
+        <v>1.2</v>
       </c>
       <c r="J232" t="n">
-        <v>10.29848305467244</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>1.26</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2820122738840825</v>
+        <v>0.7175</v>
       </c>
       <c r="J233" t="n">
-        <v>6.486282299333896</v>
+        <v>16.5025</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>1.07</v>
       </c>
       <c r="I234" t="n">
-        <v>0.04590115494602121</v>
+        <v>0.164</v>
       </c>
       <c r="J234" t="n">
-        <v>1.055726563758488</v>
+        <v>3.772</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>1.05</v>
       </c>
       <c r="I235" t="n">
-        <v>0.02478290911742736</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J235" t="n">
-        <v>0.5700069097008292</v>
+        <v>2.2908</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>0.96</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.09210155215692958</v>
+        <v>-0.2829</v>
       </c>
       <c r="J236" t="n">
-        <v>-2.11833569960938</v>
+        <v>-6.5067</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>1.24</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1170240847497017</v>
+        <v>0.4609</v>
       </c>
       <c r="J237" t="n">
-        <v>2.69155394924314</v>
+        <v>10.6007</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>1.04</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.08047538122530654</v>
+        <v>0.1404</v>
       </c>
       <c r="J238" t="n">
-        <v>-1.85093376818205</v>
+        <v>3.2292</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4569961096715331</v>
+        <v>-0.2053</v>
       </c>
       <c r="J239" t="n">
-        <v>-10.51091052244526</v>
+        <v>-4.7219</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6359428024024141</v>
+        <v>-0.3532</v>
       </c>
       <c r="J240" t="n">
-        <v>-14.62668445525552</v>
+        <v>-8.1236</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7943736009014575</v>
+        <v>-0.495</v>
       </c>
       <c r="J241" t="n">
-        <v>-18.27059282073352</v>
+        <v>-11.385</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.09</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.1289713639807279</v>
+        <v>0.2799</v>
       </c>
       <c r="J242" t="n">
-        <v>-2.321484551653102</v>
+        <v>5.0382</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>0.9</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.3216932372878577</v>
+        <v>-0.1315</v>
       </c>
       <c r="J243" t="n">
-        <v>-5.790478271181438</v>
+        <v>-2.367</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.4647203397695524</v>
+        <v>-0.3035</v>
       </c>
       <c r="J244" t="n">
-        <v>-8.364966115851944</v>
+        <v>-5.463</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>0.77</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5216413320924518</v>
+        <v>-0.372</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.389543977664133</v>
+        <v>-6.696</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.54</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7365129669398442</v>
+        <v>-0.6894</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.2572334049172</v>
+        <v>-12.4092</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.94</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4493565335574963</v>
+        <v>1.1151</v>
       </c>
       <c r="J247" t="n">
-        <v>8.088417604034934</v>
+        <v>20.0718</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3595527744315715</v>
+        <v>0.8309</v>
       </c>
       <c r="J248" t="n">
-        <v>6.471949939768288</v>
+        <v>14.9562</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>1.58</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3277154433683234</v>
+        <v>0.7431</v>
       </c>
       <c r="J249" t="n">
-        <v>5.898877980629821</v>
+        <v>13.3758</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>1.17</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0885169784599687</v>
+        <v>0.2005</v>
       </c>
       <c r="J250" t="n">
-        <v>1.593305612279436</v>
+        <v>3.609</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.57</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6700437706317509</v>
+        <v>-0.7173</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.06078787137152</v>
+        <v>-12.9114</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.14</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2292701688561506</v>
+        <v>0.4822</v>
       </c>
       <c r="J252" t="n">
-        <v>5.273213883691464</v>
+        <v>11.0906</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>1.1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1852571194948466</v>
+        <v>0.3657</v>
       </c>
       <c r="J253" t="n">
-        <v>4.260913748381472</v>
+        <v>8.411099999999999</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>1.02</v>
       </c>
       <c r="I254" t="n">
-        <v>0.05628014511538239</v>
+        <v>0.0619</v>
       </c>
       <c r="J254" t="n">
-        <v>1.294443337653795</v>
+        <v>1.4237</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>0.99</v>
       </c>
       <c r="I255" t="n">
-        <v>0.01018886208678463</v>
+        <v>-0.1072</v>
       </c>
       <c r="J255" t="n">
-        <v>0.2343438279960465</v>
+        <v>-2.4656</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.97</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0352188317968313</v>
+        <v>-0.1913</v>
       </c>
       <c r="J256" t="n">
-        <v>-0.81003313132712</v>
+        <v>-4.3999</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>1.2</v>
       </c>
       <c r="I257" t="n">
-        <v>0.1174073346122522</v>
+        <v>0.3913</v>
       </c>
       <c r="J257" t="n">
-        <v>2.7003686960818</v>
+        <v>8.9999</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1174073346122522</v>
+        <v>0.3913</v>
       </c>
       <c r="J258" t="n">
-        <v>2.7003686960818</v>
+        <v>8.9999</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>0.95</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3043836506322571</v>
+        <v>-0.1255</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.000823964541914</v>
+        <v>-2.8865</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>0.85</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5308145535227728</v>
+        <v>-0.3029</v>
       </c>
       <c r="J260" t="n">
-        <v>-12.20873473102377</v>
+        <v>-6.9667</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7934991357030765</v>
+        <v>-0.5292</v>
       </c>
       <c r="J261" t="n">
-        <v>-18.25048012117076</v>
+        <v>-12.1716</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>1.63</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3177273843740507</v>
+        <v>1.4511</v>
       </c>
       <c r="J262" t="n">
-        <v>6.672275071855064</v>
+        <v>30.4731</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>1.3</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1834434425593272</v>
+        <v>0.7625</v>
       </c>
       <c r="J263" t="n">
-        <v>3.852312293745871</v>
+        <v>16.0125</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>1.23</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1273772814543043</v>
+        <v>0.5647</v>
       </c>
       <c r="J264" t="n">
-        <v>2.67492291054039</v>
+        <v>11.8587</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>1.04</v>
       </c>
       <c r="I265" t="n">
-        <v>0.02377487736479494</v>
+        <v>0.0317</v>
       </c>
       <c r="J265" t="n">
-        <v>0.4992724246606938</v>
+        <v>0.6657</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>1.04</v>
       </c>
       <c r="I266" t="n">
-        <v>0.02377487736479494</v>
+        <v>0.0317</v>
       </c>
       <c r="J266" t="n">
-        <v>0.4992724246606938</v>
+        <v>0.6657</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>1.3</v>
       </c>
       <c r="I267" t="n">
-        <v>0.1963540562571681</v>
+        <v>0.5749</v>
       </c>
       <c r="J267" t="n">
-        <v>4.123435181400531</v>
+        <v>12.0729</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>0.97</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1497424036155204</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.144590475925928</v>
+        <v>-0.1827</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>0.68</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.5347647662710775</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="J269" t="n">
-        <v>-11.23006009169263</v>
+        <v>-10.7856</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>0.66</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5532370787668104</v>
+        <v>-0.5407</v>
       </c>
       <c r="J270" t="n">
-        <v>-11.61797865410302</v>
+        <v>-11.3547</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5710815986392667</v>
+        <v>-0.5674</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.9927135714246</v>
+        <v>-11.9154</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>1.15</v>
       </c>
       <c r="I272" t="n">
-        <v>0.01412197188345941</v>
+        <v>0.4007</v>
       </c>
       <c r="J272" t="n">
-        <v>0.2683174657857287</v>
+        <v>7.6133</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>0.98</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.2208343200028834</v>
+        <v>0.051</v>
       </c>
       <c r="J273" t="n">
-        <v>-4.195852080054784</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>0.68</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.8418647337672297</v>
+        <v>-0.4853</v>
       </c>
       <c r="J274" t="n">
-        <v>-15.99542994157737</v>
+        <v>-9.220700000000001</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>0.54</v>
       </c>
       <c r="I275" t="n">
-        <v>-1.056143105995996</v>
+        <v>-0.6767</v>
       </c>
       <c r="J275" t="n">
-        <v>-20.06671901392392</v>
+        <v>-12.8573</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>0.47</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.145327829229292</v>
+        <v>-0.7645</v>
       </c>
       <c r="J276" t="n">
-        <v>-21.76122875535655</v>
+        <v>-14.5255</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>1.77</v>
       </c>
       <c r="I277" t="n">
-        <v>0.9031342168114164</v>
+        <v>1.6938</v>
       </c>
       <c r="J277" t="n">
-        <v>17.15955011941691</v>
+        <v>32.1822</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>1.38</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5814060915458433</v>
+        <v>0.9318</v>
       </c>
       <c r="J278" t="n">
-        <v>11.04671573937102</v>
+        <v>17.7042</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>1.26</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3917007626465618</v>
+        <v>0.6239</v>
       </c>
       <c r="J279" t="n">
-        <v>7.442314490284674</v>
+        <v>11.8541</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>1.09</v>
       </c>
       <c r="I280" t="n">
-        <v>0.1783809962581445</v>
+        <v>0.1752</v>
       </c>
       <c r="J280" t="n">
-        <v>3.389238928904746</v>
+        <v>3.3288</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.88</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.03451417302182475</v>
+        <v>-0.5502</v>
       </c>
       <c r="J281" t="n">
-        <v>-0.6557692874146701</v>
+        <v>-10.4538</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7250/event_7250_evp_summary.xlsx
+++ b/database/event/7250/event_7250_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>6.0183</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1.4522</v>
       </c>
       <c r="D2" t="n">
         <v>2.0099</v>
@@ -545,7 +545,7 @@
         <v>5.6078</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1.3532</v>
       </c>
       <c r="D3" t="n">
         <v>1.8441</v>
@@ -591,7 +591,7 @@
         <v>4.3074</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.0394</v>
       </c>
       <c r="D4" t="n">
         <v>1.3187</v>
@@ -637,7 +637,7 @@
         <v>4.2119</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.0163</v>
       </c>
       <c r="D5" t="n">
         <v>1.2802</v>
@@ -683,7 +683,7 @@
         <v>3.617</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.8728</v>
       </c>
       <c r="D6" t="n">
         <v>1.0398</v>
@@ -729,7 +729,7 @@
         <v>3.4974</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.8439</v>
       </c>
       <c r="D7" t="n">
         <v>0.9915</v>
@@ -775,7 +775,7 @@
         <v>2.8223</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.681</v>
       </c>
       <c r="D8" t="n">
         <v>0.7188</v>
@@ -821,7 +821,7 @@
         <v>2.6741</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.6453</v>
       </c>
       <c r="D9" t="n">
         <v>0.6589</v>
@@ -867,7 +867,7 @@
         <v>2.62</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.6322</v>
       </c>
       <c r="D10" t="n">
         <v>0.6371</v>
@@ -913,7 +913,7 @@
         <v>2.3805</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.5744</v>
       </c>
       <c r="D11" t="n">
         <v>0.5403</v>
@@ -959,7 +959,7 @@
         <v>2.0099</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="D12" t="n">
         <v>0.3906</v>
@@ -1005,7 +1005,7 @@
         <v>1.8636</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.4497</v>
       </c>
       <c r="D13" t="n">
         <v>0.3315</v>
@@ -1051,7 +1051,7 @@
         <v>1.8418</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.4444</v>
       </c>
       <c r="D14" t="n">
         <v>0.3227</v>
@@ -1097,7 +1097,7 @@
         <v>1.5344</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.3703</v>
       </c>
       <c r="D15" t="n">
         <v>0.1985</v>
@@ -1143,7 +1143,7 @@
         <v>1.525</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="D16" t="n">
         <v>0.1947</v>
@@ -1189,7 +1189,7 @@
         <v>1.4871</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.3588</v>
       </c>
       <c r="D17" t="n">
         <v>0.1794</v>
@@ -1235,7 +1235,7 @@
         <v>1.4082</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.3398</v>
       </c>
       <c r="D18" t="n">
         <v>0.1475</v>
@@ -1281,7 +1281,7 @@
         <v>1.215</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.2932</v>
       </c>
       <c r="D19" t="n">
         <v>0.06950000000000001</v>
@@ -1327,7 +1327,7 @@
         <v>0.9323</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="D20" t="n">
         <v>-0.0447</v>
@@ -1373,7 +1373,7 @@
         <v>0.6516999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1573</v>
       </c>
       <c r="D21" t="n">
         <v>-0.1581</v>
@@ -1419,7 +1419,7 @@
         <v>0.4581</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.1105</v>
       </c>
       <c r="D22" t="n">
         <v>-0.2363</v>
@@ -1465,7 +1465,7 @@
         <v>0.3859</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.0931</v>
       </c>
       <c r="D23" t="n">
         <v>-0.2655</v>
@@ -1511,7 +1511,7 @@
         <v>0.3314</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="D24" t="n">
         <v>-0.2875</v>
@@ -1557,7 +1557,7 @@
         <v>0.1621</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.0391</v>
       </c>
       <c r="D25" t="n">
         <v>-0.3559</v>
@@ -1603,7 +1603,7 @@
         <v>0.1414</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.0341</v>
       </c>
       <c r="D26" t="n">
         <v>-0.3642</v>
@@ -1649,7 +1649,7 @@
         <v>0.1089</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.0263</v>
       </c>
       <c r="D27" t="n">
         <v>-0.3774</v>
@@ -1695,7 +1695,7 @@
         <v>-0.1208</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.0291</v>
       </c>
       <c r="D28" t="n">
         <v>-0.4702</v>
@@ -1741,7 +1741,7 @@
         <v>-0.1429</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.0345</v>
       </c>
       <c r="D29" t="n">
         <v>-0.4791</v>
@@ -1787,7 +1787,7 @@
         <v>-0.1792</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.0432</v>
       </c>
       <c r="D30" t="n">
         <v>-0.4938</v>
@@ -1833,7 +1833,7 @@
         <v>-0.5576</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.1346</v>
       </c>
       <c r="D31" t="n">
         <v>-0.6466</v>
@@ -1879,7 +1879,7 @@
         <v>-0.712</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.1718</v>
       </c>
       <c r="D32" t="n">
         <v>-0.709</v>
@@ -1925,7 +1925,7 @@
         <v>-0.7257</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.1751</v>
       </c>
       <c r="D33" t="n">
         <v>-0.7145</v>
@@ -1971,7 +1971,7 @@
         <v>-0.8663</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.209</v>
       </c>
       <c r="D34" t="n">
         <v>-0.7713</v>
@@ -2017,7 +2017,7 @@
         <v>-0.9525</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.2298</v>
       </c>
       <c r="D35" t="n">
         <v>-0.8062</v>
@@ -2063,7 +2063,7 @@
         <v>-1.0808</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.2608</v>
       </c>
       <c r="D36" t="n">
         <v>-0.858</v>
@@ -2109,7 +2109,7 @@
         <v>-1.3785</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.3326</v>
       </c>
       <c r="D37" t="n">
         <v>-0.9782</v>
@@ -2155,7 +2155,7 @@
         <v>-1.5674</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.3782</v>
       </c>
       <c r="D38" t="n">
         <v>-1.0546</v>
@@ -2201,7 +2201,7 @@
         <v>-1.7361</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.4189</v>
       </c>
       <c r="D39" t="n">
         <v>-1.1227</v>
@@ -2247,7 +2247,7 @@
         <v>-2.0927</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-0.505</v>
       </c>
       <c r="D40" t="n">
         <v>-1.2668</v>
@@ -2293,7 +2293,7 @@
         <v>-2.8198</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-0.6804</v>
       </c>
       <c r="D41" t="n">
         <v>-1.5605</v>

--- a/database/event/7250/event_7250_evp_summary.xlsx
+++ b/database/event/7250/event_7250_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.4522</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0099</v>
+        <v>1.9538</v>
       </c>
       <c r="E2" t="n">
         <v>6.0183</v>
@@ -548,7 +548,7 @@
         <v>1.3532</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8441</v>
+        <v>1.7902</v>
       </c>
       <c r="E3" t="n">
         <v>5.6078</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3074</v>
+        <v>4.8725</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0394</v>
+        <v>1.1758</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3187</v>
+        <v>1.4973</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3074</v>
+        <v>4.8725</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7396</v>
+        <v>3.3047</v>
       </c>
       <c r="G4" t="n">
         <v>1.5678</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7396</v>
+        <v>3.3047</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2205</v>
+        <v>2.6786</v>
       </c>
       <c r="J4" t="n">
         <v>1.5678</v>
@@ -621,7 +621,7 @@
         <v>120</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7883</v>
+        <v>4.2464</v>
       </c>
       <c r="N4" t="n">
         <v>221</v>
@@ -640,7 +640,7 @@
         <v>1.0163</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2802</v>
+        <v>1.2341</v>
       </c>
       <c r="E5" t="n">
         <v>4.2119</v>
@@ -686,7 +686,7 @@
         <v>0.8728</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0398</v>
+        <v>0.9971</v>
       </c>
       <c r="E6" t="n">
         <v>3.617</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4974</v>
+        <v>3.5563</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8439</v>
+        <v>0.8581</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9915</v>
+        <v>0.9729</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4974</v>
+        <v>3.5563</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4974</v>
+        <v>3.5563</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4974</v>
+        <v>3.5563</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4974</v>
+        <v>3.5563</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4974</v>
+        <v>3.5563</v>
       </c>
       <c r="N7" t="n">
         <v>143</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8223</v>
+        <v>2.8783</v>
       </c>
       <c r="C8" t="n">
-        <v>0.681</v>
+        <v>0.6945</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7188</v>
+        <v>0.7028</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8223</v>
+        <v>2.8783</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7508</v>
+        <v>4.1474</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07149999999999999</v>
+        <v>-1.2691</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7508</v>
+        <v>4.1474</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2296</v>
+        <v>3.3616</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07149999999999999</v>
+        <v>-1.2691</v>
       </c>
       <c r="K8" t="n">
         <v>71</v>
@@ -805,7 +805,7 @@
         <v>130</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3011</v>
+        <v>2.0925</v>
       </c>
       <c r="N8" t="n">
         <v>201</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.6741</v>
+        <v>2.8777</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6453</v>
+        <v>0.6944</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6589</v>
+        <v>0.7026</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6741</v>
+        <v>2.8777</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9432</v>
+        <v>0.6792</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2691</v>
+        <v>2.1985</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9432</v>
+        <v>0.6792</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1961</v>
+        <v>0.5505</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2691</v>
+        <v>2.1985</v>
       </c>
       <c r="K9" t="n">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="L9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="M9" t="n">
-        <v>1.927</v>
+        <v>2.749</v>
       </c>
       <c r="N9" t="n">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.62</v>
+        <v>2.8223</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6322</v>
+        <v>0.681</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6371</v>
+        <v>0.6805</v>
       </c>
       <c r="E10" t="n">
-        <v>2.62</v>
+        <v>2.8223</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4215</v>
+        <v>2.7508</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1985</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4215</v>
+        <v>2.7508</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3416</v>
+        <v>2.2296</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1985</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="L10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5401</v>
+        <v>2.3011</v>
       </c>
       <c r="N10" t="n">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -916,7 +916,7 @@
         <v>0.5744</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5403</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>2.3805</v>
@@ -962,7 +962,7 @@
         <v>0.485</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3906</v>
+        <v>0.3568</v>
       </c>
       <c r="E12" t="n">
         <v>2.0099</v>
@@ -998,231 +998,231 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>sLowi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8636</v>
+        <v>1.9864</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4497</v>
+        <v>0.4793</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3315</v>
+        <v>0.3475</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8636</v>
+        <v>1.9864</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3813</v>
+        <v>1.7403</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4823</v>
+        <v>0.2461</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3813</v>
+        <v>1.7403</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1196</v>
+        <v>1.4106</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4823</v>
+        <v>0.2461</v>
       </c>
       <c r="K13" t="n">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="L13" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6019</v>
+        <v>1.6567</v>
       </c>
       <c r="N13" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sLowi</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8418</v>
+        <v>1.8636</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4444</v>
+        <v>0.4497</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3227</v>
+        <v>0.2985</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8418</v>
+        <v>1.8636</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5957</v>
+        <v>1.3813</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2461</v>
+        <v>0.4823</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5957</v>
+        <v>1.3813</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2933</v>
+        <v>1.1196</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2461</v>
+        <v>0.4823</v>
       </c>
       <c r="K14" t="n">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="L14" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5394</v>
+        <v>1.6019</v>
       </c>
       <c r="N14" t="n">
-        <v>117</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5344</v>
+        <v>1.6794</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3703</v>
+        <v>0.4052</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1985</v>
+        <v>0.2252</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5344</v>
+        <v>1.6794</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3403</v>
+        <v>0.6058</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1941</v>
+        <v>1.0736</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3403</v>
+        <v>0.6058</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0864</v>
+        <v>0.491</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1941</v>
+        <v>1.0736</v>
       </c>
       <c r="K15" t="n">
+        <v>71</v>
+      </c>
+      <c r="L15" t="n">
         <v>130</v>
       </c>
-      <c r="L15" t="n">
-        <v>44</v>
-      </c>
       <c r="M15" t="n">
-        <v>1.2805</v>
+        <v>1.5646</v>
       </c>
       <c r="N15" t="n">
-        <v>174</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.525</v>
+        <v>1.5344</v>
       </c>
       <c r="C16" t="n">
-        <v>0.368</v>
+        <v>0.3703</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1947</v>
+        <v>0.1674</v>
       </c>
       <c r="E16" t="n">
-        <v>1.525</v>
+        <v>1.5344</v>
       </c>
       <c r="F16" t="n">
-        <v>1.525</v>
+        <v>1.3403</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.1941</v>
       </c>
       <c r="H16" t="n">
-        <v>1.525</v>
+        <v>1.3403</v>
       </c>
       <c r="I16" t="n">
-        <v>1.525</v>
+        <v>1.0864</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.1941</v>
       </c>
       <c r="K16" t="n">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M16" t="n">
-        <v>1.525</v>
+        <v>1.2805</v>
       </c>
       <c r="N16" t="n">
-        <v>88</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4871</v>
+        <v>1.525</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3588</v>
+        <v>0.368</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1794</v>
+        <v>0.1636</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4871</v>
+        <v>1.525</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4135</v>
+        <v>1.525</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0736</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4135</v>
+        <v>1.525</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3352</v>
+        <v>1.525</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0736</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="L17" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4088</v>
+        <v>1.525</v>
       </c>
       <c r="N17" t="n">
-        <v>201</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
@@ -1238,7 +1238,7 @@
         <v>0.3398</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1475</v>
+        <v>0.1171</v>
       </c>
       <c r="E18" t="n">
         <v>1.4082</v>
@@ -1284,7 +1284,7 @@
         <v>0.2932</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0401</v>
       </c>
       <c r="E19" t="n">
         <v>1.215</v>
@@ -1320,35 +1320,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Airax</t>
+          <t>ottoNd</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9323</v>
+        <v>0.9407</v>
       </c>
       <c r="C20" t="n">
-        <v>0.225</v>
+        <v>0.227</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0447</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9323</v>
+        <v>0.9407</v>
       </c>
       <c r="F20" t="n">
-        <v>1.806</v>
+        <v>1.9407</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8737</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.806</v>
+        <v>1.9407</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4638</v>
+        <v>1.573</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8737</v>
+        <v>-1</v>
       </c>
       <c r="K20" t="n">
         <v>83</v>
@@ -1357,7 +1357,7 @@
         <v>34</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5901</v>
+        <v>0.573</v>
       </c>
       <c r="N20" t="n">
         <v>117</v>
@@ -1366,308 +1366,308 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>Airax</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.9323</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1573</v>
+        <v>0.225</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1581</v>
+        <v>-0.0725</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.9323</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6516999999999999</v>
+        <v>1.806</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.8737</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6516999999999999</v>
+        <v>1.806</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6516999999999999</v>
+        <v>1.4638</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.8737</v>
       </c>
       <c r="K21" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.5901</v>
       </c>
       <c r="N21" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4581</v>
+        <v>0.7155</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1105</v>
+        <v>0.1727</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2363</v>
+        <v>-0.1589</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4581</v>
+        <v>0.7155</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3724</v>
+        <v>0.7155</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8305</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3724</v>
+        <v>0.7155</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3018</v>
+        <v>0.7155</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8305</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="L22" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.7155</v>
       </c>
       <c r="N22" t="n">
-        <v>221</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ottoNd</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3859</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0931</v>
+        <v>0.1573</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2655</v>
+        <v>-0.1843</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3859</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3859</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3859</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1233</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L23" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1233</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>117</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3314</v>
+        <v>0.4581</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08</v>
+        <v>0.1105</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2875</v>
+        <v>-0.2614</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3314</v>
+        <v>0.4581</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3314</v>
+        <v>-0.3724</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.8305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3314</v>
+        <v>-0.3724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3314</v>
+        <v>-0.3018</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.8305</v>
       </c>
       <c r="K24" t="n">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3314</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>143</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1621</v>
+        <v>0.3314</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0391</v>
+        <v>0.08</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3559</v>
+        <v>-0.3119</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1621</v>
+        <v>0.3314</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1621</v>
+        <v>0.3314</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1621</v>
+        <v>0.3314</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1621</v>
+        <v>0.3314</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1621</v>
+        <v>0.3314</v>
       </c>
       <c r="N25" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1414</v>
+        <v>0.1621</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0341</v>
+        <v>0.0391</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3642</v>
+        <v>-0.3793</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1414</v>
+        <v>0.1621</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1414</v>
+        <v>0.1621</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1414</v>
+        <v>0.1621</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1414</v>
+        <v>0.1621</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1414</v>
+        <v>0.1621</v>
       </c>
       <c r="N26" t="n">
-        <v>143</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1089</v>
+        <v>0.1414</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0263</v>
+        <v>0.0341</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3774</v>
+        <v>-0.3876</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1089</v>
+        <v>0.1414</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1089</v>
+        <v>0.1414</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1089</v>
+        <v>0.1414</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1089</v>
+        <v>0.1414</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1089</v>
+        <v>0.1414</v>
       </c>
       <c r="N27" t="n">
         <v>143</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0291</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4702</v>
+        <v>-0.492</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1208</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0345</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4791</v>
+        <v>-0.5008</v>
       </c>
       <c r="E29" t="n">
         <v>-0.1429</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0432</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4938</v>
+        <v>-0.5153</v>
       </c>
       <c r="E30" t="n">
         <v>-0.1792</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1346</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6466</v>
+        <v>-0.6661</v>
       </c>
       <c r="E31" t="n">
         <v>-0.5576</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1718</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.709</v>
+        <v>-0.7276</v>
       </c>
       <c r="E32" t="n">
         <v>-0.712</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1751</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7145</v>
+        <v>-0.733</v>
       </c>
       <c r="E33" t="n">
         <v>-0.7257</v>
@@ -1974,7 +1974,7 @@
         <v>-0.209</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7713</v>
+        <v>-0.789</v>
       </c>
       <c r="E34" t="n">
         <v>-0.8663</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2298</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8062</v>
+        <v>-0.8234</v>
       </c>
       <c r="E35" t="n">
         <v>-0.9525</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2608</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.858</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0808</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3326</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9782</v>
+        <v>-0.9931</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3785</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3782</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0546</v>
+        <v>-1.0684</v>
       </c>
       <c r="E38" t="n">
         <v>-1.5674</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4189</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1227</v>
+        <v>-1.1356</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7361</v>
@@ -2250,7 +2250,7 @@
         <v>-0.505</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2668</v>
+        <v>-1.2776</v>
       </c>
       <c r="E40" t="n">
         <v>-2.0927</v>
@@ -2296,7 +2296,7 @@
         <v>-0.6804</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5605</v>
+        <v>-1.5673</v>
       </c>
       <c r="E41" t="n">
         <v>-2.8198</v>

--- a/database/event/7250/event_7250_evp_summary.xlsx
+++ b/database/event/7250/event_7250_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0183</v>
+        <v>6.322</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4522</v>
+        <v>1.5255</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9538</v>
+        <v>2.2161</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0183</v>
+        <v>6.322</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7032</v>
+        <v>2.2471</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3152</v>
+        <v>4.0749</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7032</v>
+        <v>2.431</v>
       </c>
       <c r="I2" t="n">
-        <v>2.191</v>
+        <v>1.264</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3152</v>
+        <v>4.0749</v>
       </c>
       <c r="K2" t="n">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="L2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="M2" t="n">
-        <v>5.5062</v>
+        <v>5.338900000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6078</v>
+        <v>6.0817</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3532</v>
+        <v>1.4675</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7902</v>
+        <v>2.1076</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6078</v>
+        <v>6.0817</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0072</v>
+        <v>2.9945</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6006</v>
+        <v>3.0872</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0072</v>
+        <v>5.0645</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8164</v>
+        <v>2.6333</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6006</v>
+        <v>3.0872</v>
       </c>
       <c r="K3" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="L3" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="M3" t="n">
-        <v>5.417</v>
+        <v>5.7205</v>
       </c>
       <c r="N3" t="n">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8725</v>
+        <v>4.4433</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1758</v>
+        <v>1.0722</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4973</v>
+        <v>1.3679</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8725</v>
+        <v>4.4433</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3047</v>
+        <v>2.9467</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5678</v>
+        <v>1.4966</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3047</v>
+        <v>4.896</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6786</v>
+        <v>2.5457</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5678</v>
+        <v>1.4966</v>
       </c>
       <c r="K4" t="n">
         <v>101</v>
@@ -621,7 +621,7 @@
         <v>120</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2464</v>
+        <v>4.0423</v>
       </c>
       <c r="N4" t="n">
         <v>221</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2119</v>
+        <v>4.3019</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0163</v>
+        <v>1.0381</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2341</v>
+        <v>1.3041</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2119</v>
+        <v>4.3019</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4362</v>
+        <v>4.3833</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2243</v>
+        <v>-0.0814</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2872</v>
+        <v>9.9575</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2854</v>
+        <v>5.1775</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2243</v>
+        <v>-0.0814</v>
       </c>
       <c r="K5" t="n">
         <v>130</v>
@@ -667,7 +667,7 @@
         <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0611</v>
+        <v>5.0961</v>
       </c>
       <c r="N5" t="n">
         <v>174</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.617</v>
+        <v>3.7454</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8728</v>
+        <v>0.9038</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9971</v>
+        <v>1.0528</v>
       </c>
       <c r="E6" t="n">
-        <v>3.617</v>
+        <v>3.7454</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3969</v>
+        <v>0.0037</v>
       </c>
       <c r="G6" t="n">
-        <v>4.0139</v>
+        <v>3.7417</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3969</v>
+        <v>0.0037</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3217</v>
+        <v>0.0019</v>
       </c>
       <c r="J6" t="n">
-        <v>4.0139</v>
+        <v>3.7417</v>
       </c>
       <c r="K6" t="n">
         <v>101</v>
@@ -713,7 +713,7 @@
         <v>120</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6922</v>
+        <v>3.7436</v>
       </c>
       <c r="N6" t="n">
         <v>221</v>
@@ -722,185 +722,185 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5563</v>
+        <v>3.4713</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8581</v>
+        <v>0.8376</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9729</v>
+        <v>0.9291</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5563</v>
+        <v>3.4713</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5563</v>
+        <v>1.3447</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2.1266</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5563</v>
+        <v>1.3447</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5563</v>
+        <v>0.6992</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.1266</v>
       </c>
       <c r="K7" t="n">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5563</v>
+        <v>2.8258</v>
       </c>
       <c r="N7" t="n">
-        <v>143</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8783</v>
+        <v>3.2806</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6945</v>
+        <v>0.7916</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7028</v>
+        <v>0.843</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8783</v>
+        <v>3.2806</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1474</v>
+        <v>3.2806</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2691</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1474</v>
+        <v>3.8439</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3616</v>
+        <v>3.8439</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2691</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="L8" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.0925</v>
+        <v>3.8439</v>
       </c>
       <c r="N8" t="n">
-        <v>201</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8777</v>
+        <v>3.0794</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6944</v>
+        <v>0.7431</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7026</v>
+        <v>0.7522</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8777</v>
+        <v>3.0794</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6792</v>
+        <v>2.9247</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1985</v>
+        <v>0.1547</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6792</v>
+        <v>4.8185</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5505</v>
+        <v>2.5054</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1985</v>
+        <v>0.1547</v>
       </c>
       <c r="K9" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="L9" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="M9" t="n">
-        <v>2.749</v>
+        <v>2.6601</v>
       </c>
       <c r="N9" t="n">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8223</v>
+        <v>3.0503</v>
       </c>
       <c r="C10" t="n">
-        <v>0.681</v>
+        <v>0.736</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6805</v>
+        <v>0.739</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8223</v>
+        <v>3.0503</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7508</v>
+        <v>2.5447</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.5056</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7508</v>
+        <v>3.4797</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2296</v>
+        <v>1.8093</v>
       </c>
       <c r="J10" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.5056</v>
       </c>
       <c r="K10" t="n">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="L10" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3011</v>
+        <v>2.3149</v>
       </c>
       <c r="N10" t="n">
-        <v>201</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3805</v>
+        <v>2.7589</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5744</v>
+        <v>0.6657</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.6075</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3805</v>
+        <v>2.7589</v>
       </c>
       <c r="F11" t="n">
-        <v>3.153</v>
+        <v>3.2587</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7725</v>
+        <v>-0.4998</v>
       </c>
       <c r="H11" t="n">
-        <v>3.153</v>
+        <v>5.9951</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5556</v>
+        <v>3.1172</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7725</v>
+        <v>-0.4998</v>
       </c>
       <c r="K11" t="n">
         <v>130</v>
@@ -943,7 +943,7 @@
         <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7831</v>
+        <v>2.6174</v>
       </c>
       <c r="N11" t="n">
         <v>174</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0099</v>
+        <v>2.7031</v>
       </c>
       <c r="C12" t="n">
-        <v>0.485</v>
+        <v>0.6523</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3568</v>
+        <v>0.5823</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0099</v>
+        <v>2.7031</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0099</v>
+        <v>2.4512</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.2519</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0099</v>
+        <v>3.1503</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0099</v>
+        <v>1.638</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.2519</v>
       </c>
       <c r="K12" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0099</v>
+        <v>1.8899</v>
       </c>
       <c r="N12" t="n">
-        <v>146</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9864</v>
+        <v>2.6865</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4793</v>
+        <v>0.6483</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3475</v>
+        <v>0.5748</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9864</v>
+        <v>2.6865</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7403</v>
+        <v>2.3658</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2461</v>
+        <v>0.3207</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7403</v>
+        <v>2.8493</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4106</v>
+        <v>1.4815</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2461</v>
+        <v>0.3207</v>
       </c>
       <c r="K13" t="n">
         <v>83</v>
@@ -1035,7 +1035,7 @@
         <v>34</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6567</v>
+        <v>1.8022</v>
       </c>
       <c r="N13" t="n">
         <v>117</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8636</v>
+        <v>2.6071</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4497</v>
+        <v>0.6291</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2985</v>
+        <v>0.539</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8636</v>
+        <v>2.6071</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3813</v>
+        <v>3.5411</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4823</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3813</v>
+        <v>6.9902</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1196</v>
+        <v>3.6346</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4823</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="K14" t="n">
+        <v>71</v>
+      </c>
+      <c r="L14" t="n">
         <v>130</v>
       </c>
-      <c r="L14" t="n">
-        <v>44</v>
-      </c>
       <c r="M14" t="n">
-        <v>1.6019</v>
+        <v>2.7006</v>
       </c>
       <c r="N14" t="n">
-        <v>174</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6794</v>
+        <v>2.4745</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4052</v>
+        <v>0.5971</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2252</v>
+        <v>0.4791</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6794</v>
+        <v>2.4745</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6058</v>
+        <v>1.2343</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0736</v>
+        <v>1.2402</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6058</v>
+        <v>1.2343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.491</v>
+        <v>0.6418</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0736</v>
+        <v>1.2402</v>
       </c>
       <c r="K15" t="n">
         <v>71</v>
@@ -1127,7 +1127,7 @@
         <v>130</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5646</v>
+        <v>1.882</v>
       </c>
       <c r="N15" t="n">
         <v>201</v>
@@ -1136,185 +1136,185 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5344</v>
+        <v>2.0196</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3703</v>
+        <v>0.4873</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1674</v>
+        <v>0.2737</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5344</v>
+        <v>2.0196</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3403</v>
+        <v>2.0196</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1941</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3403</v>
+        <v>2.0196</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0864</v>
+        <v>2.0196</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1941</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="L16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2805</v>
+        <v>2.0196</v>
       </c>
       <c r="N16" t="n">
-        <v>174</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.525</v>
+        <v>1.9179</v>
       </c>
       <c r="C17" t="n">
-        <v>0.368</v>
+        <v>0.4628</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1636</v>
+        <v>0.2278</v>
       </c>
       <c r="E17" t="n">
-        <v>1.525</v>
+        <v>1.9179</v>
       </c>
       <c r="F17" t="n">
-        <v>1.525</v>
+        <v>1.9179</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.525</v>
+        <v>1.9179</v>
       </c>
       <c r="I17" t="n">
-        <v>1.525</v>
+        <v>1.9179</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.525</v>
+        <v>1.9179</v>
       </c>
       <c r="N17" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4082</v>
+        <v>1.7372</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3398</v>
+        <v>0.4192</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1171</v>
+        <v>0.1462</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4082</v>
+        <v>1.7372</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4082</v>
+        <v>1.7372</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4082</v>
+        <v>1.7372</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4082</v>
+        <v>1.7372</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4082</v>
+        <v>1.7372</v>
       </c>
       <c r="N18" t="n">
-        <v>143</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>Airax</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.215</v>
+        <v>1.724</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2932</v>
+        <v>0.416</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0401</v>
+        <v>0.1403</v>
       </c>
       <c r="E19" t="n">
-        <v>1.215</v>
+        <v>1.724</v>
       </c>
       <c r="F19" t="n">
-        <v>1.215</v>
+        <v>2.3545</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.215</v>
+        <v>2.8095</v>
       </c>
       <c r="I19" t="n">
-        <v>1.215</v>
+        <v>1.4608</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M19" t="n">
-        <v>1.215</v>
+        <v>0.8303000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>146</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9407</v>
+        <v>1.4279</v>
       </c>
       <c r="C20" t="n">
-        <v>0.227</v>
+        <v>0.3446</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9407</v>
+        <v>1.4279</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9407</v>
+        <v>2.4279</v>
       </c>
       <c r="G20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9407</v>
+        <v>3.0682</v>
       </c>
       <c r="I20" t="n">
-        <v>1.573</v>
+        <v>1.5953</v>
       </c>
       <c r="J20" t="n">
         <v>-1</v>
@@ -1357,7 +1357,7 @@
         <v>34</v>
       </c>
       <c r="M20" t="n">
-        <v>0.573</v>
+        <v>0.5952999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>117</v>
@@ -1366,277 +1366,277 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Airax</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9323</v>
+        <v>1.3571</v>
       </c>
       <c r="C21" t="n">
-        <v>0.225</v>
+        <v>0.3275</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0725</v>
+        <v>-0.0254</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9323</v>
+        <v>1.3571</v>
       </c>
       <c r="F21" t="n">
-        <v>1.806</v>
+        <v>1.3571</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8737</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.806</v>
+        <v>1.3571</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4638</v>
+        <v>1.3571</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8737</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="L21" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5901</v>
+        <v>1.3571</v>
       </c>
       <c r="N21" t="n">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7155</v>
+        <v>1.064</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1727</v>
+        <v>0.2567</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1589</v>
+        <v>-0.1577</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7155</v>
+        <v>1.064</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7155</v>
+        <v>0.345</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7155</v>
+        <v>0.345</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7155</v>
+        <v>0.1794</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="K22" t="n">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7155</v>
+        <v>0.8984</v>
       </c>
       <c r="N22" t="n">
-        <v>143</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.9981</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1573</v>
+        <v>0.2408</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1843</v>
+        <v>-0.1874</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.9981</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.9981</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.9981</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.9981</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.9981</v>
       </c>
       <c r="N23" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4581</v>
+        <v>0.9059</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1105</v>
+        <v>0.2186</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2614</v>
+        <v>-0.229</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4581</v>
+        <v>0.9059</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3724</v>
+        <v>0.9059</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8305</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3724</v>
+        <v>0.9059</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3018</v>
+        <v>0.9059</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8305</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="L24" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.9059</v>
       </c>
       <c r="N24" t="n">
-        <v>221</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>Banjo</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3314</v>
+        <v>0.8116</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08</v>
+        <v>0.1958</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3119</v>
+        <v>-0.2716</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3314</v>
+        <v>0.8116</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3314</v>
+        <v>1.168</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.3564</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3314</v>
+        <v>1.168</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3314</v>
+        <v>0.6073</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.3564</v>
       </c>
       <c r="K25" t="n">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3314</v>
+        <v>0.2509</v>
       </c>
       <c r="N25" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1621</v>
+        <v>0.751</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0391</v>
+        <v>0.1812</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3793</v>
+        <v>-0.299</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1621</v>
+        <v>0.751</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1621</v>
+        <v>0.751</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1621</v>
+        <v>0.751</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1621</v>
+        <v>0.751</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1621</v>
+        <v>0.751</v>
       </c>
       <c r="N26" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1414</v>
+        <v>0.703</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0341</v>
+        <v>0.1696</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3876</v>
+        <v>-0.3206</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1414</v>
+        <v>0.703</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1414</v>
+        <v>0.703</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1414</v>
+        <v>0.703</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1414</v>
+        <v>0.703</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1414</v>
+        <v>0.703</v>
       </c>
       <c r="N27" t="n">
         <v>143</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Banjo</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1208</v>
+        <v>0.3162</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0291</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.492</v>
+        <v>-0.4953</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1208</v>
+        <v>0.3162</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4975</v>
+        <v>0.3162</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.6183</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4975</v>
+        <v>0.3162</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4032</v>
+        <v>0.3162</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6183</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L28" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2151</v>
+        <v>0.3162</v>
       </c>
       <c r="N28" t="n">
-        <v>117</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1429</v>
+        <v>0.1989</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0345</v>
+        <v>0.048</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5008</v>
+        <v>-0.5482</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1429</v>
+        <v>0.1989</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1429</v>
+        <v>0.1989</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1429</v>
+        <v>0.1989</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1429</v>
+        <v>0.1989</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1429</v>
+        <v>0.1989</v>
       </c>
       <c r="N29" t="n">
         <v>74</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1792</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0432</v>
+        <v>0.0178</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5153</v>
+        <v>-0.6047</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1792</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1792</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1792</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1792</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1792</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>74</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5576</v>
+        <v>-0.2648</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1346</v>
+        <v>-0.0639</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6661</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5576</v>
+        <v>-0.2648</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5576</v>
+        <v>-0.2648</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5576</v>
+        <v>-0.2648</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5576</v>
+        <v>-0.2648</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5576</v>
+        <v>-0.2648</v>
       </c>
       <c r="N31" t="n">
         <v>146</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.712</v>
+        <v>-0.4004</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1718</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7276</v>
+        <v>-0.8188</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.712</v>
+        <v>-0.4004</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.712</v>
+        <v>-0.4004</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.712</v>
+        <v>-0.4004</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.712</v>
+        <v>-0.4004</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.712</v>
+        <v>-0.4004</v>
       </c>
       <c r="N32" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7257</v>
+        <v>-0.4145</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1751</v>
+        <v>-0.1</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.733</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7257</v>
+        <v>-0.4145</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7257</v>
+        <v>-0.4145</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7257</v>
+        <v>-0.4145</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7257</v>
+        <v>-0.4145</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7257</v>
+        <v>-0.4145</v>
       </c>
       <c r="N33" t="n">
         <v>146</v>
@@ -1964,139 +1964,139 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8663</v>
+        <v>-0.4639</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.209</v>
+        <v>-0.1119</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.789</v>
+        <v>-0.8474</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8663</v>
+        <v>-0.4639</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8663</v>
+        <v>-0.4639</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8663</v>
+        <v>-0.4639</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8663</v>
+        <v>-0.4639</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8663</v>
+        <v>-0.4639</v>
       </c>
       <c r="N34" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9525</v>
+        <v>-0.602</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2298</v>
+        <v>-0.1453</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8234</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9525</v>
+        <v>-0.602</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9525</v>
+        <v>-0.602</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9525</v>
+        <v>-0.602</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9525</v>
+        <v>-0.602</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9525</v>
+        <v>-0.602</v>
       </c>
       <c r="N35" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0808</v>
+        <v>-0.6475</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2608</v>
+        <v>-0.1562</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.9303</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0808</v>
+        <v>-0.6475</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0808</v>
+        <v>-0.6475</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0808</v>
+        <v>-0.6475</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0808</v>
+        <v>-0.6475</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0808</v>
+        <v>-0.6475</v>
       </c>
       <c r="N36" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3785</v>
+        <v>-1.0361</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3326</v>
+        <v>-0.25</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9931</v>
+        <v>-1.1058</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3785</v>
+        <v>-1.0361</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8591</v>
+        <v>-0.7993</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5194</v>
+        <v>-0.2368</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8591</v>
+        <v>-0.7993</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6963</v>
+        <v>-0.4156</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5194</v>
+        <v>-0.2368</v>
       </c>
       <c r="K37" t="n">
         <v>83</v>
@@ -2139,7 +2139,7 @@
         <v>34</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2157</v>
+        <v>-0.6524000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>117</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5674</v>
+        <v>-1.1814</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3782</v>
+        <v>-0.2851</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0684</v>
+        <v>-1.1714</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5674</v>
+        <v>-1.1814</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5674</v>
+        <v>-1.1814</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5674</v>
+        <v>-1.1814</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5674</v>
+        <v>-1.1814</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5674</v>
+        <v>-1.1814</v>
       </c>
       <c r="N38" t="n">
         <v>74</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7361</v>
+        <v>-1.4726</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4189</v>
+        <v>-0.3553</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1356</v>
+        <v>-1.3028</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7361</v>
+        <v>-1.4726</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2541</v>
+        <v>-1.1738</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.482</v>
+        <v>-0.2988</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2541</v>
+        <v>-1.1738</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0165</v>
+        <v>-0.6103</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.482</v>
+        <v>-0.2988</v>
       </c>
       <c r="K39" t="n">
         <v>130</v>
@@ -2231,7 +2231,7 @@
         <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4985</v>
+        <v>-0.9091</v>
       </c>
       <c r="N39" t="n">
         <v>174</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0927</v>
+        <v>-1.4857</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.505</v>
+        <v>-0.3585</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2776</v>
+        <v>-1.3087</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0927</v>
+        <v>-1.4857</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0927</v>
+        <v>-1.4857</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0927</v>
+        <v>-1.4857</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.0927</v>
+        <v>-1.4857</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0927</v>
+        <v>-1.4857</v>
       </c>
       <c r="N40" t="n">
         <v>146</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.8198</v>
+        <v>-2.6155</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6804</v>
+        <v>-0.6311</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5673</v>
+        <v>-1.8188</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.8198</v>
+        <v>-2.6155</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3206</v>
+        <v>-1.6417</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.4992</v>
+        <v>-0.9738</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3206</v>
+        <v>-1.6417</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.0704</v>
+        <v>-0.8536</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.4992</v>
+        <v>-0.9738</v>
       </c>
       <c r="K41" t="n">
         <v>71</v>
@@ -2323,7 +2323,7 @@
         <v>130</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.5696</v>
+        <v>-1.8274</v>
       </c>
       <c r="N41" t="n">
         <v>201</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2996</v>
+        <v>0.3164</v>
       </c>
       <c r="J2" t="n">
-        <v>6.5912</v>
+        <v>6.9608</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.88</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1857</v>
+        <v>-0.1416</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.0854</v>
+        <v>-3.1152</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3058</v>
+        <v>-0.2016</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.7276</v>
+        <v>-4.4352</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.77</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.386</v>
+        <v>-0.2508</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.492000000000001</v>
+        <v>-5.5176</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4877</v>
+        <v>-0.3183</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.7294</v>
+        <v>-7.0026</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.57</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3414</v>
+        <v>1.2205</v>
       </c>
       <c r="J7" t="n">
-        <v>29.5108</v>
+        <v>26.851</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.52</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2435</v>
+        <v>1.1578</v>
       </c>
       <c r="J8" t="n">
-        <v>27.357</v>
+        <v>25.4716</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4904</v>
+        <v>0.5542</v>
       </c>
       <c r="J9" t="n">
-        <v>10.7888</v>
+        <v>12.1924</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0353</v>
+        <v>0.1099</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7766</v>
+        <v>2.4178</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.86</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5924</v>
+        <v>-0.5251</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.0328</v>
+        <v>-11.5522</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.78</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9954</v>
+        <v>0.9123</v>
       </c>
       <c r="J12" t="n">
-        <v>19.908</v>
+        <v>18.246</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4014</v>
+        <v>0.3605</v>
       </c>
       <c r="J13" t="n">
-        <v>8.028</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2222</v>
+        <v>0.2293</v>
       </c>
       <c r="J14" t="n">
-        <v>4.444</v>
+        <v>4.586</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0216</v>
+        <v>0.056</v>
       </c>
       <c r="J15" t="n">
-        <v>0.432</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.263</v>
+        <v>-0.147</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.26</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.06</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2513</v>
+        <v>0.1912</v>
       </c>
       <c r="J17" t="n">
-        <v>5.026</v>
+        <v>3.824</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1219</v>
+        <v>-0.1156</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.438</v>
+        <v>-2.312</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2572</v>
+        <v>-0.2017</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.144</v>
+        <v>-4.034</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.54</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6767</v>
+        <v>-0.4554</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.534</v>
+        <v>-9.108000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.52</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7022</v>
+        <v>-0.4739</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.044</v>
+        <v>-9.478</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.92</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2116</v>
+        <v>1.3668</v>
       </c>
       <c r="J22" t="n">
-        <v>26.6552</v>
+        <v>30.0696</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.85</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3063</v>
+        <v>-0.1868</v>
       </c>
       <c r="J23" t="n">
-        <v>-6.7386</v>
+        <v>-4.1096</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4098</v>
+        <v>-0.2577</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.015599999999999</v>
+        <v>-5.6694</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4516</v>
+        <v>-0.2871</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.9352</v>
+        <v>-6.3162</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.65</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5825</v>
+        <v>-0.3821</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.815</v>
+        <v>-8.4062</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7603</v>
+        <v>0.7439</v>
       </c>
       <c r="J27" t="n">
-        <v>16.7266</v>
+        <v>16.3658</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.25</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.6959</v>
       </c>
       <c r="J28" t="n">
-        <v>15.6684</v>
+        <v>15.3098</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4461</v>
+        <v>0.4484</v>
       </c>
       <c r="J29" t="n">
-        <v>9.8142</v>
+        <v>9.864800000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.08</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2138</v>
+        <v>0.2608</v>
       </c>
       <c r="J30" t="n">
-        <v>4.7036</v>
+        <v>5.7376</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4258</v>
+        <v>-0.3566</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.367599999999999</v>
+        <v>-7.8452</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5206</v>
+        <v>0.6135</v>
       </c>
       <c r="J32" t="n">
-        <v>11.4532</v>
+        <v>13.497</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.86</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2523</v>
+        <v>-0.1648</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.5506</v>
+        <v>-3.6256</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3359</v>
+        <v>-0.2154</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.3898</v>
+        <v>-4.7388</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3516</v>
+        <v>-0.2254</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.7352</v>
+        <v>-4.9588</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4963</v>
+        <v>-0.3226</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.9186</v>
+        <v>-7.0972</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.78</v>
       </c>
       <c r="I37" t="n">
-        <v>1.7533</v>
+        <v>1.4947</v>
       </c>
       <c r="J37" t="n">
-        <v>38.5726</v>
+        <v>32.8834</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.36</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9327</v>
       </c>
       <c r="J38" t="n">
-        <v>20.57</v>
+        <v>20.5194</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2714</v>
+        <v>0.3332</v>
       </c>
       <c r="J39" t="n">
-        <v>5.9708</v>
+        <v>7.3304</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3245</v>
+        <v>-0.2474</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.139</v>
+        <v>-5.4428</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.865</v>
+        <v>-0.8239</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.03</v>
+        <v>-18.1258</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4817</v>
+        <v>0.4672</v>
       </c>
       <c r="J42" t="n">
-        <v>9.634</v>
+        <v>9.343999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.07</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2344</v>
+        <v>0.232</v>
       </c>
       <c r="J43" t="n">
-        <v>4.688</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.85</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.24</v>
+        <v>-0.1714</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.8</v>
+        <v>-3.428</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.63</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.3834</v>
       </c>
       <c r="J45" t="n">
-        <v>-11.602</v>
+        <v>-7.668</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.46</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7907</v>
+        <v>-0.5399</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.814</v>
+        <v>-10.798</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4968</v>
+        <v>1.0499</v>
       </c>
       <c r="J47" t="n">
-        <v>29.936</v>
+        <v>20.998</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6294</v>
+        <v>0.5431</v>
       </c>
       <c r="J48" t="n">
-        <v>12.588</v>
+        <v>10.862</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.26</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6294</v>
+        <v>0.5431</v>
       </c>
       <c r="J49" t="n">
-        <v>12.588</v>
+        <v>10.862</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.11</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2337</v>
+        <v>0.3135</v>
       </c>
       <c r="J50" t="n">
-        <v>4.674</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.06</v>
       </c>
       <c r="I51" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.1672</v>
       </c>
       <c r="J51" t="n">
-        <v>1.768</v>
+        <v>3.344</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.15</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4861</v>
+        <v>0.4921</v>
       </c>
       <c r="J52" t="n">
-        <v>6.8054</v>
+        <v>6.8894</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.73</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2936</v>
+        <v>-0.2471</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.1104</v>
+        <v>-3.4594</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.49</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.6919</v>
+        <v>-0.474</v>
       </c>
       <c r="J54" t="n">
-        <v>-9.6866</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.37</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.8527</v>
+        <v>-0.5884</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.9378</v>
+        <v>-8.2376</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.25</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0011</v>
+        <v>-0.704</v>
       </c>
       <c r="J56" t="n">
-        <v>-14.0154</v>
+        <v>-9.856</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.87</v>
       </c>
       <c r="I57" t="n">
-        <v>1.7175</v>
+        <v>1.2249</v>
       </c>
       <c r="J57" t="n">
-        <v>24.045</v>
+        <v>17.1486</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.65</v>
       </c>
       <c r="I58" t="n">
-        <v>1.3206</v>
+        <v>0.9811</v>
       </c>
       <c r="J58" t="n">
-        <v>18.4884</v>
+        <v>13.7354</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.6</v>
       </c>
       <c r="I59" t="n">
-        <v>1.2011</v>
+        <v>0.9261</v>
       </c>
       <c r="J59" t="n">
-        <v>16.8154</v>
+        <v>12.9654</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.58</v>
       </c>
       <c r="I60" t="n">
-        <v>1.1567</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>16.1938</v>
+        <v>12.6518</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.36</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7058</v>
+        <v>0.6371</v>
       </c>
       <c r="J61" t="n">
-        <v>9.8812</v>
+        <v>8.9194</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.62</v>
       </c>
       <c r="I62" t="n">
-        <v>1.4552</v>
+        <v>1.0195</v>
       </c>
       <c r="J62" t="n">
-        <v>29.104</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.49</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2021</v>
+        <v>0.8549</v>
       </c>
       <c r="J63" t="n">
-        <v>24.042</v>
+        <v>17.098</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3499</v>
+        <v>0.3795</v>
       </c>
       <c r="J64" t="n">
-        <v>6.998</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.03</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0149</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>0.298</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.72</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9119</v>
+        <v>-0.8759</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.238</v>
+        <v>-17.518</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2475</v>
+        <v>0.2545</v>
       </c>
       <c r="J67" t="n">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.92</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1368</v>
+        <v>-0.103</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.736</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.87</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2425</v>
+        <v>-0.1561</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.85</v>
+        <v>-3.122</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2601</v>
+        <v>-0.1665</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.202</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.78</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3872</v>
+        <v>-0.2472</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.744</v>
+        <v>-4.944</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.45</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1872</v>
+        <v>0.8381</v>
       </c>
       <c r="J72" t="n">
-        <v>28.4928</v>
+        <v>20.1144</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.37</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0191</v>
+        <v>0.7291</v>
       </c>
       <c r="J73" t="n">
-        <v>24.4584</v>
+        <v>17.4984</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.91</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4021</v>
+        <v>-0.3402</v>
       </c>
       <c r="J74" t="n">
-        <v>-9.650399999999999</v>
+        <v>-8.1648</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5145</v>
+        <v>-0.4545</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.348</v>
+        <v>-10.908</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7893</v>
+        <v>-0.7446</v>
       </c>
       <c r="J76" t="n">
-        <v>-18.9432</v>
+        <v>-17.8704</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.16</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3309</v>
+        <v>0.3549</v>
       </c>
       <c r="J77" t="n">
-        <v>7.9416</v>
+        <v>8.5176</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2348</v>
+        <v>0.2511</v>
       </c>
       <c r="J78" t="n">
-        <v>5.6352</v>
+        <v>6.0264</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1629</v>
+        <v>0.1658</v>
       </c>
       <c r="J79" t="n">
-        <v>3.9096</v>
+        <v>3.9792</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2219</v>
+        <v>-0.1323</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.3256</v>
+        <v>-3.1752</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.53</v>
+        <v>-0.3437</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.72</v>
+        <v>-8.248799999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.45</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1286</v>
+        <v>1.0808</v>
       </c>
       <c r="J82" t="n">
-        <v>27.0864</v>
+        <v>25.9392</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.27</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7297</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>17.5128</v>
+        <v>17.4792</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.19</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5167</v>
+        <v>0.5385</v>
       </c>
       <c r="J84" t="n">
-        <v>12.4008</v>
+        <v>12.924</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0568</v>
+        <v>0.1232</v>
       </c>
       <c r="J85" t="n">
-        <v>1.3632</v>
+        <v>2.9568</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2553</v>
+        <v>-0.178</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.1272</v>
+        <v>-4.272</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2863</v>
+        <v>0.3021</v>
       </c>
       <c r="J87" t="n">
-        <v>6.8712</v>
+        <v>7.2504</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0262</v>
+        <v>-0.0391</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.6288</v>
+        <v>-0.9384</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2156</v>
+        <v>-0.1443</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.1744</v>
+        <v>-3.4632</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2534</v>
+        <v>-0.165</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.0816</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5894</v>
+        <v>-0.3889</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.1456</v>
+        <v>-9.333600000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.63</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4624</v>
+        <v>1.299</v>
       </c>
       <c r="J92" t="n">
-        <v>29.248</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.47</v>
       </c>
       <c r="I93" t="n">
-        <v>1.1497</v>
+        <v>1.0975</v>
       </c>
       <c r="J93" t="n">
-        <v>22.994</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.15</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3639</v>
+        <v>0.432</v>
       </c>
       <c r="J94" t="n">
-        <v>7.278</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1056</v>
+        <v>0.1783</v>
       </c>
       <c r="J95" t="n">
-        <v>2.112</v>
+        <v>3.566</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7119</v>
+        <v>-0.6549</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.238</v>
+        <v>-13.098</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2698</v>
+        <v>0.281</v>
       </c>
       <c r="J97" t="n">
-        <v>5.396</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2356</v>
+        <v>0.2378</v>
       </c>
       <c r="J98" t="n">
-        <v>4.712</v>
+        <v>4.756</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.88</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2156</v>
+        <v>-0.1443</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.312</v>
+        <v>-2.886</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3523</v>
+        <v>-0.2256</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.046</v>
+        <v>-4.512</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6401</v>
+        <v>-0.426</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.802</v>
+        <v>-8.52</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.33</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5847</v>
+        <v>0.7022</v>
       </c>
       <c r="J102" t="n">
-        <v>12.2787</v>
+        <v>14.7462</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.14</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3206</v>
+        <v>0.3496</v>
       </c>
       <c r="J103" t="n">
-        <v>6.7326</v>
+        <v>7.3416</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.78</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3936</v>
+        <v>-0.25</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.265599999999999</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.74</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4507</v>
+        <v>-0.2891</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.464700000000001</v>
+        <v>-6.0711</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5838</v>
+        <v>-0.384</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.2598</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.64</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4986</v>
+        <v>1.3218</v>
       </c>
       <c r="J107" t="n">
-        <v>31.4706</v>
+        <v>27.7578</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.36</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9327</v>
       </c>
       <c r="J108" t="n">
-        <v>19.635</v>
+        <v>19.5867</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1829</v>
+        <v>0.2477</v>
       </c>
       <c r="J109" t="n">
-        <v>3.8409</v>
+        <v>5.2017</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2568</v>
+        <v>-0.179</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.3928</v>
+        <v>-3.759</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5</v>
+        <v>-0.4292</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.5</v>
+        <v>-9.013199999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.91</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0773</v>
+        <v>0.9887</v>
       </c>
       <c r="J112" t="n">
-        <v>18.3141</v>
+        <v>16.8079</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.73</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8961</v>
+        <v>0.8218</v>
       </c>
       <c r="J113" t="n">
-        <v>15.2337</v>
+        <v>13.9706</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.27</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3293</v>
+        <v>0.3436</v>
       </c>
       <c r="J114" t="n">
-        <v>5.5981</v>
+        <v>5.8412</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.16</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1797</v>
+        <v>0.2085</v>
       </c>
       <c r="J115" t="n">
-        <v>3.0549</v>
+        <v>3.5445</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.03</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0299</v>
+        <v>0.017</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.5083</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>0.0161</v>
+        <v>-0.0242</v>
       </c>
       <c r="J117" t="n">
-        <v>0.2737</v>
+        <v>-0.4114</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.79</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2565</v>
+        <v>-0.2109</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.3605</v>
+        <v>-3.5853</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.73</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.355</v>
+        <v>-0.2704</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.035</v>
+        <v>-4.5968</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.58</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6052</v>
+        <v>-0.4082</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.2884</v>
+        <v>-6.9394</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.46</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7637</v>
+        <v>-0.5205</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.9829</v>
+        <v>-8.8485</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.39</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.8181</v>
       </c>
       <c r="J122" t="n">
-        <v>13.336</v>
+        <v>16.362</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.36</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6298</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J123" t="n">
-        <v>12.596</v>
+        <v>15.312</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.8</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3577</v>
+        <v>-0.2276</v>
       </c>
       <c r="J124" t="n">
-        <v>-7.154</v>
+        <v>-4.552</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.53</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.7163</v>
+        <v>-0.4829</v>
       </c>
       <c r="J125" t="n">
-        <v>-14.326</v>
+        <v>-9.657999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.45</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8102</v>
+        <v>-0.5551</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.204</v>
+        <v>-11.102</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.97</v>
       </c>
       <c r="I127" t="n">
-        <v>1.9858</v>
+        <v>1.688</v>
       </c>
       <c r="J127" t="n">
-        <v>39.716</v>
+        <v>33.76</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.31</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7966</v>
       </c>
       <c r="J128" t="n">
-        <v>15.212</v>
+        <v>15.932</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6161</v>
+        <v>0.6864</v>
       </c>
       <c r="J129" t="n">
-        <v>12.322</v>
+        <v>13.728</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1518</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.036</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.89</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5263</v>
+        <v>-0.4526</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.526</v>
+        <v>-9.052</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0759</v>
       </c>
       <c r="J132" t="n">
-        <v>-1.624</v>
+        <v>-1.518</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.91</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1391</v>
+        <v>-0.111</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.782</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.89</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1778</v>
+        <v>-0.1329</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.556</v>
+        <v>-2.658</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.85</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2627</v>
+        <v>-0.1735</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.254</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3773</v>
+        <v>-0.2434</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.546</v>
+        <v>-4.868</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.69</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8963</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="J137" t="n">
-        <v>17.926</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.54</v>
       </c>
       <c r="I138" t="n">
-        <v>0.733</v>
+        <v>0.656</v>
       </c>
       <c r="J138" t="n">
-        <v>14.66</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.28</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4069</v>
+        <v>0.3698</v>
       </c>
       <c r="J139" t="n">
-        <v>8.138</v>
+        <v>7.396</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.97</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.16</v>
+        <v>-0.0752</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.2</v>
+        <v>-1.504</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.44</v>
+        <v>-0.2744</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.800000000000001</v>
+        <v>-5.488</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.84</v>
       </c>
       <c r="I142" t="n">
-        <v>1.8989</v>
+        <v>1.6059</v>
       </c>
       <c r="J142" t="n">
-        <v>45.5736</v>
+        <v>38.5416</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.11</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3539</v>
+        <v>0.3505</v>
       </c>
       <c r="J143" t="n">
-        <v>8.493600000000001</v>
+        <v>8.412000000000001</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.02</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0259</v>
+        <v>0.0736</v>
       </c>
       <c r="J144" t="n">
-        <v>0.6216</v>
+        <v>1.7664</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.78</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.7494</v>
+        <v>-0.7002</v>
       </c>
       <c r="J145" t="n">
-        <v>-17.9856</v>
+        <v>-16.8048</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8651</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="J146" t="n">
-        <v>-20.7624</v>
+        <v>-19.8264</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.43</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6688</v>
+        <v>0.8205</v>
       </c>
       <c r="J147" t="n">
-        <v>16.0512</v>
+        <v>19.692</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.11</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2292</v>
+        <v>0.2573</v>
       </c>
       <c r="J148" t="n">
-        <v>5.5008</v>
+        <v>6.1752</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0625</v>
+        <v>0.0867</v>
       </c>
       <c r="J149" t="n">
-        <v>1.5</v>
+        <v>2.0808</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.86</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3037</v>
+        <v>-0.182</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.2888</v>
+        <v>-4.368</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.77</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4342</v>
+        <v>-0.2733</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.4208</v>
+        <v>-6.5592</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>0.966</v>
+        <v>0.9524</v>
       </c>
       <c r="J152" t="n">
-        <v>22.218</v>
+        <v>21.9052</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.09</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2467</v>
+        <v>0.29</v>
       </c>
       <c r="J153" t="n">
-        <v>5.6741</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.07</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1831</v>
+        <v>0.2316</v>
       </c>
       <c r="J154" t="n">
-        <v>4.2113</v>
+        <v>5.3268</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.07</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1831</v>
+        <v>0.2316</v>
       </c>
       <c r="J155" t="n">
-        <v>4.2113</v>
+        <v>5.3268</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.06</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1505</v>
+        <v>0.2011</v>
       </c>
       <c r="J156" t="n">
-        <v>3.4615</v>
+        <v>4.6253</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.5</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7855</v>
+        <v>0.9794</v>
       </c>
       <c r="J157" t="n">
-        <v>18.0665</v>
+        <v>22.5262</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3004</v>
+        <v>0.3253</v>
       </c>
       <c r="J158" t="n">
-        <v>6.9092</v>
+        <v>7.4819</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.95</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0944</v>
+        <v>-0.0709</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.1712</v>
+        <v>-1.6307</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.59</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6485</v>
+        <v>-0.4317</v>
       </c>
       <c r="J160" t="n">
-        <v>-14.9155</v>
+        <v>-9.9291</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.52</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7328</v>
+        <v>-0.4954</v>
       </c>
       <c r="J161" t="n">
-        <v>-16.8544</v>
+        <v>-11.3942</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.73</v>
       </c>
       <c r="I162" t="n">
-        <v>1.6203</v>
+        <v>1.4058</v>
       </c>
       <c r="J162" t="n">
-        <v>32.406</v>
+        <v>28.116</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.54</v>
       </c>
       <c r="I163" t="n">
-        <v>1.263</v>
+        <v>1.1737</v>
       </c>
       <c r="J163" t="n">
-        <v>25.26</v>
+        <v>23.474</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.42</v>
       </c>
       <c r="I164" t="n">
-        <v>1.017</v>
+        <v>1.0188</v>
       </c>
       <c r="J164" t="n">
-        <v>20.34</v>
+        <v>20.376</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3201</v>
+        <v>-0.2365</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.402</v>
+        <v>-4.73</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.8616</v>
+        <v>-0.8192</v>
       </c>
       <c r="J166" t="n">
-        <v>-17.232</v>
+        <v>-16.384</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.14</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3456</v>
+        <v>0.3769</v>
       </c>
       <c r="J167" t="n">
-        <v>6.912</v>
+        <v>7.538</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0097</v>
+        <v>-0.0196</v>
       </c>
       <c r="J168" t="n">
-        <v>0.194</v>
+        <v>-0.392</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2538</v>
+        <v>-0.1722</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.076</v>
+        <v>-3.444</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4607</v>
+        <v>-0.2998</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.214</v>
+        <v>-5.996</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.61</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6088</v>
+        <v>-0.4036</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.176</v>
+        <v>-8.071999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.98</v>
       </c>
       <c r="I172" t="n">
-        <v>1.9358</v>
+        <v>1.6379</v>
       </c>
       <c r="J172" t="n">
-        <v>30.9728</v>
+        <v>26.2064</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.81</v>
       </c>
       <c r="I173" t="n">
-        <v>1.6636</v>
+        <v>1.4478</v>
       </c>
       <c r="J173" t="n">
-        <v>26.6176</v>
+        <v>23.1648</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.54</v>
       </c>
       <c r="I174" t="n">
-        <v>1.1448</v>
+        <v>1.1388</v>
       </c>
       <c r="J174" t="n">
-        <v>18.3168</v>
+        <v>18.2208</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.24</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4743</v>
+        <v>0.5936</v>
       </c>
       <c r="J175" t="n">
-        <v>7.5888</v>
+        <v>9.4976</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2057</v>
+        <v>-0.1176</v>
       </c>
       <c r="J176" t="n">
-        <v>-3.2912</v>
+        <v>-1.8816</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2828</v>
+        <v>0.2985</v>
       </c>
       <c r="J177" t="n">
-        <v>4.5248</v>
+        <v>4.776</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.75</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2963</v>
+        <v>-0.2423</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.7408</v>
+        <v>-3.8768</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.68</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4105</v>
+        <v>-0.3105</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.568</v>
+        <v>-4.968</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.49</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.7131</v>
+        <v>-0.4851</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.4096</v>
+        <v>-7.7616</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.32</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.9268</v>
+        <v>-0.6453</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.8288</v>
+        <v>-10.3248</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.03</v>
       </c>
       <c r="I182" t="n">
-        <v>0.1469</v>
+        <v>0.1258</v>
       </c>
       <c r="J182" t="n">
-        <v>3.0849</v>
+        <v>2.6418</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0994</v>
+        <v>0.0689</v>
       </c>
       <c r="J183" t="n">
-        <v>2.0874</v>
+        <v>1.4469</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.87</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2215</v>
+        <v>-0.1532</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.6515</v>
+        <v>-3.2172</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3296</v>
+        <v>-0.2135</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.9216</v>
+        <v>-4.4835</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.64</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5725</v>
+        <v>-0.3772</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.0225</v>
+        <v>-7.9212</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.01</v>
       </c>
       <c r="I187" t="n">
-        <v>2.0303</v>
+        <v>1.7453</v>
       </c>
       <c r="J187" t="n">
-        <v>42.6363</v>
+        <v>36.6513</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.47</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1338</v>
+        <v>1.0908</v>
       </c>
       <c r="J188" t="n">
-        <v>23.8098</v>
+        <v>22.9068</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.02</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0429</v>
+        <v>0.0336</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.9009</v>
+        <v>0.7056</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2006</v>
+        <v>-0.1174</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.2126</v>
+        <v>-2.4654</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.79</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.7661</v>
+        <v>-0.7136</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.0881</v>
+        <v>-14.9856</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2501</v>
+        <v>0.2703</v>
       </c>
       <c r="J192" t="n">
-        <v>8.753500000000001</v>
+        <v>9.4605</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2333</v>
+        <v>0.25</v>
       </c>
       <c r="J193" t="n">
-        <v>8.1655</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.03</v>
       </c>
       <c r="I194" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0944</v>
       </c>
       <c r="J194" t="n">
-        <v>3.4685</v>
+        <v>3.304</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.97</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0849</v>
+        <v>-0.0488</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.9715</v>
+        <v>-1.708</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4913</v>
+        <v>-0.3156</v>
       </c>
       <c r="J196" t="n">
-        <v>-17.1955</v>
+        <v>-11.046</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.39</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0382</v>
+        <v>1.0131</v>
       </c>
       <c r="J197" t="n">
-        <v>36.337</v>
+        <v>35.4585</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.38</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0168</v>
+        <v>0.9959</v>
       </c>
       <c r="J198" t="n">
-        <v>35.588</v>
+        <v>34.8565</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.11</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3241</v>
+        <v>0.3478</v>
       </c>
       <c r="J199" t="n">
-        <v>11.3435</v>
+        <v>12.173</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4764</v>
+        <v>-0.4104</v>
       </c>
       <c r="J200" t="n">
-        <v>-16.674</v>
+        <v>-14.364</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6831</v>
+        <v>-0.628</v>
       </c>
       <c r="J201" t="n">
-        <v>-23.9085</v>
+        <v>-21.98</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.64</v>
       </c>
       <c r="I202" t="n">
-        <v>0.944</v>
+        <v>0.9335</v>
       </c>
       <c r="J202" t="n">
-        <v>18.88</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.29</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5308</v>
+        <v>0.4807</v>
       </c>
       <c r="J203" t="n">
-        <v>10.616</v>
+        <v>9.614000000000001</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.52</v>
+        <v>-0.3377</v>
       </c>
       <c r="J204" t="n">
-        <v>-10.4</v>
+        <v>-6.754</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.62</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.6102</v>
+        <v>-0.4033</v>
       </c>
       <c r="J205" t="n">
-        <v>-12.204</v>
+        <v>-8.066000000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.42</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.5843</v>
       </c>
       <c r="J206" t="n">
-        <v>-16.946</v>
+        <v>-11.686</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.29</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4581</v>
+        <v>0.3949</v>
       </c>
       <c r="J207" t="n">
-        <v>9.162000000000001</v>
+        <v>7.898</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.25</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4031</v>
+        <v>0.3472</v>
       </c>
       <c r="J208" t="n">
-        <v>8.061999999999999</v>
+        <v>6.944</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.11</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1693</v>
+        <v>0.1717</v>
       </c>
       <c r="J209" t="n">
-        <v>3.386</v>
+        <v>3.434</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.06</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0801</v>
+        <v>0.0987</v>
       </c>
       <c r="J210" t="n">
-        <v>1.602</v>
+        <v>1.974</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.04</v>
       </c>
       <c r="I211" t="n">
-        <v>0.0416</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J211" t="n">
-        <v>0.832</v>
+        <v>1.324</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.08</v>
       </c>
       <c r="I212" t="n">
-        <v>2.0249</v>
+        <v>1.7394</v>
       </c>
       <c r="J212" t="n">
-        <v>30.3735</v>
+        <v>26.091</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.87</v>
       </c>
       <c r="I213" t="n">
-        <v>1.7535</v>
+        <v>1.5084</v>
       </c>
       <c r="J213" t="n">
-        <v>26.3025</v>
+        <v>22.626</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.55</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1328</v>
+        <v>1.1477</v>
       </c>
       <c r="J214" t="n">
-        <v>16.992</v>
+        <v>17.2155</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.51</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0398</v>
+        <v>1.1019</v>
       </c>
       <c r="J215" t="n">
-        <v>15.597</v>
+        <v>16.5285</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.75</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.9026</v>
+        <v>-0.8668</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.539</v>
+        <v>-13.002</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.65</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.4243</v>
+        <v>-0.3295</v>
       </c>
       <c r="J217" t="n">
-        <v>-6.3645</v>
+        <v>-4.9425</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.64</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.4409</v>
+        <v>-0.3389</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.6135</v>
+        <v>-5.0835</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.62</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4761</v>
+        <v>-0.3572</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.1415</v>
+        <v>-5.358</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.59</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5413</v>
+        <v>-0.3831</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.1195</v>
+        <v>-5.7465</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.53</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6374</v>
+        <v>-0.438</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.561</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.66</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4309</v>
+        <v>1.292</v>
       </c>
       <c r="J222" t="n">
-        <v>25.7562</v>
+        <v>23.256</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.63</v>
       </c>
       <c r="I223" t="n">
-        <v>1.3741</v>
+        <v>1.2567</v>
       </c>
       <c r="J223" t="n">
-        <v>24.7338</v>
+        <v>22.6206</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.48</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0719</v>
+        <v>1.0778</v>
       </c>
       <c r="J224" t="n">
-        <v>19.2942</v>
+        <v>19.4004</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.43</v>
       </c>
       <c r="I225" t="n">
-        <v>0.9571</v>
+        <v>1.0126</v>
       </c>
       <c r="J225" t="n">
-        <v>17.2278</v>
+        <v>18.2268</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.89</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5544</v>
+        <v>-0.4803</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.979200000000001</v>
+        <v>-8.6454</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.12</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3443</v>
+        <v>0.3734</v>
       </c>
       <c r="J227" t="n">
-        <v>6.1974</v>
+        <v>6.7212</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.86</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1839</v>
+        <v>-0.1532</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.3102</v>
+        <v>-2.7576</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.84</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2181</v>
+        <v>-0.1743</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.9258</v>
+        <v>-3.1374</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.58</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.6303</v>
+        <v>-0.4213</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.3454</v>
+        <v>-7.5834</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.53</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6944</v>
+        <v>-0.4678</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.4992</v>
+        <v>-8.420400000000001</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.48</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2</v>
+        <v>1.1248</v>
       </c>
       <c r="J232" t="n">
-        <v>27.6</v>
+        <v>25.8704</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.26</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7175</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="J233" t="n">
-        <v>16.5025</v>
+        <v>16.3346</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.07</v>
       </c>
       <c r="I234" t="n">
-        <v>0.164</v>
+        <v>0.2236</v>
       </c>
       <c r="J234" t="n">
-        <v>3.772</v>
+        <v>5.1428</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.05</v>
       </c>
       <c r="I235" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1612</v>
       </c>
       <c r="J235" t="n">
-        <v>2.2908</v>
+        <v>3.7076</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.96</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2829</v>
+        <v>-0.2078</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.5067</v>
+        <v>-4.7794</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.24</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4609</v>
+        <v>0.5342</v>
       </c>
       <c r="J237" t="n">
-        <v>10.6007</v>
+        <v>12.2866</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.04</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1404</v>
+        <v>0.1299</v>
       </c>
       <c r="J238" t="n">
-        <v>3.2292</v>
+        <v>2.9877</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2053</v>
+        <v>-0.1278</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.7219</v>
+        <v>-2.9394</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3532</v>
+        <v>-0.2218</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.1236</v>
+        <v>-5.1014</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.495</v>
+        <v>-0.3197</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.385</v>
+        <v>-7.3531</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.09</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2799</v>
+        <v>0.221</v>
       </c>
       <c r="J242" t="n">
-        <v>5.0382</v>
+        <v>3.978</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.9</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1315</v>
+        <v>-0.115</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.367</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3035</v>
+        <v>-0.2079</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.463</v>
+        <v>-3.7422</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.77</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.372</v>
+        <v>-0.2465</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.696</v>
+        <v>-4.437</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.54</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6894</v>
+        <v>-0.4635</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.4092</v>
+        <v>-8.343</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.94</v>
       </c>
       <c r="I247" t="n">
-        <v>1.1151</v>
+        <v>1.0167</v>
       </c>
       <c r="J247" t="n">
-        <v>20.0718</v>
+        <v>18.3006</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>0.8309</v>
+        <v>0.7575</v>
       </c>
       <c r="J248" t="n">
-        <v>14.9562</v>
+        <v>13.635</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.58</v>
       </c>
       <c r="I249" t="n">
-        <v>0.7431</v>
+        <v>0.6761</v>
       </c>
       <c r="J249" t="n">
-        <v>13.3758</v>
+        <v>12.1698</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.17</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2005</v>
+        <v>0.2253</v>
       </c>
       <c r="J250" t="n">
-        <v>3.609</v>
+        <v>4.0554</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.57</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7173</v>
+        <v>-0.4854</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.9114</v>
+        <v>-8.7372</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.14</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4822</v>
+        <v>0.4453</v>
       </c>
       <c r="J252" t="n">
-        <v>11.0906</v>
+        <v>10.2419</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3657</v>
+        <v>0.335</v>
       </c>
       <c r="J253" t="n">
-        <v>8.411099999999999</v>
+        <v>7.705</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.02</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0619</v>
+        <v>0.0859</v>
       </c>
       <c r="J254" t="n">
-        <v>1.4237</v>
+        <v>1.9757</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.99</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1072</v>
+        <v>-0.0633</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.4656</v>
+        <v>-1.4559</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.97</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1913</v>
+        <v>-0.141</v>
       </c>
       <c r="J256" t="n">
-        <v>-4.3999</v>
+        <v>-3.243</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.2</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3913</v>
+        <v>0.446</v>
       </c>
       <c r="J257" t="n">
-        <v>8.9999</v>
+        <v>10.258</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3913</v>
+        <v>0.446</v>
       </c>
       <c r="J258" t="n">
-        <v>8.9999</v>
+        <v>10.258</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.95</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1255</v>
+        <v>-0.0738</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.8865</v>
+        <v>-1.6974</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.85</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3029</v>
+        <v>-0.1854</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.9667</v>
+        <v>-4.2642</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5292</v>
+        <v>-0.3432</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.1716</v>
+        <v>-7.8936</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.63</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4511</v>
+        <v>1.2926</v>
       </c>
       <c r="J262" t="n">
-        <v>30.4731</v>
+        <v>27.1446</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.3</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7625</v>
+        <v>0.7817</v>
       </c>
       <c r="J263" t="n">
-        <v>16.0125</v>
+        <v>16.4157</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.23</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5647</v>
+        <v>0.6236</v>
       </c>
       <c r="J264" t="n">
-        <v>11.8587</v>
+        <v>13.0956</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.04</v>
       </c>
       <c r="I265" t="n">
-        <v>0.0317</v>
+        <v>0.1075</v>
       </c>
       <c r="J265" t="n">
-        <v>0.6657</v>
+        <v>2.2575</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.04</v>
       </c>
       <c r="I266" t="n">
-        <v>0.0317</v>
+        <v>0.1075</v>
       </c>
       <c r="J266" t="n">
-        <v>0.6657</v>
+        <v>2.2575</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.3</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5749</v>
+        <v>0.6901</v>
       </c>
       <c r="J267" t="n">
-        <v>12.0729</v>
+        <v>14.4921</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.97</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0326</v>
       </c>
       <c r="J268" t="n">
-        <v>-0.1827</v>
+        <v>-0.6846</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.68</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.3365</v>
       </c>
       <c r="J269" t="n">
-        <v>-10.7856</v>
+        <v>-7.0665</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.66</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5407</v>
+        <v>-0.3555</v>
       </c>
       <c r="J270" t="n">
-        <v>-11.3547</v>
+        <v>-7.4655</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5674</v>
+        <v>-0.3743</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.9154</v>
+        <v>-7.8603</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.15</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4007</v>
+        <v>0.4509</v>
       </c>
       <c r="J272" t="n">
-        <v>7.6133</v>
+        <v>8.5671</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.98</v>
       </c>
       <c r="I273" t="n">
-        <v>0.051</v>
+        <v>0.0026</v>
       </c>
       <c r="J273" t="n">
-        <v>0.969</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.68</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.4853</v>
+        <v>-0.3242</v>
       </c>
       <c r="J274" t="n">
-        <v>-9.220700000000001</v>
+        <v>-6.1598</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.54</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.6767</v>
+        <v>-0.4554</v>
       </c>
       <c r="J275" t="n">
-        <v>-12.8573</v>
+        <v>-8.6526</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.47</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7645</v>
+        <v>-0.5202</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.5255</v>
+        <v>-9.883800000000001</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.77</v>
       </c>
       <c r="I277" t="n">
-        <v>1.6938</v>
+        <v>1.4549</v>
       </c>
       <c r="J277" t="n">
-        <v>32.1822</v>
+        <v>27.6431</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.38</v>
       </c>
       <c r="I278" t="n">
-        <v>0.9318</v>
+        <v>0.9496</v>
       </c>
       <c r="J278" t="n">
-        <v>17.7042</v>
+        <v>18.0424</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.26</v>
       </c>
       <c r="I279" t="n">
-        <v>0.6239</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J279" t="n">
-        <v>11.8541</v>
+        <v>13.072</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.09</v>
       </c>
       <c r="I280" t="n">
-        <v>0.1752</v>
+        <v>0.256</v>
       </c>
       <c r="J280" t="n">
-        <v>3.3288</v>
+        <v>4.864</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.88</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5502</v>
+        <v>-0.4786</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.4538</v>
+        <v>-9.093400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7250/event_7250_evp_summary.xlsx
+++ b/database/event/7250/event_7250_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.322</v>
+        <v>6.5447</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5255</v>
+        <v>1.5793</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2161</v>
+        <v>2.3551</v>
       </c>
       <c r="E2" t="n">
-        <v>6.322</v>
+        <v>6.5447</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2471</v>
+        <v>2.1479</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0749</v>
+        <v>4.3968</v>
       </c>
       <c r="H2" t="n">
-        <v>2.431</v>
+        <v>2.1926</v>
       </c>
       <c r="I2" t="n">
-        <v>1.264</v>
+        <v>1.184</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0749</v>
+        <v>4.3968</v>
       </c>
       <c r="K2" t="n">
         <v>101</v>
@@ -529,7 +529,7 @@
         <v>120</v>
       </c>
       <c r="M2" t="n">
-        <v>5.338900000000001</v>
+        <v>5.5808</v>
       </c>
       <c r="N2" t="n">
         <v>221</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0817</v>
+        <v>6.3267</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4675</v>
+        <v>1.5267</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1076</v>
+        <v>2.2558</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0817</v>
+        <v>6.3267</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9945</v>
+        <v>2.9654</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0872</v>
+        <v>3.3613</v>
       </c>
       <c r="H3" t="n">
-        <v>5.0645</v>
+        <v>4.8897</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6333</v>
+        <v>2.6404</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0872</v>
+        <v>3.3613</v>
       </c>
       <c r="K3" t="n">
         <v>71</v>
@@ -575,7 +575,7 @@
         <v>130</v>
       </c>
       <c r="M3" t="n">
-        <v>5.7205</v>
+        <v>6.0017</v>
       </c>
       <c r="N3" t="n">
         <v>201</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4433</v>
+        <v>4.6482</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0722</v>
+        <v>1.1216</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3679</v>
+        <v>1.4918</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4433</v>
+        <v>4.6482</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9467</v>
+        <v>2.9313</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4966</v>
+        <v>1.7169</v>
       </c>
       <c r="H4" t="n">
-        <v>4.896</v>
+        <v>4.7771</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5457</v>
+        <v>2.5796</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4966</v>
+        <v>1.7169</v>
       </c>
       <c r="K4" t="n">
         <v>101</v>
@@ -621,7 +621,7 @@
         <v>120</v>
       </c>
       <c r="M4" t="n">
-        <v>4.0423</v>
+        <v>4.2965</v>
       </c>
       <c r="N4" t="n">
         <v>221</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3019</v>
+        <v>4.1765</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0381</v>
+        <v>1.0078</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3041</v>
+        <v>1.277</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3019</v>
+        <v>4.1765</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3833</v>
+        <v>4.2664</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0814</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>9.9575</v>
+        <v>9.182399999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1775</v>
+        <v>4.9584</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0814</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>130</v>
@@ -667,7 +667,7 @@
         <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0961</v>
+        <v>4.8685</v>
       </c>
       <c r="N5" t="n">
         <v>174</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7454</v>
+        <v>3.7888</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9038</v>
+        <v>0.9143</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0528</v>
+        <v>1.1005</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7454</v>
+        <v>3.7888</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0037</v>
+        <v>0.0241</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7417</v>
+        <v>3.7647</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0037</v>
+        <v>0.0241</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0019</v>
+        <v>0.013</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7417</v>
+        <v>3.7647</v>
       </c>
       <c r="K6" t="n">
         <v>101</v>
@@ -713,7 +713,7 @@
         <v>120</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7436</v>
+        <v>3.7777</v>
       </c>
       <c r="N6" t="n">
         <v>221</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4713</v>
+        <v>3.45</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8376</v>
+        <v>0.8325</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9291</v>
+        <v>0.9463</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4713</v>
+        <v>3.45</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3447</v>
+        <v>1.1967</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1266</v>
+        <v>2.2533</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3447</v>
+        <v>1.1967</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6992</v>
+        <v>0.6462</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1266</v>
+        <v>2.2533</v>
       </c>
       <c r="K7" t="n">
         <v>101</v>
@@ -759,7 +759,7 @@
         <v>120</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8258</v>
+        <v>2.8995</v>
       </c>
       <c r="N7" t="n">
         <v>221</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2806</v>
+        <v>3.0706</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7916</v>
+        <v>0.7409</v>
       </c>
       <c r="D8" t="n">
-        <v>0.843</v>
+        <v>0.7736</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2806</v>
+        <v>3.0706</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2806</v>
+        <v>2.846</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.2246</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8439</v>
+        <v>4.4958</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8439</v>
+        <v>2.4277</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.2246</v>
       </c>
       <c r="K8" t="n">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8439</v>
+        <v>2.6523</v>
       </c>
       <c r="N8" t="n">
-        <v>143</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0794</v>
+        <v>2.9627</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7431</v>
+        <v>0.7149</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7522</v>
+        <v>0.7245</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0794</v>
+        <v>2.9627</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9247</v>
+        <v>2.4533</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1547</v>
+        <v>0.5094</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8185</v>
+        <v>3.2002</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5054</v>
+        <v>1.7281</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1547</v>
+        <v>0.5094</v>
       </c>
       <c r="K9" t="n">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="L9" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6601</v>
+        <v>2.2375</v>
       </c>
       <c r="N9" t="n">
-        <v>201</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0503</v>
+        <v>2.9565</v>
       </c>
       <c r="C10" t="n">
-        <v>0.736</v>
+        <v>0.7134</v>
       </c>
       <c r="D10" t="n">
-        <v>0.739</v>
+        <v>0.7217</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0503</v>
+        <v>2.9565</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5447</v>
+        <v>2.9565</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5056</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4797</v>
+        <v>3.7459</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8093</v>
+        <v>3.7459</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5056</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3149</v>
+        <v>3.7459</v>
       </c>
       <c r="N10" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7589</v>
+        <v>2.6838</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6657</v>
+        <v>0.6476</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6075</v>
+        <v>0.5975</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7589</v>
+        <v>2.6838</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2587</v>
+        <v>3.2109</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4998</v>
+        <v>-0.5271</v>
       </c>
       <c r="H11" t="n">
-        <v>5.9951</v>
+        <v>5.6997</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1172</v>
+        <v>3.0778</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4998</v>
+        <v>-0.5271</v>
       </c>
       <c r="K11" t="n">
         <v>130</v>
@@ -943,7 +943,7 @@
         <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6174</v>
+        <v>2.5507</v>
       </c>
       <c r="N11" t="n">
         <v>174</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7031</v>
+        <v>2.6321</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6523</v>
+        <v>0.6351</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5823</v>
+        <v>0.574</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7031</v>
+        <v>2.6321</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4512</v>
+        <v>2.381</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2519</v>
+        <v>0.2511</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1503</v>
+        <v>2.9617</v>
       </c>
       <c r="I12" t="n">
-        <v>1.638</v>
+        <v>1.5993</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2519</v>
+        <v>0.2511</v>
       </c>
       <c r="K12" t="n">
         <v>130</v>
@@ -989,7 +989,7 @@
         <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8899</v>
+        <v>1.8504</v>
       </c>
       <c r="N12" t="n">
         <v>174</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6865</v>
+        <v>2.5781</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6483</v>
+        <v>0.6221</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5748</v>
+        <v>0.5494</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6865</v>
+        <v>2.5781</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3658</v>
+        <v>2.2556</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3207</v>
+        <v>0.3225</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8493</v>
+        <v>2.5478</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4815</v>
+        <v>1.3758</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3207</v>
+        <v>0.3225</v>
       </c>
       <c r="K13" t="n">
         <v>83</v>
@@ -1035,7 +1035,7 @@
         <v>34</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8022</v>
+        <v>1.6983</v>
       </c>
       <c r="N13" t="n">
         <v>117</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6071</v>
+        <v>2.4742</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6291</v>
+        <v>0.597</v>
       </c>
       <c r="D14" t="n">
-        <v>0.539</v>
+        <v>0.5021</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6071</v>
+        <v>2.4742</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5411</v>
+        <v>3.4687</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>6.9902</v>
+        <v>6.5505</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6346</v>
+        <v>3.5372</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>71</v>
@@ -1081,7 +1081,7 @@
         <v>130</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7006</v>
+        <v>2.5427</v>
       </c>
       <c r="N14" t="n">
         <v>201</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4745</v>
+        <v>2.4721</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5971</v>
+        <v>0.5965</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4791</v>
+        <v>0.5011</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4745</v>
+        <v>2.4721</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2343</v>
+        <v>1.1713</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2402</v>
+        <v>1.3008</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2343</v>
+        <v>1.1713</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6418</v>
+        <v>0.6325</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2402</v>
+        <v>1.3008</v>
       </c>
       <c r="K15" t="n">
         <v>71</v>
@@ -1127,7 +1127,7 @@
         <v>130</v>
       </c>
       <c r="M15" t="n">
-        <v>1.882</v>
+        <v>1.9333</v>
       </c>
       <c r="N15" t="n">
         <v>201</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0196</v>
+        <v>1.9908</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4873</v>
+        <v>0.4804</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2737</v>
+        <v>0.282</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0196</v>
+        <v>1.9908</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0196</v>
+        <v>1.9908</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0196</v>
+        <v>1.9908</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0196</v>
+        <v>1.9908</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0196</v>
+        <v>1.9908</v>
       </c>
       <c r="N16" t="n">
         <v>146</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9179</v>
+        <v>1.9178</v>
       </c>
       <c r="C17" t="n">
         <v>0.4628</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2278</v>
+        <v>0.2488</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9179</v>
+        <v>1.9178</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9179</v>
+        <v>1.9178</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9179</v>
+        <v>1.9178</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9179</v>
+        <v>1.9178</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9179</v>
+        <v>1.9178</v>
       </c>
       <c r="N17" t="n">
         <v>143</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7372</v>
+        <v>1.6566</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4192</v>
+        <v>0.3997</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1462</v>
+        <v>0.1299</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7372</v>
+        <v>1.6566</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7372</v>
+        <v>1.6566</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7372</v>
+        <v>1.6566</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7372</v>
+        <v>1.6566</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7372</v>
+        <v>1.6566</v>
       </c>
       <c r="N18" t="n">
         <v>88</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.724</v>
+        <v>1.6174</v>
       </c>
       <c r="C19" t="n">
-        <v>0.416</v>
+        <v>0.3903</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1403</v>
+        <v>0.1121</v>
       </c>
       <c r="E19" t="n">
-        <v>1.724</v>
+        <v>1.6174</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3545</v>
+        <v>2.2867</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6693</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8095</v>
+        <v>2.6504</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4608</v>
+        <v>1.4312</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6693</v>
       </c>
       <c r="K19" t="n">
         <v>83</v>
@@ -1311,7 +1311,7 @@
         <v>34</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8303000000000001</v>
+        <v>0.7619</v>
       </c>
       <c r="N19" t="n">
         <v>117</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4279</v>
+        <v>1.3683</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3446</v>
+        <v>0.3302</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0066</v>
+        <v>-0.0013</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4279</v>
+        <v>1.3683</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4279</v>
+        <v>2.3683</v>
       </c>
       <c r="G20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>3.0682</v>
+        <v>2.9197</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5953</v>
+        <v>1.5766</v>
       </c>
       <c r="J20" t="n">
         <v>-1</v>
@@ -1357,7 +1357,7 @@
         <v>34</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5952999999999999</v>
+        <v>0.5766</v>
       </c>
       <c r="N20" t="n">
         <v>117</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3571</v>
+        <v>1.2786</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3275</v>
+        <v>0.3085</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0254</v>
+        <v>-0.0422</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3571</v>
+        <v>1.2786</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3571</v>
+        <v>1.2786</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3571</v>
+        <v>1.2786</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3571</v>
+        <v>1.2786</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3571</v>
+        <v>1.2786</v>
       </c>
       <c r="N21" t="n">
         <v>146</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.064</v>
+        <v>1.2712</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2567</v>
+        <v>0.3067</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1577</v>
+        <v>-0.0455</v>
       </c>
       <c r="E22" t="n">
-        <v>1.064</v>
+        <v>1.2712</v>
       </c>
       <c r="F22" t="n">
-        <v>0.345</v>
+        <v>0.3476</v>
       </c>
       <c r="G22" t="n">
-        <v>0.719</v>
+        <v>0.9236</v>
       </c>
       <c r="H22" t="n">
-        <v>0.345</v>
+        <v>0.3476</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1794</v>
+        <v>0.1877</v>
       </c>
       <c r="J22" t="n">
-        <v>0.719</v>
+        <v>0.9236</v>
       </c>
       <c r="K22" t="n">
         <v>101</v>
@@ -1449,7 +1449,7 @@
         <v>120</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8984</v>
+        <v>1.1113</v>
       </c>
       <c r="N22" t="n">
         <v>221</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9981</v>
+        <v>0.9011</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2408</v>
+        <v>0.2174</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1874</v>
+        <v>-0.214</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9981</v>
+        <v>0.9011</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9981</v>
+        <v>0.9011</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9981</v>
+        <v>0.9011</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9981</v>
+        <v>0.9011</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9981</v>
+        <v>0.9011</v>
       </c>
       <c r="N23" t="n">
         <v>143</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9059</v>
+        <v>0.8568</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2186</v>
+        <v>0.2067</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.229</v>
+        <v>-0.2342</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9059</v>
+        <v>0.8568</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9059</v>
+        <v>0.8568</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9059</v>
+        <v>0.8568</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9059</v>
+        <v>0.8568</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9059</v>
+        <v>0.8568</v>
       </c>
       <c r="N24" t="n">
         <v>88</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Banjo</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8116</v>
+        <v>0.7104</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1958</v>
+        <v>0.1714</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2716</v>
+        <v>-0.3008</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8116</v>
+        <v>0.7104</v>
       </c>
       <c r="F25" t="n">
-        <v>1.168</v>
+        <v>0.7104</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3564</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.168</v>
+        <v>0.7104</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6073</v>
+        <v>0.7104</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3564</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="L25" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2509</v>
+        <v>0.7104</v>
       </c>
       <c r="N25" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>Banjo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.751</v>
+        <v>0.6876</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1812</v>
+        <v>0.1659</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.299</v>
+        <v>-0.3112</v>
       </c>
       <c r="E26" t="n">
-        <v>0.751</v>
+        <v>0.6876</v>
       </c>
       <c r="F26" t="n">
-        <v>0.751</v>
+        <v>1.0552</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.3676</v>
       </c>
       <c r="H26" t="n">
-        <v>0.751</v>
+        <v>1.0552</v>
       </c>
       <c r="I26" t="n">
-        <v>0.751</v>
+        <v>0.5698</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.3676</v>
       </c>
       <c r="K26" t="n">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M26" t="n">
-        <v>0.751</v>
+        <v>0.2022</v>
       </c>
       <c r="N26" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.703</v>
+        <v>0.6575</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1696</v>
+        <v>0.1587</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3206</v>
+        <v>-0.3249</v>
       </c>
       <c r="E27" t="n">
-        <v>0.703</v>
+        <v>0.6575</v>
       </c>
       <c r="F27" t="n">
-        <v>0.703</v>
+        <v>0.6575</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.703</v>
+        <v>0.6575</v>
       </c>
       <c r="I27" t="n">
-        <v>0.703</v>
+        <v>0.6575</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.703</v>
+        <v>0.6575</v>
       </c>
       <c r="N27" t="n">
         <v>143</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3162</v>
+        <v>0.3181</v>
       </c>
       <c r="C28" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4953</v>
+        <v>-0.4794</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3162</v>
+        <v>0.3181</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3162</v>
+        <v>0.3181</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3162</v>
+        <v>0.3181</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3162</v>
+        <v>0.3181</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3162</v>
+        <v>0.3181</v>
       </c>
       <c r="N28" t="n">
         <v>88</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1989</v>
+        <v>0.1354</v>
       </c>
       <c r="C29" t="n">
-        <v>0.048</v>
+        <v>0.0327</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5482</v>
+        <v>-0.5626</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1989</v>
+        <v>0.1354</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1989</v>
+        <v>0.1354</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1989</v>
+        <v>0.1354</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1989</v>
+        <v>0.1354</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1989</v>
+        <v>0.1354</v>
       </c>
       <c r="N29" t="n">
         <v>74</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0324</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0178</v>
+        <v>0.0078</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6047</v>
+        <v>-0.6095</v>
       </c>
       <c r="E30" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0324</v>
       </c>
       <c r="F30" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0324</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0324</v>
       </c>
       <c r="I30" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0324</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0324</v>
       </c>
       <c r="N30" t="n">
         <v>74</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2648</v>
+        <v>-0.2386</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0639</v>
+        <v>-0.0576</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.7328</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2648</v>
+        <v>-0.2386</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2648</v>
+        <v>-0.2386</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2648</v>
+        <v>-0.2386</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2648</v>
+        <v>-0.2386</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2648</v>
+        <v>-0.2386</v>
       </c>
       <c r="N31" t="n">
         <v>146</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4004</v>
+        <v>-0.4295</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.1036</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8188</v>
+        <v>-0.8197</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4004</v>
+        <v>-0.4295</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4004</v>
+        <v>-0.4295</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4004</v>
+        <v>-0.4295</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4004</v>
+        <v>-0.4295</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4004</v>
+        <v>-0.4295</v>
       </c>
       <c r="N32" t="n">
         <v>88</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4145</v>
+        <v>-0.4532</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1</v>
+        <v>-0.1094</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8250999999999999</v>
+        <v>-0.8305</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4145</v>
+        <v>-0.4532</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4145</v>
+        <v>-0.4532</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4145</v>
+        <v>-0.4532</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4145</v>
+        <v>-0.4532</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4145</v>
+        <v>-0.4532</v>
       </c>
       <c r="N33" t="n">
         <v>146</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4639</v>
+        <v>-0.4951</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1119</v>
+        <v>-0.1195</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8474</v>
+        <v>-0.8496</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4639</v>
+        <v>-0.4951</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4639</v>
+        <v>-0.4951</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4639</v>
+        <v>-0.4951</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4639</v>
+        <v>-0.4951</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4639</v>
+        <v>-0.4951</v>
       </c>
       <c r="N34" t="n">
         <v>74</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.602</v>
+        <v>-0.6276</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1453</v>
+        <v>-0.1514</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9098000000000001</v>
+        <v>-0.9099</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.602</v>
+        <v>-0.6276</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.602</v>
+        <v>-0.6276</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.602</v>
+        <v>-0.6276</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.602</v>
+        <v>-0.6276</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.602</v>
+        <v>-0.6276</v>
       </c>
       <c r="N35" t="n">
         <v>88</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6475</v>
+        <v>-0.6865</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1562</v>
+        <v>-0.1657</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9303</v>
+        <v>-0.9367</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6475</v>
+        <v>-0.6865</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6475</v>
+        <v>-0.6865</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6475</v>
+        <v>-0.6865</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6475</v>
+        <v>-0.6865</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6475</v>
+        <v>-0.6865</v>
       </c>
       <c r="N36" t="n">
         <v>74</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0361</v>
+        <v>-0.8962</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.25</v>
+        <v>-0.2163</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1058</v>
+        <v>-1.0322</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0361</v>
+        <v>-0.8962</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7993</v>
+        <v>-0.7045</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.2368</v>
+        <v>-0.1917</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7993</v>
+        <v>-0.7045</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4156</v>
+        <v>-0.3804</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.2368</v>
+        <v>-0.1917</v>
       </c>
       <c r="K37" t="n">
         <v>83</v>
@@ -2139,7 +2139,7 @@
         <v>34</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6524000000000001</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>117</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1814</v>
+        <v>-1.2061</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2851</v>
+        <v>-0.291</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1714</v>
+        <v>-1.1732</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1814</v>
+        <v>-1.2061</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1814</v>
+        <v>-1.2061</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1814</v>
+        <v>-1.2061</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1814</v>
+        <v>-1.2061</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1814</v>
+        <v>-1.2061</v>
       </c>
       <c r="N38" t="n">
         <v>74</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4726</v>
+        <v>-1.3761</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3553</v>
+        <v>-0.3321</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3028</v>
+        <v>-1.2506</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4726</v>
+        <v>-1.3761</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1738</v>
+        <v>-1.0483</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.2988</v>
+        <v>-0.3278</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1738</v>
+        <v>-1.0483</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6103</v>
+        <v>-0.5661</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.2988</v>
+        <v>-0.3278</v>
       </c>
       <c r="K39" t="n">
         <v>130</v>
@@ -2231,7 +2231,7 @@
         <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9091</v>
+        <v>-0.8939</v>
       </c>
       <c r="N39" t="n">
         <v>174</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4857</v>
+        <v>-1.4794</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3585</v>
+        <v>-0.357</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3087</v>
+        <v>-1.2977</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4857</v>
+        <v>-1.4794</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4857</v>
+        <v>-1.4794</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4857</v>
+        <v>-1.4794</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4857</v>
+        <v>-1.4794</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4857</v>
+        <v>-1.4794</v>
       </c>
       <c r="N40" t="n">
         <v>146</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.6155</v>
+        <v>-2.3348</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6311</v>
+        <v>-0.5634</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8188</v>
+        <v>-1.6871</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.6155</v>
+        <v>-2.3348</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6417</v>
+        <v>-1.3874</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9738</v>
+        <v>-0.9474</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6417</v>
+        <v>-1.3874</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8536</v>
+        <v>-0.7492</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9738</v>
+        <v>-0.9474</v>
       </c>
       <c r="K41" t="n">
         <v>71</v>
@@ -2323,7 +2323,7 @@
         <v>130</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8274</v>
+        <v>-1.6966</v>
       </c>
       <c r="N41" t="n">
         <v>201</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3164</v>
+        <v>0.3083</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9608</v>
+        <v>6.7826</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.88</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1416</v>
+        <v>-0.1582</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.1152</v>
+        <v>-3.4804</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2016</v>
+        <v>-0.2191</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.4352</v>
+        <v>-4.8202</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.77</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2508</v>
+        <v>-0.2678</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.5176</v>
+        <v>-5.8916</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3183</v>
+        <v>-0.3336</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.0026</v>
+        <v>-7.3392</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.57</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2205</v>
+        <v>1.2565</v>
       </c>
       <c r="J7" t="n">
-        <v>26.851</v>
+        <v>27.643</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.52</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1578</v>
+        <v>1.1657</v>
       </c>
       <c r="J8" t="n">
-        <v>25.4716</v>
+        <v>25.6454</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5542</v>
+        <v>0.5412</v>
       </c>
       <c r="J9" t="n">
-        <v>12.1924</v>
+        <v>11.9064</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1099</v>
+        <v>0.1313</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4178</v>
+        <v>2.8886</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.86</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5251</v>
+        <v>-0.4891</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.5522</v>
+        <v>-10.7602</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.78</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9123</v>
+        <v>0.8929</v>
       </c>
       <c r="J12" t="n">
-        <v>18.246</v>
+        <v>17.858</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3605</v>
+        <v>0.3768</v>
       </c>
       <c r="J13" t="n">
-        <v>7.21</v>
+        <v>7.536</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2293</v>
+        <v>0.2481</v>
       </c>
       <c r="J14" t="n">
-        <v>4.586</v>
+        <v>4.962</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>0.056</v>
+        <v>0.0726</v>
       </c>
       <c r="J15" t="n">
-        <v>1.12</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.147</v>
+        <v>-0.1541</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.94</v>
+        <v>-3.082</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.06</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1912</v>
+        <v>0.1838</v>
       </c>
       <c r="J17" t="n">
-        <v>3.824</v>
+        <v>3.676</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1156</v>
+        <v>-0.1354</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.312</v>
+        <v>-2.708</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2017</v>
+        <v>-0.2214</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.034</v>
+        <v>-4.428</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.54</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4554</v>
+        <v>-0.4667</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.108000000000001</v>
+        <v>-9.334</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.52</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4739</v>
+        <v>-0.4842</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.478</v>
+        <v>-9.683999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.92</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3668</v>
+        <v>1.4773</v>
       </c>
       <c r="J22" t="n">
-        <v>30.0696</v>
+        <v>32.5006</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.85</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1868</v>
+        <v>-0.2006</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.1096</v>
+        <v>-4.4132</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2577</v>
+        <v>-0.2712</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.6694</v>
+        <v>-5.9664</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2871</v>
+        <v>-0.3</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.3162</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.65</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3821</v>
+        <v>-0.3922</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.4062</v>
+        <v>-8.628399999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7439</v>
+        <v>0.7055</v>
       </c>
       <c r="J27" t="n">
-        <v>16.3658</v>
+        <v>15.521</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.25</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6959</v>
+        <v>0.6631</v>
       </c>
       <c r="J28" t="n">
-        <v>15.3098</v>
+        <v>14.5882</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4484</v>
+        <v>0.4412</v>
       </c>
       <c r="J29" t="n">
-        <v>9.864800000000001</v>
+        <v>9.7064</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.08</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2608</v>
+        <v>0.2677</v>
       </c>
       <c r="J30" t="n">
-        <v>5.7376</v>
+        <v>5.8894</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3566</v>
+        <v>-0.3408</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.8452</v>
+        <v>-7.4976</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6135</v>
+        <v>0.5856</v>
       </c>
       <c r="J32" t="n">
-        <v>13.497</v>
+        <v>12.8832</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.86</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1648</v>
+        <v>-0.1811</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.6256</v>
+        <v>-3.9842</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2154</v>
+        <v>-0.2319</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.7388</v>
+        <v>-5.1018</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2254</v>
+        <v>-0.2418</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.9588</v>
+        <v>-5.3196</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3226</v>
+        <v>-0.337</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.0972</v>
+        <v>-7.414</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.78</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4947</v>
+        <v>1.6169</v>
       </c>
       <c r="J37" t="n">
-        <v>32.8834</v>
+        <v>35.5718</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.36</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9327</v>
+        <v>0.8752</v>
       </c>
       <c r="J38" t="n">
-        <v>20.5194</v>
+        <v>19.2544</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3332</v>
+        <v>0.3379</v>
       </c>
       <c r="J39" t="n">
-        <v>7.3304</v>
+        <v>7.4338</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2474</v>
+        <v>-0.2352</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.4428</v>
+        <v>-5.1744</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8239</v>
+        <v>-0.7573</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.1258</v>
+        <v>-16.6606</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4672</v>
+        <v>0.5087</v>
       </c>
       <c r="J42" t="n">
-        <v>9.343999999999999</v>
+        <v>10.174</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.07</v>
       </c>
       <c r="I43" t="n">
-        <v>0.232</v>
+        <v>0.2269</v>
       </c>
       <c r="J43" t="n">
-        <v>4.64</v>
+        <v>4.538</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.85</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1714</v>
+        <v>-0.1888</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.428</v>
+        <v>-3.776</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.63</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3834</v>
+        <v>-0.3964</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.668</v>
+        <v>-7.928</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.46</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5399</v>
+        <v>-0.5445</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.798</v>
+        <v>-10.89</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0499</v>
+        <v>1.1545</v>
       </c>
       <c r="J47" t="n">
-        <v>20.998</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5431</v>
+        <v>0.6045</v>
       </c>
       <c r="J48" t="n">
-        <v>10.862</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.26</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5431</v>
+        <v>0.6045</v>
       </c>
       <c r="J49" t="n">
-        <v>10.862</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.11</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3135</v>
+        <v>0.3247</v>
       </c>
       <c r="J50" t="n">
-        <v>6.27</v>
+        <v>6.494</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.06</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1672</v>
+        <v>0.1879</v>
       </c>
       <c r="J51" t="n">
-        <v>3.344</v>
+        <v>3.758</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.15</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4921</v>
+        <v>0.5113</v>
       </c>
       <c r="J52" t="n">
-        <v>6.8894</v>
+        <v>7.1582</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.73</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2471</v>
+        <v>-0.2729</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.4594</v>
+        <v>-3.8206</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.49</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.474</v>
+        <v>-0.4886</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.636</v>
+        <v>-6.8404</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.37</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5884</v>
+        <v>-0.5945</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.2376</v>
+        <v>-8.323</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.25</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.704</v>
+        <v>-0.7004</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.856</v>
+        <v>-9.8056</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.87</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2249</v>
+        <v>1.3517</v>
       </c>
       <c r="J57" t="n">
-        <v>17.1486</v>
+        <v>18.9238</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.65</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9811</v>
+        <v>1.092</v>
       </c>
       <c r="J58" t="n">
-        <v>13.7354</v>
+        <v>15.288</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.6</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9261</v>
+        <v>1.0325</v>
       </c>
       <c r="J59" t="n">
-        <v>12.9654</v>
+        <v>14.455</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.58</v>
       </c>
       <c r="I60" t="n">
-        <v>0.9036999999999999</v>
+        <v>1.0082</v>
       </c>
       <c r="J60" t="n">
-        <v>12.6518</v>
+        <v>14.1148</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.36</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6371</v>
+        <v>0.7178</v>
       </c>
       <c r="J61" t="n">
-        <v>8.9194</v>
+        <v>10.0492</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.62</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0195</v>
+        <v>1.1189</v>
       </c>
       <c r="J62" t="n">
-        <v>20.39</v>
+        <v>22.378</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.49</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8549</v>
+        <v>0.9432</v>
       </c>
       <c r="J63" t="n">
-        <v>17.098</v>
+        <v>18.864</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3795</v>
+        <v>0.4095</v>
       </c>
       <c r="J64" t="n">
-        <v>7.59</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.03</v>
       </c>
       <c r="I65" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.1041</v>
       </c>
       <c r="J65" t="n">
-        <v>1.69</v>
+        <v>2.082</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.72</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8759</v>
+        <v>-0.8024</v>
       </c>
       <c r="J66" t="n">
-        <v>-17.518</v>
+        <v>-16.048</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2545</v>
+        <v>0.2535</v>
       </c>
       <c r="J67" t="n">
-        <v>5.09</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.92</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.103</v>
+        <v>-0.117</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.06</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.87</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1561</v>
+        <v>-0.1719</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.122</v>
+        <v>-3.438</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1665</v>
+        <v>-0.1824</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.33</v>
+        <v>-3.648</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.78</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2472</v>
+        <v>-0.2629</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.944</v>
+        <v>-5.258</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.45</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8381</v>
+        <v>0.9184</v>
       </c>
       <c r="J72" t="n">
-        <v>20.1144</v>
+        <v>22.0416</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.37</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7291</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>17.4984</v>
+        <v>19.2216</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.91</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3402</v>
+        <v>-0.3293</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.1648</v>
+        <v>-7.9032</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4545</v>
+        <v>-0.4339</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.908</v>
+        <v>-10.4136</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7446</v>
+        <v>-0.6927</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.8704</v>
+        <v>-16.6248</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.16</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3549</v>
+        <v>0.3681</v>
       </c>
       <c r="J77" t="n">
-        <v>8.5176</v>
+        <v>8.8344</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2511</v>
+        <v>0.2559</v>
       </c>
       <c r="J78" t="n">
-        <v>6.0264</v>
+        <v>6.1416</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1658</v>
+        <v>0.173</v>
       </c>
       <c r="J79" t="n">
-        <v>3.9792</v>
+        <v>4.152</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1323</v>
+        <v>-0.1454</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.1752</v>
+        <v>-3.4896</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3437</v>
+        <v>-0.3552</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.248799999999999</v>
+        <v>-8.524800000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.45</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0808</v>
+        <v>1.0363</v>
       </c>
       <c r="J82" t="n">
-        <v>25.9392</v>
+        <v>24.8712</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.27</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.6946</v>
       </c>
       <c r="J83" t="n">
-        <v>17.4792</v>
+        <v>16.6704</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.19</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5385</v>
+        <v>0.5251</v>
       </c>
       <c r="J84" t="n">
-        <v>12.924</v>
+        <v>12.6024</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1232</v>
+        <v>0.1406</v>
       </c>
       <c r="J85" t="n">
-        <v>2.9568</v>
+        <v>3.3744</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.178</v>
+        <v>-0.1687</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.272</v>
+        <v>-4.0488</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3021</v>
+        <v>0.2978</v>
       </c>
       <c r="J87" t="n">
-        <v>7.2504</v>
+        <v>7.1472</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0391</v>
+        <v>-0.0499</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.9384</v>
+        <v>-1.1976</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1443</v>
+        <v>-0.1602</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.4632</v>
+        <v>-3.8448</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.165</v>
+        <v>-0.1813</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.96</v>
+        <v>-4.3512</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3889</v>
+        <v>-0.4007</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.333600000000001</v>
+        <v>-9.6168</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.63</v>
       </c>
       <c r="I92" t="n">
-        <v>1.299</v>
+        <v>1.2734</v>
       </c>
       <c r="J92" t="n">
-        <v>25.98</v>
+        <v>25.468</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.47</v>
       </c>
       <c r="I93" t="n">
-        <v>1.0975</v>
+        <v>1.0574</v>
       </c>
       <c r="J93" t="n">
-        <v>21.95</v>
+        <v>21.148</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.15</v>
       </c>
       <c r="I94" t="n">
-        <v>0.432</v>
+        <v>0.4301</v>
       </c>
       <c r="J94" t="n">
-        <v>8.640000000000001</v>
+        <v>8.602</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1783</v>
+        <v>0.1956</v>
       </c>
       <c r="J95" t="n">
-        <v>3.566</v>
+        <v>3.912</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6549</v>
+        <v>-0.6063</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.098</v>
+        <v>-12.126</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.281</v>
+        <v>0.2778</v>
       </c>
       <c r="J97" t="n">
-        <v>5.62</v>
+        <v>5.556</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2378</v>
+        <v>0.2364</v>
       </c>
       <c r="J98" t="n">
-        <v>4.756</v>
+        <v>4.728</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.88</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1443</v>
+        <v>-0.1602</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.886</v>
+        <v>-3.204</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2256</v>
+        <v>-0.242</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.512</v>
+        <v>-4.84</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.426</v>
+        <v>-0.4362</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.52</v>
+        <v>-8.724</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.33</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7022</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>14.7462</v>
+        <v>14.0469</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.14</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3496</v>
+        <v>0.3455</v>
       </c>
       <c r="J103" t="n">
-        <v>7.3416</v>
+        <v>7.2555</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.78</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.25</v>
+        <v>-0.2651</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.25</v>
+        <v>-5.5671</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.74</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2891</v>
+        <v>-0.3034</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.0711</v>
+        <v>-6.3714</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.384</v>
+        <v>-0.3953</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.064</v>
+        <v>-8.301299999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.64</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3218</v>
+        <v>1.2958</v>
       </c>
       <c r="J107" t="n">
-        <v>27.7578</v>
+        <v>27.2118</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.36</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9327</v>
+        <v>0.8752</v>
       </c>
       <c r="J108" t="n">
-        <v>19.5867</v>
+        <v>18.3792</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2477</v>
+        <v>0.2587</v>
       </c>
       <c r="J109" t="n">
-        <v>5.2017</v>
+        <v>5.4327</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.179</v>
+        <v>-0.1694</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.759</v>
+        <v>-3.5574</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4292</v>
+        <v>-0.4044</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.013199999999999</v>
+        <v>-8.4924</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.91</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9887</v>
+        <v>0.9739</v>
       </c>
       <c r="J112" t="n">
-        <v>16.8079</v>
+        <v>16.5563</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.73</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8218</v>
+        <v>0.8153</v>
       </c>
       <c r="J113" t="n">
-        <v>13.9706</v>
+        <v>13.8601</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.27</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3436</v>
+        <v>0.3642</v>
       </c>
       <c r="J114" t="n">
-        <v>5.8412</v>
+        <v>6.1914</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.16</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2085</v>
+        <v>0.2323</v>
       </c>
       <c r="J115" t="n">
-        <v>3.5445</v>
+        <v>3.9491</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.03</v>
       </c>
       <c r="I116" t="n">
-        <v>0.017</v>
+        <v>0.0377</v>
       </c>
       <c r="J116" t="n">
-        <v>0.289</v>
+        <v>0.6409</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0242</v>
+        <v>-0.0458</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.4114</v>
+        <v>-0.7786</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.79</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2109</v>
+        <v>-0.2329</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.5853</v>
+        <v>-3.9593</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.73</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2704</v>
+        <v>-0.291</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.5968</v>
+        <v>-4.947</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.58</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4082</v>
+        <v>-0.4238</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.9394</v>
+        <v>-7.2046</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.46</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5205</v>
+        <v>-0.5292</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.8485</v>
+        <v>-8.9964</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.39</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8181</v>
+        <v>0.7711</v>
       </c>
       <c r="J122" t="n">
-        <v>16.362</v>
+        <v>15.422</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.36</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.7242</v>
       </c>
       <c r="J123" t="n">
-        <v>15.312</v>
+        <v>14.484</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.8</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2276</v>
+        <v>-0.2435</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.552</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.53</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4829</v>
+        <v>-0.4899</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.657999999999999</v>
+        <v>-9.798</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.45</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5551</v>
+        <v>-0.5579</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.102</v>
+        <v>-11.158</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.97</v>
       </c>
       <c r="I127" t="n">
-        <v>1.688</v>
+        <v>1.6851</v>
       </c>
       <c r="J127" t="n">
-        <v>33.76</v>
+        <v>33.702</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.31</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7966</v>
+        <v>0.7594</v>
       </c>
       <c r="J128" t="n">
-        <v>15.932</v>
+        <v>15.188</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6864</v>
+        <v>0.6614</v>
       </c>
       <c r="J129" t="n">
-        <v>13.728</v>
+        <v>13.228</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0482</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.39</v>
+        <v>-0.964</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.89</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4526</v>
+        <v>-0.4208</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.052</v>
+        <v>-8.416</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0759</v>
+        <v>-0.0897</v>
       </c>
       <c r="J132" t="n">
-        <v>-1.518</v>
+        <v>-1.794</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.91</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.111</v>
+        <v>-0.1263</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.22</v>
+        <v>-2.526</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.89</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1329</v>
+        <v>-0.1488</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.658</v>
+        <v>-2.976</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.85</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1735</v>
+        <v>-0.1903</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.47</v>
+        <v>-3.806</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2434</v>
+        <v>-0.26</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.868</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.69</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8032</v>
       </c>
       <c r="J137" t="n">
-        <v>16.28</v>
+        <v>16.064</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.54</v>
       </c>
       <c r="I138" t="n">
-        <v>0.656</v>
+        <v>0.6571</v>
       </c>
       <c r="J138" t="n">
-        <v>13.12</v>
+        <v>13.142</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.28</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3698</v>
+        <v>0.3863</v>
       </c>
       <c r="J139" t="n">
-        <v>7.396</v>
+        <v>7.726</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.97</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0752</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>-1.504</v>
+        <v>-1.554</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2744</v>
+        <v>-0.2823</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.488</v>
+        <v>-5.646</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.84</v>
       </c>
       <c r="I142" t="n">
-        <v>1.6059</v>
+        <v>1.5886</v>
       </c>
       <c r="J142" t="n">
-        <v>38.5416</v>
+        <v>38.1264</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.11</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3505</v>
+        <v>0.3496</v>
       </c>
       <c r="J143" t="n">
-        <v>8.412000000000001</v>
+        <v>8.3904</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.02</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0736</v>
+        <v>0.0859</v>
       </c>
       <c r="J144" t="n">
-        <v>1.7664</v>
+        <v>2.0616</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.78</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.7002</v>
+        <v>-0.6524</v>
       </c>
       <c r="J145" t="n">
-        <v>-16.8048</v>
+        <v>-15.6576</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.7631</v>
       </c>
       <c r="J146" t="n">
-        <v>-19.8264</v>
+        <v>-18.3144</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.43</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8205</v>
+        <v>0.7832</v>
       </c>
       <c r="J147" t="n">
-        <v>19.692</v>
+        <v>18.7968</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.11</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2573</v>
+        <v>0.2651</v>
       </c>
       <c r="J148" t="n">
-        <v>6.1752</v>
+        <v>6.3624</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0867</v>
+        <v>0.0964</v>
       </c>
       <c r="J149" t="n">
-        <v>2.0808</v>
+        <v>2.3136</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.86</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.182</v>
+        <v>-0.1944</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.368</v>
+        <v>-4.6656</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.77</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2733</v>
+        <v>-0.2853</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.5592</v>
+        <v>-6.8472</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9524</v>
+        <v>0.8902</v>
       </c>
       <c r="J152" t="n">
-        <v>21.9052</v>
+        <v>20.4746</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.09</v>
       </c>
       <c r="I153" t="n">
-        <v>0.29</v>
+        <v>0.2949</v>
       </c>
       <c r="J153" t="n">
-        <v>6.67</v>
+        <v>6.7827</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.07</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2316</v>
+        <v>0.2402</v>
       </c>
       <c r="J154" t="n">
-        <v>5.3268</v>
+        <v>5.5246</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.07</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2316</v>
+        <v>0.2402</v>
       </c>
       <c r="J155" t="n">
-        <v>5.3268</v>
+        <v>5.5246</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.06</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2011</v>
+        <v>0.2114</v>
       </c>
       <c r="J156" t="n">
-        <v>4.6253</v>
+        <v>4.8622</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.5</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9794</v>
+        <v>0.9232</v>
       </c>
       <c r="J157" t="n">
-        <v>22.5262</v>
+        <v>21.2336</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3253</v>
+        <v>0.3235</v>
       </c>
       <c r="J158" t="n">
-        <v>7.4819</v>
+        <v>7.4405</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.95</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0709</v>
+        <v>-0.0823</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.6307</v>
+        <v>-1.8929</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.59</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4317</v>
+        <v>-0.4407</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.9291</v>
+        <v>-10.1361</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.52</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4954</v>
+        <v>-0.5012</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.3942</v>
+        <v>-11.5276</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.73</v>
       </c>
       <c r="I162" t="n">
-        <v>1.4058</v>
+        <v>1.3892</v>
       </c>
       <c r="J162" t="n">
-        <v>28.116</v>
+        <v>27.784</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.54</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1737</v>
+        <v>1.1424</v>
       </c>
       <c r="J163" t="n">
-        <v>23.474</v>
+        <v>22.848</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.42</v>
       </c>
       <c r="I164" t="n">
-        <v>1.0188</v>
+        <v>0.9678</v>
       </c>
       <c r="J164" t="n">
-        <v>20.376</v>
+        <v>19.356</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2365</v>
+        <v>-0.219</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.73</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.8192</v>
+        <v>-0.7497</v>
       </c>
       <c r="J166" t="n">
-        <v>-16.384</v>
+        <v>-14.994</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.14</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3769</v>
+        <v>0.3656</v>
       </c>
       <c r="J167" t="n">
-        <v>7.538</v>
+        <v>7.312</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0196</v>
+        <v>-0.0302</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.392</v>
+        <v>-0.604</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1722</v>
+        <v>-0.1894</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.444</v>
+        <v>-3.788</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2998</v>
+        <v>-0.3155</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.996</v>
+        <v>-6.31</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.61</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4036</v>
+        <v>-0.4155</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.071999999999999</v>
+        <v>-8.31</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.98</v>
       </c>
       <c r="I172" t="n">
-        <v>1.6379</v>
+        <v>1.6424</v>
       </c>
       <c r="J172" t="n">
-        <v>26.2064</v>
+        <v>26.2784</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.81</v>
       </c>
       <c r="I173" t="n">
-        <v>1.4478</v>
+        <v>1.4424</v>
       </c>
       <c r="J173" t="n">
-        <v>23.1648</v>
+        <v>23.0784</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.54</v>
       </c>
       <c r="I174" t="n">
-        <v>1.1388</v>
+        <v>1.112</v>
       </c>
       <c r="J174" t="n">
-        <v>18.2208</v>
+        <v>17.792</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.24</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5936</v>
+        <v>0.5879</v>
       </c>
       <c r="J175" t="n">
-        <v>9.4976</v>
+        <v>9.4064</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1176</v>
+        <v>-0.082</v>
       </c>
       <c r="J176" t="n">
-        <v>-1.8816</v>
+        <v>-1.312</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2985</v>
+        <v>0.265</v>
       </c>
       <c r="J177" t="n">
-        <v>4.776</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.75</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2423</v>
+        <v>-0.2654</v>
       </c>
       <c r="J178" t="n">
-        <v>-3.8768</v>
+        <v>-4.2464</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.68</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3105</v>
+        <v>-0.3313</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.968</v>
+        <v>-5.3008</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.49</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4851</v>
+        <v>-0.4973</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.7616</v>
+        <v>-7.9568</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.32</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6453</v>
+        <v>-0.6456</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.3248</v>
+        <v>-10.3296</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.03</v>
       </c>
       <c r="I182" t="n">
-        <v>0.1258</v>
+        <v>0.1246</v>
       </c>
       <c r="J182" t="n">
-        <v>2.6418</v>
+        <v>2.6166</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0689</v>
+        <v>0.0658</v>
       </c>
       <c r="J183" t="n">
-        <v>1.4469</v>
+        <v>1.3818</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.87</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1532</v>
+        <v>-0.1697</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.2172</v>
+        <v>-3.5637</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2135</v>
+        <v>-0.2304</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.4835</v>
+        <v>-4.8384</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.64</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3772</v>
+        <v>-0.39</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.9212</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.01</v>
       </c>
       <c r="I187" t="n">
-        <v>1.7453</v>
+        <v>1.7431</v>
       </c>
       <c r="J187" t="n">
-        <v>36.6513</v>
+        <v>36.6051</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.47</v>
       </c>
       <c r="I188" t="n">
-        <v>1.0908</v>
+        <v>1.0512</v>
       </c>
       <c r="J188" t="n">
-        <v>22.9068</v>
+        <v>22.0752</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.02</v>
       </c>
       <c r="I189" t="n">
-        <v>0.0336</v>
+        <v>0.058</v>
       </c>
       <c r="J189" t="n">
-        <v>0.7056</v>
+        <v>1.218</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1174</v>
+        <v>-0.1031</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.4654</v>
+        <v>-2.1651</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.79</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.7136</v>
+        <v>-0.6572</v>
       </c>
       <c r="J191" t="n">
-        <v>-14.9856</v>
+        <v>-13.8012</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2703</v>
+        <v>0.2746</v>
       </c>
       <c r="J192" t="n">
-        <v>9.4605</v>
+        <v>9.611000000000001</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.25</v>
+        <v>0.2551</v>
       </c>
       <c r="J193" t="n">
-        <v>8.75</v>
+        <v>8.9285</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.03</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0944</v>
+        <v>0.1018</v>
       </c>
       <c r="J194" t="n">
-        <v>3.304</v>
+        <v>3.563</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.97</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0488</v>
+        <v>-0.0573</v>
       </c>
       <c r="J195" t="n">
-        <v>-1.708</v>
+        <v>-2.0055</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3156</v>
+        <v>-0.3279</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.046</v>
+        <v>-11.4765</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.39</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0131</v>
+        <v>0.9524</v>
       </c>
       <c r="J197" t="n">
-        <v>35.4585</v>
+        <v>33.334</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.38</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9959</v>
+        <v>0.9335</v>
       </c>
       <c r="J198" t="n">
-        <v>34.8565</v>
+        <v>32.6725</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.11</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3478</v>
+        <v>0.3479</v>
       </c>
       <c r="J199" t="n">
-        <v>12.173</v>
+        <v>12.1765</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4104</v>
+        <v>-0.3912</v>
       </c>
       <c r="J200" t="n">
-        <v>-14.364</v>
+        <v>-13.692</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.628</v>
+        <v>-0.5874</v>
       </c>
       <c r="J201" t="n">
-        <v>-21.98</v>
+        <v>-20.559</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.64</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9335</v>
+        <v>0.8844</v>
       </c>
       <c r="J202" t="n">
-        <v>18.67</v>
+        <v>17.688</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.29</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4807</v>
+        <v>0.472</v>
       </c>
       <c r="J203" t="n">
-        <v>9.614000000000001</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3377</v>
+        <v>-0.3506</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.754</v>
+        <v>-7.012</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.62</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4033</v>
+        <v>-0.4137</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.066000000000001</v>
+        <v>-8.273999999999999</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.42</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5843</v>
+        <v>-0.5849</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.686</v>
+        <v>-11.698</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.29</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3949</v>
+        <v>0.4076</v>
       </c>
       <c r="J207" t="n">
-        <v>7.898</v>
+        <v>8.151999999999999</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.25</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3472</v>
+        <v>0.3617</v>
       </c>
       <c r="J208" t="n">
-        <v>6.944</v>
+        <v>7.234</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.11</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1717</v>
+        <v>0.1885</v>
       </c>
       <c r="J209" t="n">
-        <v>3.434</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.06</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0987</v>
+        <v>0.1142</v>
       </c>
       <c r="J210" t="n">
-        <v>1.974</v>
+        <v>2.284</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.04</v>
       </c>
       <c r="I211" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0803</v>
       </c>
       <c r="J211" t="n">
-        <v>1.324</v>
+        <v>1.606</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.08</v>
       </c>
       <c r="I212" t="n">
-        <v>1.7394</v>
+        <v>1.7498</v>
       </c>
       <c r="J212" t="n">
-        <v>26.091</v>
+        <v>26.247</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.87</v>
       </c>
       <c r="I213" t="n">
-        <v>1.5084</v>
+        <v>1.5076</v>
       </c>
       <c r="J213" t="n">
-        <v>22.626</v>
+        <v>22.614</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.55</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1477</v>
+        <v>1.1222</v>
       </c>
       <c r="J214" t="n">
-        <v>17.2155</v>
+        <v>16.833</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.51</v>
       </c>
       <c r="I215" t="n">
-        <v>1.1019</v>
+        <v>1.0722</v>
       </c>
       <c r="J215" t="n">
-        <v>16.5285</v>
+        <v>16.083</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.75</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.8668</v>
+        <v>-0.7834</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.002</v>
+        <v>-11.751</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.65</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.3295</v>
+        <v>-0.3513</v>
       </c>
       <c r="J217" t="n">
-        <v>-4.9425</v>
+        <v>-5.2695</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.64</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3389</v>
+        <v>-0.3603</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.0835</v>
+        <v>-5.4045</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.62</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3572</v>
+        <v>-0.3779</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.358</v>
+        <v>-5.6685</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.59</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3831</v>
+        <v>-0.4027</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.7465</v>
+        <v>-6.0405</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.53</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.438</v>
+        <v>-0.4546</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.57</v>
+        <v>-6.819</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.66</v>
       </c>
       <c r="I222" t="n">
-        <v>1.292</v>
+        <v>1.2739</v>
       </c>
       <c r="J222" t="n">
-        <v>23.256</v>
+        <v>22.9302</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.63</v>
       </c>
       <c r="I223" t="n">
-        <v>1.2567</v>
+        <v>1.2362</v>
       </c>
       <c r="J223" t="n">
-        <v>22.6206</v>
+        <v>22.2516</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.48</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0778</v>
+        <v>1.0419</v>
       </c>
       <c r="J224" t="n">
-        <v>19.4004</v>
+        <v>18.7542</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.43</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0126</v>
+        <v>0.9659</v>
       </c>
       <c r="J225" t="n">
-        <v>18.2268</v>
+        <v>17.3862</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.89</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4803</v>
+        <v>-0.4404</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.6454</v>
+        <v>-7.9272</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.12</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3734</v>
+        <v>0.3547</v>
       </c>
       <c r="J227" t="n">
-        <v>6.7212</v>
+        <v>6.3846</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.86</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1532</v>
+        <v>-0.1723</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.7576</v>
+        <v>-3.1014</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.84</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1743</v>
+        <v>-0.1935</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.1374</v>
+        <v>-3.483</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.58</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4213</v>
+        <v>-0.4341</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.5834</v>
+        <v>-7.8138</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.53</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4678</v>
+        <v>-0.478</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.420400000000001</v>
+        <v>-8.603999999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.48</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1248</v>
+        <v>1.0845</v>
       </c>
       <c r="J232" t="n">
-        <v>25.8704</v>
+        <v>24.9435</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.26</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6776</v>
       </c>
       <c r="J233" t="n">
-        <v>16.3346</v>
+        <v>15.5848</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.07</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2236</v>
+        <v>0.2347</v>
       </c>
       <c r="J234" t="n">
-        <v>5.1428</v>
+        <v>5.3981</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.05</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1612</v>
+        <v>0.1757</v>
       </c>
       <c r="J235" t="n">
-        <v>3.7076</v>
+        <v>4.0411</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.96</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2078</v>
+        <v>-0.1989</v>
       </c>
       <c r="J236" t="n">
-        <v>-4.7794</v>
+        <v>-4.5747</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.24</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5342</v>
+        <v>0.5175</v>
       </c>
       <c r="J237" t="n">
-        <v>12.2866</v>
+        <v>11.9025</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.04</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1299</v>
+        <v>0.1346</v>
       </c>
       <c r="J238" t="n">
-        <v>2.9877</v>
+        <v>3.0958</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1278</v>
+        <v>-0.1419</v>
       </c>
       <c r="J239" t="n">
-        <v>-2.9394</v>
+        <v>-3.2637</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2218</v>
+        <v>-0.2369</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.1014</v>
+        <v>-5.4487</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3197</v>
+        <v>-0.3329</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.3531</v>
+        <v>-7.6567</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.09</v>
       </c>
       <c r="I242" t="n">
-        <v>0.221</v>
+        <v>0.2184</v>
       </c>
       <c r="J242" t="n">
-        <v>3.978</v>
+        <v>3.9312</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.9</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.115</v>
+        <v>-0.1322</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.07</v>
+        <v>-2.3796</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2079</v>
+        <v>-0.2261</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.7422</v>
+        <v>-4.0698</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.77</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2465</v>
+        <v>-0.2644</v>
       </c>
       <c r="J245" t="n">
-        <v>-4.437</v>
+        <v>-4.7592</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.54</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4635</v>
+        <v>-0.4731</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.343</v>
+        <v>-8.5158</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.94</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0167</v>
+        <v>1.0027</v>
       </c>
       <c r="J247" t="n">
-        <v>18.3006</v>
+        <v>18.0486</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>0.7575</v>
+        <v>0.7551</v>
       </c>
       <c r="J248" t="n">
-        <v>13.635</v>
+        <v>13.5918</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.58</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6761</v>
+        <v>0.6795</v>
       </c>
       <c r="J249" t="n">
-        <v>12.1698</v>
+        <v>12.231</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.17</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2253</v>
+        <v>0.2481</v>
       </c>
       <c r="J250" t="n">
-        <v>4.0554</v>
+        <v>4.4658</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.57</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4854</v>
+        <v>-0.4861</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.7372</v>
+        <v>-8.7498</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.14</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4453</v>
+        <v>0.4332</v>
       </c>
       <c r="J252" t="n">
-        <v>10.2419</v>
+        <v>9.9636</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.335</v>
+        <v>0.3324</v>
       </c>
       <c r="J253" t="n">
-        <v>7.705</v>
+        <v>7.6452</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.02</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0859</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="J254" t="n">
-        <v>1.9757</v>
+        <v>2.1689</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.99</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0633</v>
+        <v>-0.0654</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.4559</v>
+        <v>-1.5042</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.97</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.141</v>
+        <v>-0.143</v>
       </c>
       <c r="J256" t="n">
-        <v>-3.243</v>
+        <v>-3.289</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.2</v>
       </c>
       <c r="I257" t="n">
-        <v>0.446</v>
+        <v>0.4391</v>
       </c>
       <c r="J257" t="n">
-        <v>10.258</v>
+        <v>10.0993</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.446</v>
+        <v>0.4391</v>
       </c>
       <c r="J258" t="n">
-        <v>10.258</v>
+        <v>10.0993</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.95</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0738</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J259" t="n">
-        <v>-1.6974</v>
+        <v>-1.9435</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.85</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1854</v>
+        <v>-0.1995</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.2642</v>
+        <v>-4.5885</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3432</v>
+        <v>-0.3549</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.8936</v>
+        <v>-8.162699999999999</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.63</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2926</v>
+        <v>1.2678</v>
       </c>
       <c r="J262" t="n">
-        <v>27.1446</v>
+        <v>26.6238</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.3</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7817</v>
+        <v>0.7448</v>
       </c>
       <c r="J263" t="n">
-        <v>16.4157</v>
+        <v>15.6408</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.23</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6236</v>
+        <v>0.6039</v>
       </c>
       <c r="J264" t="n">
-        <v>13.0956</v>
+        <v>12.6819</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.04</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1075</v>
+        <v>0.1296</v>
       </c>
       <c r="J265" t="n">
-        <v>2.2575</v>
+        <v>2.7216</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.04</v>
       </c>
       <c r="I266" t="n">
-        <v>0.1075</v>
+        <v>0.1296</v>
       </c>
       <c r="J266" t="n">
-        <v>2.2575</v>
+        <v>2.7216</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.3</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6901</v>
+        <v>0.6513</v>
       </c>
       <c r="J267" t="n">
-        <v>14.4921</v>
+        <v>13.6773</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.97</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0326</v>
+        <v>-0.0448</v>
       </c>
       <c r="J268" t="n">
-        <v>-0.6846</v>
+        <v>-0.9408</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.68</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3365</v>
+        <v>-0.3514</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.0665</v>
+        <v>-7.3794</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.66</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3555</v>
+        <v>-0.3696</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.4655</v>
+        <v>-7.7616</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3743</v>
+        <v>-0.3877</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.8603</v>
+        <v>-8.1417</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.15</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4509</v>
+        <v>0.4242</v>
       </c>
       <c r="J272" t="n">
-        <v>8.5671</v>
+        <v>8.059799999999999</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.98</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0026</v>
+        <v>-0.0137</v>
       </c>
       <c r="J273" t="n">
-        <v>0.0494</v>
+        <v>-0.2603</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.68</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3242</v>
+        <v>-0.3418</v>
       </c>
       <c r="J274" t="n">
-        <v>-6.1598</v>
+        <v>-6.4942</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.54</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4554</v>
+        <v>-0.4667</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.6526</v>
+        <v>-8.8673</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.47</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5202</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.883800000000001</v>
+        <v>-10.0263</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.77</v>
       </c>
       <c r="I277" t="n">
-        <v>1.4549</v>
+        <v>1.4408</v>
       </c>
       <c r="J277" t="n">
-        <v>27.6431</v>
+        <v>27.3752</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.38</v>
       </c>
       <c r="I278" t="n">
-        <v>0.9496</v>
+        <v>0.8958</v>
       </c>
       <c r="J278" t="n">
-        <v>18.0424</v>
+        <v>17.0202</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.26</v>
       </c>
       <c r="I279" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6624</v>
       </c>
       <c r="J279" t="n">
-        <v>13.072</v>
+        <v>12.5856</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.09</v>
       </c>
       <c r="I280" t="n">
-        <v>0.256</v>
+        <v>0.2713</v>
       </c>
       <c r="J280" t="n">
-        <v>4.864</v>
+        <v>5.1547</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.88</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4786</v>
+        <v>-0.445</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.093400000000001</v>
+        <v>-8.455</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7250/event_7250_evp_summary.xlsx
+++ b/database/event/7250/event_7250_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.5447</v>
+        <v>6.7727</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5793</v>
+        <v>1.6343</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3551</v>
+        <v>2.4114</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5447</v>
+        <v>6.7727</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1479</v>
+        <v>2.9654</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3968</v>
+        <v>3.3708</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1926</v>
+        <v>4.8897</v>
       </c>
       <c r="I2" t="n">
-        <v>1.184</v>
+        <v>2.6404</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3968</v>
+        <v>3.3708</v>
       </c>
       <c r="K2" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="L2" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="M2" t="n">
-        <v>5.5808</v>
+        <v>6.011200000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3267</v>
+        <v>6.6008</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5267</v>
+        <v>1.5928</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2558</v>
+        <v>2.3346</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3267</v>
+        <v>6.6008</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9654</v>
+        <v>2.1479</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3613</v>
+        <v>4.3985</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8897</v>
+        <v>2.1926</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6404</v>
+        <v>1.184</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3613</v>
+        <v>4.3985</v>
       </c>
       <c r="K3" t="n">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="L3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0017</v>
+        <v>5.5825</v>
       </c>
       <c r="N3" t="n">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6482</v>
+        <v>4.6707</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1216</v>
+        <v>1.1271</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4918</v>
+        <v>1.4725</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6482</v>
+        <v>4.6707</v>
       </c>
       <c r="F4" t="n">
         <v>2.9313</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7169</v>
+        <v>1.7017</v>
       </c>
       <c r="H4" t="n">
         <v>4.7771</v>
@@ -612,7 +612,7 @@
         <v>2.5796</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7169</v>
+        <v>1.7017</v>
       </c>
       <c r="K4" t="n">
         <v>101</v>
@@ -621,7 +621,7 @@
         <v>120</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2965</v>
+        <v>4.2813</v>
       </c>
       <c r="N4" t="n">
         <v>221</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1765</v>
+        <v>4.4162</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0078</v>
+        <v>1.0656</v>
       </c>
       <c r="D5" t="n">
-        <v>1.277</v>
+        <v>1.3588</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1765</v>
+        <v>4.4162</v>
       </c>
       <c r="F5" t="n">
         <v>4.2664</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7888</v>
+        <v>3.7264</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9143</v>
+        <v>0.8992</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1005</v>
+        <v>1.0507</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7888</v>
+        <v>3.7264</v>
       </c>
       <c r="F6" t="n">
         <v>0.0241</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7647</v>
+        <v>3.7857</v>
       </c>
       <c r="H6" t="n">
         <v>0.0241</v>
@@ -704,7 +704,7 @@
         <v>0.013</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7647</v>
+        <v>3.7857</v>
       </c>
       <c r="K6" t="n">
         <v>101</v>
@@ -713,7 +713,7 @@
         <v>120</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7777</v>
+        <v>3.7987</v>
       </c>
       <c r="N6" t="n">
         <v>221</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.45</v>
+        <v>3.4408</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8325</v>
+        <v>0.8303</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9463</v>
+        <v>0.9231</v>
       </c>
       <c r="E7" t="n">
-        <v>3.45</v>
+        <v>3.4408</v>
       </c>
       <c r="F7" t="n">
         <v>1.1967</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2533</v>
+        <v>2.1649</v>
       </c>
       <c r="H7" t="n">
         <v>1.1967</v>
@@ -750,7 +750,7 @@
         <v>0.6462</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2533</v>
+        <v>2.1649</v>
       </c>
       <c r="K7" t="n">
         <v>101</v>
@@ -759,7 +759,7 @@
         <v>120</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8995</v>
+        <v>2.8111</v>
       </c>
       <c r="N7" t="n">
         <v>221</v>
@@ -768,173 +768,173 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0706</v>
+        <v>3.2134</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7409</v>
+        <v>0.7754</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7736</v>
+        <v>0.8215</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0706</v>
+        <v>3.2134</v>
       </c>
       <c r="F8" t="n">
-        <v>2.846</v>
+        <v>2.9565</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2246</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4958</v>
+        <v>3.7459</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4277</v>
+        <v>3.7459</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2246</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="L8" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6523</v>
+        <v>3.7459</v>
       </c>
       <c r="N8" t="n">
-        <v>201</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9627</v>
+        <v>3.0152</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7149</v>
+        <v>0.7276</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7245</v>
+        <v>0.733</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9627</v>
+        <v>3.0152</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4533</v>
+        <v>2.846</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5094</v>
+        <v>0.2239</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2002</v>
+        <v>4.4958</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7281</v>
+        <v>2.4277</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5094</v>
+        <v>0.2239</v>
       </c>
       <c r="K9" t="n">
+        <v>71</v>
+      </c>
+      <c r="L9" t="n">
         <v>130</v>
       </c>
-      <c r="L9" t="n">
-        <v>44</v>
-      </c>
       <c r="M9" t="n">
-        <v>2.2375</v>
+        <v>2.6516</v>
       </c>
       <c r="N9" t="n">
-        <v>174</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9565</v>
+        <v>2.8934</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7134</v>
+        <v>0.6982</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7217</v>
+        <v>0.6786</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9565</v>
+        <v>2.8934</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9565</v>
+        <v>3.2109</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.5271</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7459</v>
+        <v>5.6997</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7459</v>
+        <v>3.0778</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.5271</v>
       </c>
       <c r="K10" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7459</v>
+        <v>2.5507</v>
       </c>
       <c r="N10" t="n">
-        <v>143</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6838</v>
+        <v>2.8044</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6476</v>
+        <v>0.6767</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5975</v>
+        <v>0.6388</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6838</v>
+        <v>2.8044</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2109</v>
+        <v>2.4533</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5271</v>
+        <v>0.5094</v>
       </c>
       <c r="H11" t="n">
-        <v>5.6997</v>
+        <v>3.2002</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0778</v>
+        <v>1.7281</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5271</v>
+        <v>0.5094</v>
       </c>
       <c r="K11" t="n">
         <v>130</v>
@@ -943,7 +943,7 @@
         <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5507</v>
+        <v>2.2375</v>
       </c>
       <c r="N11" t="n">
         <v>174</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6321</v>
+        <v>2.7262</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6351</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.574</v>
+        <v>0.6039</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6321</v>
+        <v>2.7262</v>
       </c>
       <c r="F12" t="n">
         <v>2.381</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sLowi</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5781</v>
+        <v>2.5787</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6221</v>
+        <v>0.6223</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5494</v>
+        <v>0.538</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5781</v>
+        <v>2.5787</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2556</v>
+        <v>3.4687</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3225</v>
+        <v>-0.9841</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5478</v>
+        <v>6.5505</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3758</v>
+        <v>3.5372</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3225</v>
+        <v>-0.9841</v>
       </c>
       <c r="K13" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="L13" t="n">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6983</v>
+        <v>2.5531</v>
       </c>
       <c r="N13" t="n">
-        <v>117</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4742</v>
+        <v>2.5643</v>
       </c>
       <c r="C14" t="n">
-        <v>0.597</v>
+        <v>0.6188</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5021</v>
+        <v>0.5316</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4742</v>
+        <v>2.5643</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4687</v>
+        <v>2.0696</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9945000000000001</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.5505</v>
+        <v>2.0696</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5372</v>
+        <v>2.0696</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9945000000000001</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="L14" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5427</v>
+        <v>2.0696</v>
       </c>
       <c r="N14" t="n">
-        <v>201</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>sLowi</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4721</v>
+        <v>2.4883</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5965</v>
+        <v>0.6004</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5011</v>
+        <v>0.4976</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4721</v>
+        <v>2.4883</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1713</v>
+        <v>2.2556</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3008</v>
+        <v>0.3225</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1713</v>
+        <v>2.5478</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6325</v>
+        <v>1.3758</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3008</v>
+        <v>0.3225</v>
       </c>
       <c r="K15" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="L15" t="n">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9333</v>
+        <v>1.6983</v>
       </c>
       <c r="N15" t="n">
-        <v>201</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9908</v>
+        <v>2.4632</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4804</v>
+        <v>0.5944</v>
       </c>
       <c r="D16" t="n">
-        <v>0.282</v>
+        <v>0.4864</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9908</v>
+        <v>2.4632</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9908</v>
+        <v>1.1713</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.3002</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9908</v>
+        <v>1.1713</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9908</v>
+        <v>0.6325</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.3002</v>
       </c>
       <c r="K16" t="n">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9908</v>
+        <v>1.9327</v>
       </c>
       <c r="N16" t="n">
-        <v>146</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17">
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9178</v>
+        <v>2.1835</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4628</v>
+        <v>0.5269</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2488</v>
+        <v>0.3615</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9178</v>
+        <v>2.1835</v>
       </c>
       <c r="F17" t="n">
         <v>1.9178</v>
@@ -1228,185 +1228,185 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Airax</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6566</v>
+        <v>1.8565</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3997</v>
+        <v>0.448</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1299</v>
+        <v>0.2154</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6566</v>
+        <v>1.8565</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6566</v>
+        <v>2.2867</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.6693</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6566</v>
+        <v>2.6504</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6566</v>
+        <v>1.4312</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.6693</v>
       </c>
       <c r="K18" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6566</v>
+        <v>0.7619</v>
       </c>
       <c r="N18" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Airax</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6174</v>
+        <v>1.7395</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3903</v>
+        <v>0.4197</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1121</v>
+        <v>0.1632</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6174</v>
+        <v>1.7395</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2867</v>
+        <v>1.6447</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6693</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6504</v>
+        <v>1.6447</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4312</v>
+        <v>1.6447</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6693</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L19" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7619</v>
+        <v>1.6447</v>
       </c>
       <c r="N19" t="n">
-        <v>117</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ottoNd</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3683</v>
+        <v>1.413</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3302</v>
+        <v>0.341</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0013</v>
+        <v>0.0173</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3683</v>
+        <v>1.413</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3683</v>
+        <v>1.2945</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9197</v>
+        <v>1.2945</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5766</v>
+        <v>1.2945</v>
       </c>
       <c r="J20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="L20" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5766</v>
+        <v>1.2945</v>
       </c>
       <c r="N20" t="n">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>ottoNd</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2786</v>
+        <v>1.3632</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3085</v>
+        <v>0.3289</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0422</v>
+        <v>-0.0049</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2786</v>
+        <v>1.3632</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2786</v>
+        <v>2.3683</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2786</v>
+        <v>2.9197</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2786</v>
+        <v>1.5766</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K21" t="n">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2786</v>
+        <v>0.5766</v>
       </c>
       <c r="N21" t="n">
-        <v>146</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2712</v>
+        <v>1.2198</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3067</v>
+        <v>0.2943</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0455</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2712</v>
+        <v>1.2198</v>
       </c>
       <c r="F22" t="n">
         <v>0.3476</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9236</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="H22" t="n">
         <v>0.3476</v>
@@ -1440,7 +1440,7 @@
         <v>0.1877</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9236</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>101</v>
@@ -1449,7 +1449,7 @@
         <v>120</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1113</v>
+        <v>1.0884</v>
       </c>
       <c r="N22" t="n">
         <v>221</v>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9011</v>
+        <v>0.9216</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2174</v>
+        <v>0.2224</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.214</v>
+        <v>-0.2022</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9011</v>
+        <v>0.9216</v>
       </c>
       <c r="F23" t="n">
         <v>0.9011</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8568</v>
+        <v>0.7798</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2067</v>
+        <v>0.1882</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2342</v>
+        <v>-0.2655</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8568</v>
+        <v>0.7798</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8568</v>
+        <v>0.8444</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8568</v>
+        <v>0.8444</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8568</v>
+        <v>0.8444</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8568</v>
+        <v>0.8444</v>
       </c>
       <c r="N24" t="n">
         <v>88</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7104</v>
+        <v>0.6653</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1714</v>
+        <v>0.1605</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3008</v>
+        <v>-0.3166</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7104</v>
+        <v>0.6653</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7104</v>
+        <v>0.6575</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7104</v>
+        <v>0.6575</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7104</v>
+        <v>0.6575</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7104</v>
+        <v>0.6575</v>
       </c>
       <c r="N25" t="n">
         <v>143</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Banjo</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6876</v>
+        <v>0.639</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1659</v>
+        <v>0.1542</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3112</v>
+        <v>-0.3284</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6876</v>
+        <v>0.639</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0552</v>
+        <v>0.7104</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3676</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0552</v>
+        <v>0.7104</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5698</v>
+        <v>0.7104</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3676</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="L26" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2022</v>
+        <v>0.7104</v>
       </c>
       <c r="N26" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>Banjo</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6575</v>
+        <v>0.6194</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1587</v>
+        <v>0.1495</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3249</v>
+        <v>-0.3371</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6575</v>
+        <v>0.6194</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6575</v>
+        <v>1.0552</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.3676</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6575</v>
+        <v>1.0552</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6575</v>
+        <v>0.5698</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.3676</v>
       </c>
       <c r="K27" t="n">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6575</v>
+        <v>0.2022</v>
       </c>
       <c r="N27" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3181</v>
+        <v>0.3877</v>
       </c>
       <c r="C28" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4794</v>
+        <v>-0.4406</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3181</v>
+        <v>0.3877</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3181</v>
+        <v>0.3186</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3181</v>
+        <v>0.3186</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3181</v>
+        <v>0.3186</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3181</v>
+        <v>0.3186</v>
       </c>
       <c r="N28" t="n">
         <v>88</v>
@@ -1734,32 +1734,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1354</v>
+        <v>0.1575</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0327</v>
+        <v>0.038</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5626</v>
+        <v>-0.5435</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1354</v>
+        <v>0.1575</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1354</v>
+        <v>0.0324</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1354</v>
+        <v>0.0324</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1354</v>
+        <v>0.0324</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1354</v>
+        <v>0.0324</v>
       </c>
       <c r="N29" t="n">
         <v>74</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0324</v>
+        <v>0.1517</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0078</v>
+        <v>0.0366</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6095</v>
+        <v>-0.5461</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0324</v>
+        <v>0.1517</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0324</v>
+        <v>0.1354</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0324</v>
+        <v>0.1354</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0324</v>
+        <v>0.1354</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0324</v>
+        <v>0.1354</v>
       </c>
       <c r="N30" t="n">
         <v>74</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2386</v>
+        <v>-0.3698</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0576</v>
+        <v>-0.0892</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7328</v>
+        <v>-0.779</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2386</v>
+        <v>-0.3698</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2386</v>
+        <v>-0.212</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2386</v>
+        <v>-0.212</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2386</v>
+        <v>-0.212</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2386</v>
+        <v>-0.212</v>
       </c>
       <c r="N31" t="n">
         <v>146</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4295</v>
+        <v>-0.6115</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1036</v>
+        <v>-0.1476</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8197</v>
+        <v>-0.887</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4295</v>
+        <v>-0.6115</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4295</v>
+        <v>-0.4951</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4295</v>
+        <v>-0.4951</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4295</v>
+        <v>-0.4951</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4295</v>
+        <v>-0.4951</v>
       </c>
       <c r="N32" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4532</v>
+        <v>-0.6217</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1094</v>
+        <v>-0.15</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8305</v>
+        <v>-0.8915</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4532</v>
+        <v>-0.6217</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4532</v>
+        <v>-0.4276</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4532</v>
+        <v>-0.4276</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4532</v>
+        <v>-0.4276</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4532</v>
+        <v>-0.4276</v>
       </c>
       <c r="N33" t="n">
         <v>146</v>
@@ -1964,32 +1964,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4951</v>
+        <v>-0.7594</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1195</v>
+        <v>-0.1832</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8496</v>
+        <v>-0.953</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4951</v>
+        <v>-0.7594</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4951</v>
+        <v>-0.6865</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4951</v>
+        <v>-0.6865</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4951</v>
+        <v>-0.6865</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4951</v>
+        <v>-0.6865</v>
       </c>
       <c r="N34" t="n">
         <v>74</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6276</v>
+        <v>-0.8212</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1514</v>
+        <v>-0.1982</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9099</v>
+        <v>-0.9806</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6276</v>
+        <v>-0.8212</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6276</v>
+        <v>-0.6358</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6276</v>
+        <v>-0.6358</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6276</v>
+        <v>-0.6358</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6276</v>
+        <v>-0.6358</v>
       </c>
       <c r="N35" t="n">
         <v>88</v>
@@ -2056,47 +2056,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6865</v>
+        <v>-0.8727</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1657</v>
+        <v>-0.2106</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9367</v>
+        <v>-1.0036</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6865</v>
+        <v>-0.8727</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6865</v>
+        <v>-0.4279</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6865</v>
+        <v>-0.4279</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6865</v>
+        <v>-0.4279</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6865</v>
+        <v>-0.4279</v>
       </c>
       <c r="N36" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37">
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8962</v>
+        <v>-0.9698</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2163</v>
+        <v>-0.234</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0322</v>
+        <v>-1.047</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8962</v>
+        <v>-0.9698</v>
       </c>
       <c r="F37" t="n">
         <v>-0.7045</v>
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2061</v>
+        <v>-1.5418</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.291</v>
+        <v>-0.372</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1732</v>
+        <v>-1.3025</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2061</v>
+        <v>-1.5418</v>
       </c>
       <c r="F38" t="n">
         <v>-1.2061</v>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3761</v>
+        <v>-1.5867</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3321</v>
+        <v>-0.3829</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2506</v>
+        <v>-1.3226</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3761</v>
+        <v>-1.5867</v>
       </c>
       <c r="F39" t="n">
         <v>-1.0483</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4794</v>
+        <v>-1.7006</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.357</v>
+        <v>-0.4104</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2977</v>
+        <v>-1.3734</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4794</v>
+        <v>-1.7006</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4794</v>
+        <v>-1.4553</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4794</v>
+        <v>-1.4553</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4794</v>
+        <v>-1.4553</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4794</v>
+        <v>-1.4553</v>
       </c>
       <c r="N40" t="n">
         <v>146</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.3348</v>
+        <v>-2.6018</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5634</v>
+        <v>-0.6278</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6871</v>
+        <v>-1.776</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.3348</v>
+        <v>-2.6018</v>
       </c>
       <c r="F41" t="n">
         <v>-1.3874</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9474</v>
+        <v>-0.9295</v>
       </c>
       <c r="H41" t="n">
         <v>-1.3874</v>
@@ -2314,7 +2314,7 @@
         <v>-0.7492</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9474</v>
+        <v>-0.9295</v>
       </c>
       <c r="K41" t="n">
         <v>71</v>
@@ -2323,7 +2323,7 @@
         <v>130</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6966</v>
+        <v>-1.6787</v>
       </c>
       <c r="N41" t="n">
         <v>201</v>
@@ -2426,13 +2426,13 @@
         <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3083</v>
+        <v>0.3262</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7826</v>
+        <v>7.1764</v>
       </c>
     </row>
     <row r="3">
@@ -2466,13 +2466,13 @@
         <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1582</v>
+        <v>-0.1478</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.4804</v>
+        <v>-3.2516</v>
       </c>
     </row>
     <row r="4">
@@ -2506,13 +2506,13 @@
         <v>22</v>
       </c>
       <c r="H4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2191</v>
+        <v>-0.2096</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.8202</v>
+        <v>-4.6112</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.77</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2678</v>
+        <v>-0.2684</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.8916</v>
+        <v>-5.9048</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3336</v>
+        <v>-0.3343</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.3392</v>
+        <v>-7.3546</v>
       </c>
     </row>
     <row r="7">
@@ -2626,13 +2626,13 @@
         <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2565</v>
+        <v>1.2413</v>
       </c>
       <c r="J7" t="n">
-        <v>27.643</v>
+        <v>27.3086</v>
       </c>
     </row>
     <row r="8">
@@ -2666,13 +2666,13 @@
         <v>22</v>
       </c>
       <c r="H8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1657</v>
+        <v>1.1867</v>
       </c>
       <c r="J8" t="n">
-        <v>25.6454</v>
+        <v>26.1074</v>
       </c>
     </row>
     <row r="9">
@@ -2706,13 +2706,13 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5412</v>
+        <v>0.4528</v>
       </c>
       <c r="J9" t="n">
-        <v>11.9064</v>
+        <v>9.961600000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1313</v>
+        <v>0.133</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8886</v>
+        <v>2.926</v>
       </c>
     </row>
     <row r="11">
@@ -2786,13 +2786,13 @@
         <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4891</v>
+        <v>-0.512</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.7602</v>
+        <v>-11.264</v>
       </c>
     </row>
     <row r="12">
@@ -8426,13 +8426,13 @@
         <v>23</v>
       </c>
       <c r="H152" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8902</v>
+        <v>0.9061</v>
       </c>
       <c r="J152" t="n">
-        <v>20.4746</v>
+        <v>20.8403</v>
       </c>
     </row>
     <row r="153">
@@ -8466,19 +8466,19 @@
         <v>23</v>
       </c>
       <c r="H153" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2949</v>
+        <v>0.319</v>
       </c>
       <c r="J153" t="n">
-        <v>6.7827</v>
+        <v>7.337</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -8506,19 +8506,19 @@
         <v>23</v>
       </c>
       <c r="H154" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2402</v>
+        <v>0.319</v>
       </c>
       <c r="J154" t="n">
-        <v>5.5246</v>
+        <v>7.337</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -8546,13 +8546,13 @@
         <v>23</v>
       </c>
       <c r="H155" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2402</v>
+        <v>0.2658</v>
       </c>
       <c r="J155" t="n">
-        <v>5.5246</v>
+        <v>6.1134</v>
       </c>
     </row>
     <row r="156">
@@ -8586,13 +8586,13 @@
         <v>23</v>
       </c>
       <c r="H156" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2114</v>
+        <v>0.238</v>
       </c>
       <c r="J156" t="n">
-        <v>4.8622</v>
+        <v>5.474</v>
       </c>
     </row>
     <row r="157">
@@ -8626,13 +8626,13 @@
         <v>23</v>
       </c>
       <c r="H157" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9232</v>
+        <v>0.9113</v>
       </c>
       <c r="J157" t="n">
-        <v>21.2336</v>
+        <v>20.9599</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3235</v>
+        <v>0.3251</v>
       </c>
       <c r="J158" t="n">
-        <v>7.4405</v>
+        <v>7.4773</v>
       </c>
     </row>
     <row r="159">
@@ -8706,13 +8706,13 @@
         <v>23</v>
       </c>
       <c r="H159" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0823</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.8929</v>
+        <v>-2.1781</v>
       </c>
     </row>
     <row r="160">
@@ -8746,13 +8746,13 @@
         <v>23</v>
       </c>
       <c r="H160" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4407</v>
+        <v>-0.4489</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.1361</v>
+        <v>-10.3247</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.52</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5012</v>
+        <v>-0.5007</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.5276</v>
+        <v>-11.5161</v>
       </c>
     </row>
     <row r="162">

--- a/database/event/7250/event_7250_evp_summary.xlsx
+++ b/database/event/7250/event_7250_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7727</v>
+        <v>6.8188</v>
       </c>
       <c r="C2" t="n">
-        <v>1.6343</v>
+        <v>1.6454</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4114</v>
+        <v>2.5005</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7727</v>
+        <v>6.8188</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9654</v>
+        <v>3.0207</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3708</v>
+        <v>3.3616</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8897</v>
+        <v>4.8984</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6404</v>
+        <v>2.7503</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3708</v>
+        <v>3.3616</v>
       </c>
       <c r="K2" t="n">
         <v>71</v>
@@ -529,7 +529,7 @@
         <v>130</v>
       </c>
       <c r="M2" t="n">
-        <v>6.011200000000001</v>
+        <v>6.1119</v>
       </c>
       <c r="N2" t="n">
         <v>201</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6008</v>
+        <v>6.611</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5928</v>
+        <v>1.5953</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3346</v>
+        <v>2.4058</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6008</v>
+        <v>6.611</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1479</v>
+        <v>2.165</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3985</v>
+        <v>4.3916</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1926</v>
+        <v>2.165</v>
       </c>
       <c r="I3" t="n">
-        <v>1.184</v>
+        <v>1.2156</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3985</v>
+        <v>4.3916</v>
       </c>
       <c r="K3" t="n">
         <v>101</v>
@@ -575,7 +575,7 @@
         <v>120</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5825</v>
+        <v>5.607200000000001</v>
       </c>
       <c r="N3" t="n">
         <v>221</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6707</v>
+        <v>4.6909</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1271</v>
+        <v>1.1319</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4725</v>
+        <v>1.5311</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6707</v>
+        <v>4.6909</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9313</v>
+        <v>2.969</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7017</v>
+        <v>1.6842</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7771</v>
+        <v>4.7043</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5796</v>
+        <v>2.6413</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7017</v>
+        <v>1.6842</v>
       </c>
       <c r="K4" t="n">
         <v>101</v>
@@ -621,7 +621,7 @@
         <v>120</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2813</v>
+        <v>4.3255</v>
       </c>
       <c r="N4" t="n">
         <v>221</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4162</v>
+        <v>4.2266</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0656</v>
+        <v>1.0199</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3588</v>
+        <v>1.3196</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4162</v>
+        <v>4.2266</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2664</v>
+        <v>4.0954</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.1085</v>
       </c>
       <c r="H5" t="n">
-        <v>9.182399999999999</v>
+        <v>8.933400000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9584</v>
+        <v>5.0158</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.1085</v>
       </c>
       <c r="K5" t="n">
         <v>130</v>
@@ -667,7 +667,7 @@
         <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8685</v>
+        <v>4.907299999999999</v>
       </c>
       <c r="N5" t="n">
         <v>174</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7264</v>
+        <v>3.6048</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8992</v>
+        <v>0.8699</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0507</v>
+        <v>1.0364</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7264</v>
+        <v>3.6048</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0241</v>
+        <v>-0.0413</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7857</v>
+        <v>3.7295</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0241</v>
+        <v>-0.0413</v>
       </c>
       <c r="I6" t="n">
-        <v>0.013</v>
+        <v>-0.0232</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7857</v>
+        <v>3.7295</v>
       </c>
       <c r="K6" t="n">
         <v>101</v>
@@ -713,7 +713,7 @@
         <v>120</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7987</v>
+        <v>3.7063</v>
       </c>
       <c r="N6" t="n">
         <v>221</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4408</v>
+        <v>3.4135</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8303</v>
+        <v>0.8237</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9231</v>
+        <v>0.9492</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4408</v>
+        <v>3.4135</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1967</v>
+        <v>1.2254</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1649</v>
+        <v>2.1089</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1967</v>
+        <v>1.2254</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6462</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1649</v>
+        <v>2.1089</v>
       </c>
       <c r="K7" t="n">
         <v>101</v>
@@ -759,7 +759,7 @@
         <v>120</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8111</v>
+        <v>2.7969</v>
       </c>
       <c r="N7" t="n">
         <v>221</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2134</v>
+        <v>3.0501</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7754</v>
+        <v>0.736</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8215</v>
+        <v>0.7837</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2134</v>
+        <v>3.0501</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9565</v>
+        <v>2.8558</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7459</v>
+        <v>4.2791</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7459</v>
+        <v>2.4026</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="K8" t="n">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7459</v>
+        <v>2.6516</v>
       </c>
       <c r="N8" t="n">
-        <v>143</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0152</v>
+        <v>3.0263</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7276</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.733</v>
+        <v>0.7728</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0152</v>
+        <v>3.0263</v>
       </c>
       <c r="F9" t="n">
-        <v>2.846</v>
+        <v>2.7694</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2239</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4958</v>
+        <v>3.3965</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4277</v>
+        <v>3.3965</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2239</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="L9" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6516</v>
+        <v>3.3965</v>
       </c>
       <c r="N9" t="n">
-        <v>201</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8934</v>
+        <v>2.9535</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6982</v>
+        <v>0.7127</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6786</v>
+        <v>0.7397</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8934</v>
+        <v>2.9535</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2109</v>
+        <v>3.2376</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5271</v>
+        <v>-0.4937</v>
       </c>
       <c r="H10" t="n">
-        <v>5.6997</v>
+        <v>5.7129</v>
       </c>
       <c r="I10" t="n">
-        <v>3.0778</v>
+        <v>3.2076</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5271</v>
+        <v>-0.4937</v>
       </c>
       <c r="K10" t="n">
         <v>130</v>
@@ -897,7 +897,7 @@
         <v>44</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5507</v>
+        <v>2.7139</v>
       </c>
       <c r="N10" t="n">
         <v>174</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8044</v>
+        <v>2.8294</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6767</v>
+        <v>0.6827</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6388</v>
+        <v>0.6831</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8044</v>
+        <v>2.8294</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4533</v>
+        <v>2.5718</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5094</v>
+        <v>0.4159</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2002</v>
+        <v>3.2132</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7281</v>
+        <v>1.8041</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5094</v>
+        <v>0.4159</v>
       </c>
       <c r="K11" t="n">
         <v>130</v>
@@ -943,7 +943,7 @@
         <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2375</v>
+        <v>2.22</v>
       </c>
       <c r="N11" t="n">
         <v>174</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7262</v>
+        <v>2.8203</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6805</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6039</v>
+        <v>0.679</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7262</v>
+        <v>2.8203</v>
       </c>
       <c r="F12" t="n">
-        <v>2.381</v>
+        <v>2.5138</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2511</v>
+        <v>0.2124</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9617</v>
+        <v>2.9954</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5993</v>
+        <v>1.6818</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2511</v>
+        <v>0.2124</v>
       </c>
       <c r="K12" t="n">
         <v>130</v>
@@ -989,7 +989,7 @@
         <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8504</v>
+        <v>1.8942</v>
       </c>
       <c r="N12" t="n">
         <v>174</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>sLowi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5787</v>
+        <v>2.6301</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6223</v>
+        <v>0.6347</v>
       </c>
       <c r="D13" t="n">
-        <v>0.538</v>
+        <v>0.5923</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5787</v>
+        <v>2.6301</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4687</v>
+        <v>2.3623</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9841</v>
+        <v>0.3576</v>
       </c>
       <c r="H13" t="n">
-        <v>6.5505</v>
+        <v>2.4267</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5372</v>
+        <v>1.3625</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9841</v>
+        <v>0.3576</v>
       </c>
       <c r="K13" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="L13" t="n">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5531</v>
+        <v>1.7201</v>
       </c>
       <c r="N13" t="n">
-        <v>201</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5643</v>
+        <v>2.5352</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6188</v>
+        <v>0.6118</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5316</v>
+        <v>0.5491</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5643</v>
+        <v>2.5352</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0696</v>
+        <v>2.0405</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0696</v>
+        <v>2.0405</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0696</v>
+        <v>2.0405</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0696</v>
+        <v>2.0405</v>
       </c>
       <c r="N14" t="n">
         <v>146</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sLowi</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4883</v>
+        <v>2.4945</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6004</v>
+        <v>0.6019</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4976</v>
+        <v>0.5306</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4883</v>
+        <v>2.4945</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2556</v>
+        <v>3.4082</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3225</v>
+        <v>-1.0078</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5478</v>
+        <v>6.3533</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3758</v>
+        <v>3.5672</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3225</v>
+        <v>-1.0078</v>
       </c>
       <c r="K15" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="L15" t="n">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6983</v>
+        <v>2.5594</v>
       </c>
       <c r="N15" t="n">
-        <v>117</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4632</v>
+        <v>2.3634</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5944</v>
+        <v>0.5703</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4864</v>
+        <v>0.4709</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4632</v>
+        <v>2.3634</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1713</v>
+        <v>1.1587</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3002</v>
+        <v>1.213</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1713</v>
+        <v>1.1587</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6325</v>
+        <v>0.6506</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3002</v>
+        <v>1.213</v>
       </c>
       <c r="K16" t="n">
         <v>71</v>
@@ -1173,7 +1173,7 @@
         <v>130</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9327</v>
+        <v>1.8636</v>
       </c>
       <c r="N16" t="n">
         <v>201</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>Airax</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1835</v>
+        <v>1.9874</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5269</v>
+        <v>0.4796</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3615</v>
+        <v>0.2996</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1835</v>
+        <v>1.9874</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9178</v>
+        <v>2.3931</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.6448</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9178</v>
+        <v>2.5423</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9178</v>
+        <v>1.4274</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.6448</v>
       </c>
       <c r="K17" t="n">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9178</v>
+        <v>0.7826</v>
       </c>
       <c r="N17" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Airax</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8565</v>
+        <v>1.9062</v>
       </c>
       <c r="C18" t="n">
-        <v>0.448</v>
+        <v>0.46</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2154</v>
+        <v>0.2626</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8565</v>
+        <v>1.9062</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2867</v>
+        <v>1.6405</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6693</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6504</v>
+        <v>1.6405</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4312</v>
+        <v>1.6405</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6693</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="L18" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7619</v>
+        <v>1.6405</v>
       </c>
       <c r="N18" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7395</v>
+        <v>1.6106</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4197</v>
+        <v>0.3886</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1632</v>
+        <v>0.1279</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7395</v>
+        <v>1.6106</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6447</v>
+        <v>1.5158</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6447</v>
+        <v>1.5158</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6447</v>
+        <v>1.5158</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6447</v>
+        <v>1.5158</v>
       </c>
       <c r="N19" t="n">
         <v>88</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>ottoNd</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.413</v>
+        <v>1.4416</v>
       </c>
       <c r="C20" t="n">
-        <v>0.341</v>
+        <v>0.3479</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0173</v>
+        <v>0.0509</v>
       </c>
       <c r="E20" t="n">
-        <v>1.413</v>
+        <v>1.4416</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2945</v>
+        <v>2.4467</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2945</v>
+        <v>2.7435</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2945</v>
+        <v>1.5404</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K20" t="n">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2945</v>
+        <v>0.5404</v>
       </c>
       <c r="N20" t="n">
-        <v>146</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ottoNd</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3632</v>
+        <v>1.3105</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3289</v>
+        <v>0.3162</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0049</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3632</v>
+        <v>1.3105</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3683</v>
+        <v>1.192</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9197</v>
+        <v>1.192</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5766</v>
+        <v>1.192</v>
       </c>
       <c r="J21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="L21" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5766</v>
+        <v>1.192</v>
       </c>
       <c r="N21" t="n">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2198</v>
+        <v>1.1371</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2943</v>
+        <v>0.2744</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0878</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2198</v>
+        <v>1.1371</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3476</v>
+        <v>0.2134</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9522</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3476</v>
+        <v>0.2134</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1877</v>
+        <v>0.1198</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.9522</v>
       </c>
       <c r="K22" t="n">
         <v>101</v>
@@ -1449,7 +1449,7 @@
         <v>120</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0884</v>
+        <v>1.072</v>
       </c>
       <c r="N22" t="n">
         <v>221</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9216</v>
+        <v>0.822</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2224</v>
+        <v>0.1984</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2022</v>
+        <v>-0.2313</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9216</v>
+        <v>0.822</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9011</v>
+        <v>0.8015</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9011</v>
+        <v>0.8015</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9011</v>
+        <v>0.8015</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9011</v>
+        <v>0.8015</v>
       </c>
       <c r="N23" t="n">
         <v>143</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7798</v>
+        <v>0.694</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1882</v>
+        <v>0.1675</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2655</v>
+        <v>-0.2896</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7798</v>
+        <v>0.694</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8444</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8444</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8444</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8444</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>88</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6653</v>
+        <v>0.6058</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1605</v>
+        <v>0.1462</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3166</v>
+        <v>-0.3298</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6653</v>
+        <v>0.6058</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6575</v>
+        <v>0.6772</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6575</v>
+        <v>0.6772</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6575</v>
+        <v>0.6772</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6575</v>
+        <v>0.6772</v>
       </c>
       <c r="N25" t="n">
         <v>143</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.639</v>
+        <v>0.5614</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1542</v>
+        <v>0.1355</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3284</v>
+        <v>-0.35</v>
       </c>
       <c r="E26" t="n">
-        <v>0.639</v>
+        <v>0.5614</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7104</v>
+        <v>0.5536</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7104</v>
+        <v>0.5536</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7104</v>
+        <v>0.5536</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7104</v>
+        <v>0.5536</v>
       </c>
       <c r="N26" t="n">
         <v>143</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6194</v>
+        <v>0.5001</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1495</v>
+        <v>0.1207</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3371</v>
+        <v>-0.378</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6194</v>
+        <v>0.5001</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0552</v>
+        <v>0.9885</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3676</v>
+        <v>-0.4202</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0552</v>
+        <v>0.9885</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5698</v>
+        <v>0.555</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3676</v>
+        <v>-0.4202</v>
       </c>
       <c r="K27" t="n">
         <v>83</v>
@@ -1679,7 +1679,7 @@
         <v>34</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2022</v>
+        <v>0.1348</v>
       </c>
       <c r="N27" t="n">
         <v>117</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3877</v>
+        <v>0.2704</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0936</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4406</v>
+        <v>-0.4826</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3877</v>
+        <v>0.2704</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3186</v>
+        <v>0.2013</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3186</v>
+        <v>0.2013</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3186</v>
+        <v>0.2013</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3186</v>
+        <v>0.2013</v>
       </c>
       <c r="N28" t="n">
         <v>88</v>
@@ -1734,32 +1734,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1575</v>
+        <v>0.1024</v>
       </c>
       <c r="C29" t="n">
-        <v>0.038</v>
+        <v>0.0247</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5435</v>
+        <v>-0.5591</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1575</v>
+        <v>0.1024</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0324</v>
+        <v>0.0861</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0324</v>
+        <v>0.0861</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0324</v>
+        <v>0.0861</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0324</v>
+        <v>0.0861</v>
       </c>
       <c r="N29" t="n">
         <v>74</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1517</v>
+        <v>0.0696</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0366</v>
+        <v>0.0168</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5461</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1517</v>
+        <v>0.0696</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1354</v>
+        <v>-0.0555</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1354</v>
+        <v>-0.0555</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1354</v>
+        <v>-0.0555</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1354</v>
+        <v>-0.0555</v>
       </c>
       <c r="N30" t="n">
         <v>74</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3698</v>
+        <v>-0.4279</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0892</v>
+        <v>-0.1033</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.779</v>
+        <v>-0.8007</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3698</v>
+        <v>-0.4279</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.212</v>
+        <v>-0.2701</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.212</v>
+        <v>-0.2701</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.212</v>
+        <v>-0.2701</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.212</v>
+        <v>-0.2701</v>
       </c>
       <c r="N31" t="n">
         <v>146</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6115</v>
+        <v>-0.6441</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1476</v>
+        <v>-0.1554</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.887</v>
+        <v>-0.8992</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6115</v>
+        <v>-0.6441</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4951</v>
+        <v>-0.45</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4951</v>
+        <v>-0.45</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4951</v>
+        <v>-0.45</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4951</v>
+        <v>-0.45</v>
       </c>
       <c r="N32" t="n">
-        <v>74</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6217</v>
+        <v>-0.6448</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.15</v>
+        <v>-0.1556</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8915</v>
+        <v>-0.8995</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6217</v>
+        <v>-0.6448</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4276</v>
+        <v>-0.5284</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4276</v>
+        <v>-0.5284</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4276</v>
+        <v>-0.5284</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4276</v>
+        <v>-0.5284</v>
       </c>
       <c r="N33" t="n">
-        <v>146</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7594</v>
+        <v>-0.7585</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1832</v>
+        <v>-0.183</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.953</v>
+        <v>-0.9513</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7594</v>
+        <v>-0.7585</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6865</v>
+        <v>-0.6856</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6865</v>
+        <v>-0.6856</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6865</v>
+        <v>-0.6856</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6865</v>
+        <v>-0.6856</v>
       </c>
       <c r="N34" t="n">
         <v>74</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8212</v>
+        <v>-0.8278</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1982</v>
+        <v>-0.1998</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9806</v>
+        <v>-0.9829</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8212</v>
+        <v>-0.8278</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6358</v>
+        <v>-0.6424</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6358</v>
+        <v>-0.6424</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6358</v>
+        <v>-0.6424</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6358</v>
+        <v>-0.6424</v>
       </c>
       <c r="N35" t="n">
         <v>88</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8727</v>
+        <v>-0.8802</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2106</v>
+        <v>-0.2124</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0036</v>
+        <v>-1.0068</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8727</v>
+        <v>-0.8802</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4279</v>
+        <v>-0.4354</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4279</v>
+        <v>-0.4354</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4279</v>
+        <v>-0.4354</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4279</v>
+        <v>-0.4354</v>
       </c>
       <c r="N36" t="n">
         <v>88</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9698</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.234</v>
+        <v>-0.239</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.047</v>
+        <v>-1.057</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9698</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7045</v>
+        <v>-0.667</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1917</v>
+        <v>-0.2498</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7045</v>
+        <v>-0.667</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.3804</v>
+        <v>-0.3745</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1917</v>
+        <v>-0.2498</v>
       </c>
       <c r="K37" t="n">
         <v>83</v>
@@ -2139,7 +2139,7 @@
         <v>34</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.6243</v>
       </c>
       <c r="N37" t="n">
         <v>117</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kyuubii</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5418</v>
+        <v>-1.3221</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.372</v>
+        <v>-0.319</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.3025</v>
+        <v>-1.2081</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5418</v>
+        <v>-1.3221</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2061</v>
+        <v>-0.8225</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.289</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2061</v>
+        <v>-0.8225</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2061</v>
+        <v>-0.4618</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.289</v>
       </c>
       <c r="K38" t="n">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2061</v>
+        <v>-0.7507999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>74</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>kyuubii</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5867</v>
+        <v>-1.5477</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3829</v>
+        <v>-0.3735</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3226</v>
+        <v>-1.3108</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5867</v>
+        <v>-1.5477</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0483</v>
+        <v>-1.212</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.3278</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0483</v>
+        <v>-1.212</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5661</v>
+        <v>-1.212</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.3278</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="L39" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.8939</v>
+        <v>-1.212</v>
       </c>
       <c r="N39" t="n">
-        <v>174</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7006</v>
+        <v>-1.6347</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4104</v>
+        <v>-0.3945</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3734</v>
+        <v>-1.3505</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7006</v>
+        <v>-1.6347</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4553</v>
+        <v>-1.3894</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4553</v>
+        <v>-1.3894</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4553</v>
+        <v>-1.3894</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4553</v>
+        <v>-1.3894</v>
       </c>
       <c r="N40" t="n">
         <v>146</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.6018</v>
+        <v>-2.4654</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6278</v>
+        <v>-0.5949</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.776</v>
+        <v>-1.7289</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.6018</v>
+        <v>-2.4654</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3874</v>
+        <v>-1.271</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9295</v>
+        <v>-0.9095</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3874</v>
+        <v>-1.271</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7492</v>
+        <v>-0.7136</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9295</v>
+        <v>-0.9095</v>
       </c>
       <c r="K41" t="n">
         <v>71</v>
@@ -2323,7 +2323,7 @@
         <v>130</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6787</v>
+        <v>-1.6231</v>
       </c>
       <c r="N41" t="n">
         <v>201</v>
@@ -2429,10 +2429,10 @@
         <v>1.12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3262</v>
+        <v>0.2763</v>
       </c>
       <c r="J2" t="n">
-        <v>7.1764</v>
+        <v>6.0786</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.89</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1478</v>
+        <v>-0.1309</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.2516</v>
+        <v>-2.8798</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.83</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2096</v>
+        <v>-0.1907</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.6112</v>
+        <v>-4.1954</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.77</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2684</v>
+        <v>-0.2496</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.9048</v>
+        <v>-5.4912</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3343</v>
+        <v>-0.3181</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.3546</v>
+        <v>-6.9982</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.56</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2413</v>
+        <v>1.2617</v>
       </c>
       <c r="J7" t="n">
-        <v>27.3086</v>
+        <v>27.7574</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.53</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1867</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>26.1074</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4528</v>
+        <v>0.4193</v>
       </c>
       <c r="J9" t="n">
-        <v>9.961600000000001</v>
+        <v>9.224600000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>0.133</v>
+        <v>0.1095</v>
       </c>
       <c r="J10" t="n">
-        <v>2.926</v>
+        <v>2.409</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.512</v>
+        <v>-0.4736</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.264</v>
+        <v>-10.4192</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.78</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8929</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>17.858</v>
+        <v>16.502</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3768</v>
+        <v>0.3176</v>
       </c>
       <c r="J13" t="n">
-        <v>7.536</v>
+        <v>6.352</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2481</v>
+        <v>0.2021</v>
       </c>
       <c r="J14" t="n">
-        <v>4.962</v>
+        <v>4.042</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0726</v>
+        <v>0.0525</v>
       </c>
       <c r="J15" t="n">
-        <v>1.452</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1541</v>
+        <v>-0.1352</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.082</v>
+        <v>-2.704</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.06</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1838</v>
+        <v>0.1743</v>
       </c>
       <c r="J17" t="n">
-        <v>3.676</v>
+        <v>3.486</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1354</v>
+        <v>-0.1202</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.708</v>
+        <v>-2.404</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2214</v>
+        <v>-0.2053</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.428</v>
+        <v>-4.106</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.54</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4667</v>
+        <v>-0.4615</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.334</v>
+        <v>-9.23</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.52</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4842</v>
+        <v>-0.4811</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.683999999999999</v>
+        <v>-9.622</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.92</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4773</v>
+        <v>1.4954</v>
       </c>
       <c r="J22" t="n">
-        <v>32.5006</v>
+        <v>32.8988</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.85</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2006</v>
+        <v>-0.18</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.4132</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2712</v>
+        <v>-0.2519</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.9664</v>
+        <v>-5.5418</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3</v>
+        <v>-0.2821</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.6</v>
+        <v>-6.2062</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.65</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3922</v>
+        <v>-0.3811</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.628399999999999</v>
+        <v>-8.3842</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7055</v>
+        <v>0.6734</v>
       </c>
       <c r="J27" t="n">
-        <v>15.521</v>
+        <v>14.8148</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.25</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6631</v>
+        <v>0.629</v>
       </c>
       <c r="J28" t="n">
-        <v>14.5882</v>
+        <v>13.838</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4412</v>
+        <v>0.4032</v>
       </c>
       <c r="J29" t="n">
-        <v>9.7064</v>
+        <v>8.8704</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.08</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2677</v>
+        <v>0.2346</v>
       </c>
       <c r="J30" t="n">
-        <v>5.8894</v>
+        <v>5.1612</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.91</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3408</v>
+        <v>-0.299</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.4976</v>
+        <v>-6.578</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5856</v>
+        <v>0.5316</v>
       </c>
       <c r="J32" t="n">
-        <v>12.8832</v>
+        <v>11.6952</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.86</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1811</v>
+        <v>-0.1621</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.9842</v>
+        <v>-3.5662</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2319</v>
+        <v>-0.2123</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.1018</v>
+        <v>-4.6706</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2418</v>
+        <v>-0.2222</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.3196</v>
+        <v>-4.8884</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.337</v>
+        <v>-0.3209</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.414</v>
+        <v>-7.0598</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.78</v>
       </c>
       <c r="I37" t="n">
-        <v>1.6169</v>
+        <v>1.649</v>
       </c>
       <c r="J37" t="n">
-        <v>35.5718</v>
+        <v>36.278</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.36</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8752</v>
+        <v>0.8559</v>
       </c>
       <c r="J38" t="n">
-        <v>19.2544</v>
+        <v>18.8298</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3379</v>
+        <v>0.3041</v>
       </c>
       <c r="J39" t="n">
-        <v>7.4338</v>
+        <v>6.6902</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2352</v>
+        <v>-0.1984</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.1744</v>
+        <v>-4.3648</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7573</v>
+        <v>-0.7328</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.6606</v>
+        <v>-16.1216</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5087</v>
+        <v>0.4808</v>
       </c>
       <c r="J42" t="n">
-        <v>10.174</v>
+        <v>9.616</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.07</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2269</v>
+        <v>0.1847</v>
       </c>
       <c r="J43" t="n">
-        <v>4.538</v>
+        <v>3.694</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.85</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1888</v>
+        <v>-0.1707</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.776</v>
+        <v>-3.414</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.63</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3964</v>
+        <v>-0.3847</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.928</v>
+        <v>-7.694</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.46</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5445</v>
+        <v>-0.5506</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.89</v>
+        <v>-11.012</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1545</v>
+        <v>1.1485</v>
       </c>
       <c r="J47" t="n">
-        <v>23.09</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6045</v>
+        <v>0.5969</v>
       </c>
       <c r="J48" t="n">
-        <v>12.09</v>
+        <v>11.938</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.26</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6045</v>
+        <v>0.5969</v>
       </c>
       <c r="J49" t="n">
-        <v>12.09</v>
+        <v>11.938</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.11</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3247</v>
+        <v>0.2926</v>
       </c>
       <c r="J50" t="n">
-        <v>6.494</v>
+        <v>5.852</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.06</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1879</v>
+        <v>0.1602</v>
       </c>
       <c r="J51" t="n">
-        <v>3.758</v>
+        <v>3.204</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.15</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5113</v>
+        <v>0.5283</v>
       </c>
       <c r="J52" t="n">
-        <v>7.1582</v>
+        <v>7.3962</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.73</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2729</v>
+        <v>-0.2601</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.8206</v>
+        <v>-3.6414</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.49</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4886</v>
+        <v>-0.4857</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.8404</v>
+        <v>-6.7998</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.37</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5945</v>
+        <v>-0.6049</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.323</v>
+        <v>-8.4686</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.25</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7004</v>
+        <v>-0.7306</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.8056</v>
+        <v>-10.2284</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.87</v>
       </c>
       <c r="I57" t="n">
-        <v>1.3517</v>
+        <v>1.3593</v>
       </c>
       <c r="J57" t="n">
-        <v>18.9238</v>
+        <v>19.0302</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.65</v>
       </c>
       <c r="I58" t="n">
-        <v>1.092</v>
+        <v>1.0896</v>
       </c>
       <c r="J58" t="n">
-        <v>15.288</v>
+        <v>15.2544</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.6</v>
       </c>
       <c r="I59" t="n">
-        <v>1.0325</v>
+        <v>1.0291</v>
       </c>
       <c r="J59" t="n">
-        <v>14.455</v>
+        <v>14.4074</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.58</v>
       </c>
       <c r="I60" t="n">
-        <v>1.0082</v>
+        <v>1.0046</v>
       </c>
       <c r="J60" t="n">
-        <v>14.1148</v>
+        <v>14.0644</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.36</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7178</v>
+        <v>0.7136</v>
       </c>
       <c r="J61" t="n">
-        <v>10.0492</v>
+        <v>9.990399999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.62</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1189</v>
+        <v>1.1118</v>
       </c>
       <c r="J62" t="n">
-        <v>22.378</v>
+        <v>22.236</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.49</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9432</v>
+        <v>0.929</v>
       </c>
       <c r="J63" t="n">
-        <v>18.864</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4095</v>
+        <v>0.3755</v>
       </c>
       <c r="J64" t="n">
-        <v>8.19</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.03</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1041</v>
+        <v>0.0837</v>
       </c>
       <c r="J65" t="n">
-        <v>2.082</v>
+        <v>1.674</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.72</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8024</v>
+        <v>-0.7823</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.048</v>
+        <v>-15.646</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2535</v>
+        <v>0.2071</v>
       </c>
       <c r="J67" t="n">
-        <v>5.07</v>
+        <v>4.142</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.92</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.117</v>
+        <v>-0.1008</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.34</v>
+        <v>-2.016</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.87</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1719</v>
+        <v>-0.1528</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.438</v>
+        <v>-3.056</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1824</v>
+        <v>-0.163</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.648</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.78</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2629</v>
+        <v>-0.2436</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.258</v>
+        <v>-4.872</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.45</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9184</v>
+        <v>0.9051</v>
       </c>
       <c r="J72" t="n">
-        <v>22.0416</v>
+        <v>21.7224</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.37</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.7851</v>
       </c>
       <c r="J73" t="n">
-        <v>19.2216</v>
+        <v>18.8424</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.91</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3293</v>
+        <v>-0.2872</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.9032</v>
+        <v>-6.8928</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4339</v>
+        <v>-0.391</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.4136</v>
+        <v>-9.384</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6927</v>
+        <v>-0.6602</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.6248</v>
+        <v>-15.8448</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.16</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3681</v>
+        <v>0.3132</v>
       </c>
       <c r="J77" t="n">
-        <v>8.8344</v>
+        <v>7.5168</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2559</v>
+        <v>0.2088</v>
       </c>
       <c r="J78" t="n">
-        <v>6.1416</v>
+        <v>5.0112</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.173</v>
+        <v>0.1351</v>
       </c>
       <c r="J79" t="n">
-        <v>4.152</v>
+        <v>3.2424</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1454</v>
+        <v>-0.126</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.4896</v>
+        <v>-3.024</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3552</v>
+        <v>-0.3409</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.524800000000001</v>
+        <v>-8.1816</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.45</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0363</v>
+        <v>1.0394</v>
       </c>
       <c r="J82" t="n">
-        <v>24.8712</v>
+        <v>24.9456</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.27</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6946</v>
+        <v>0.6639</v>
       </c>
       <c r="J83" t="n">
-        <v>16.6704</v>
+        <v>15.9336</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.19</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5251</v>
+        <v>0.4899</v>
       </c>
       <c r="J84" t="n">
-        <v>12.6024</v>
+        <v>11.7576</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1406</v>
+        <v>0.1167</v>
       </c>
       <c r="J85" t="n">
-        <v>3.3744</v>
+        <v>2.8008</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1687</v>
+        <v>-0.1372</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.0488</v>
+        <v>-3.2928</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2978</v>
+        <v>0.2484</v>
       </c>
       <c r="J87" t="n">
-        <v>7.1472</v>
+        <v>5.9616</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0499</v>
+        <v>-0.0401</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.1976</v>
+        <v>-0.9624</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1602</v>
+        <v>-0.142</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.8448</v>
+        <v>-3.408</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1813</v>
+        <v>-0.1622</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.3512</v>
+        <v>-3.8928</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4007</v>
+        <v>-0.3896</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.6168</v>
+        <v>-9.3504</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.63</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2734</v>
+        <v>1.2919</v>
       </c>
       <c r="J92" t="n">
-        <v>25.468</v>
+        <v>25.838</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.47</v>
       </c>
       <c r="I93" t="n">
-        <v>1.0574</v>
+        <v>1.0641</v>
       </c>
       <c r="J93" t="n">
-        <v>21.148</v>
+        <v>21.282</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.15</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4301</v>
+        <v>0.3964</v>
       </c>
       <c r="J94" t="n">
-        <v>8.602</v>
+        <v>7.928</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1956</v>
+        <v>0.1677</v>
       </c>
       <c r="J95" t="n">
-        <v>3.912</v>
+        <v>3.354</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6063</v>
+        <v>-0.572</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.126</v>
+        <v>-11.44</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2778</v>
+        <v>0.2297</v>
       </c>
       <c r="J97" t="n">
-        <v>5.556</v>
+        <v>4.594</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2364</v>
+        <v>0.1918</v>
       </c>
       <c r="J98" t="n">
-        <v>4.728</v>
+        <v>3.836</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.88</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1602</v>
+        <v>-0.142</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.204</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.242</v>
+        <v>-0.2224</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.84</v>
+        <v>-4.448</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4362</v>
+        <v>-0.4286</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.724</v>
+        <v>-8.571999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.33</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6152</v>
       </c>
       <c r="J102" t="n">
-        <v>14.0469</v>
+        <v>12.9192</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.14</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3455</v>
+        <v>0.2924</v>
       </c>
       <c r="J103" t="n">
-        <v>7.2555</v>
+        <v>6.1404</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.78</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2651</v>
+        <v>-0.2457</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.5671</v>
+        <v>-5.1597</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.74</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3034</v>
+        <v>-0.2855</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.3714</v>
+        <v>-5.9955</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3953</v>
+        <v>-0.3839</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.301299999999999</v>
+        <v>-8.0619</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.64</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2958</v>
+        <v>1.3163</v>
       </c>
       <c r="J107" t="n">
-        <v>27.2118</v>
+        <v>27.6423</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.36</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8752</v>
+        <v>0.8559</v>
       </c>
       <c r="J108" t="n">
-        <v>18.3792</v>
+        <v>17.9739</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2587</v>
+        <v>0.2274</v>
       </c>
       <c r="J109" t="n">
-        <v>5.4327</v>
+        <v>4.7754</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1694</v>
+        <v>-0.1379</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.5574</v>
+        <v>-2.8959</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4044</v>
+        <v>-0.3631</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.4924</v>
+        <v>-7.6251</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.91</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9739</v>
+        <v>0.9104</v>
       </c>
       <c r="J112" t="n">
-        <v>16.5563</v>
+        <v>15.4768</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.73</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8153</v>
+        <v>0.7443</v>
       </c>
       <c r="J113" t="n">
-        <v>13.8601</v>
+        <v>12.6531</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.27</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3642</v>
+        <v>0.3098</v>
       </c>
       <c r="J114" t="n">
-        <v>6.1914</v>
+        <v>5.2666</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.16</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2323</v>
+        <v>0.1893</v>
       </c>
       <c r="J115" t="n">
-        <v>3.9491</v>
+        <v>3.2181</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.03</v>
       </c>
       <c r="I116" t="n">
-        <v>0.0377</v>
+        <v>0.022</v>
       </c>
       <c r="J116" t="n">
-        <v>0.6409</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0458</v>
+        <v>-0.0312</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.7786</v>
+        <v>-0.5304</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.79</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2329</v>
+        <v>-0.2181</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.9593</v>
+        <v>-3.7077</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.73</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.291</v>
+        <v>-0.277</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.947</v>
+        <v>-4.709</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.58</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4238</v>
+        <v>-0.4146</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.2046</v>
+        <v>-7.0482</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.46</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5292</v>
+        <v>-0.5312</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.9964</v>
+        <v>-9.0304</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.39</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7711</v>
+        <v>0.7245</v>
       </c>
       <c r="J122" t="n">
-        <v>15.422</v>
+        <v>14.49</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.36</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7242</v>
+        <v>0.6746</v>
       </c>
       <c r="J123" t="n">
-        <v>14.484</v>
+        <v>13.492</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.8</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2435</v>
+        <v>-0.2238</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.87</v>
+        <v>-4.476</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.53</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4899</v>
+        <v>-0.4889</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.798</v>
+        <v>-9.778</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.45</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5579</v>
+        <v>-0.5668</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.158</v>
+        <v>-11.336</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.97</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6851</v>
+        <v>1.7365</v>
       </c>
       <c r="J127" t="n">
-        <v>33.702</v>
+        <v>34.73</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.31</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7594</v>
+        <v>0.7368</v>
       </c>
       <c r="J128" t="n">
-        <v>15.188</v>
+        <v>14.736</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6614</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>13.228</v>
+        <v>12.692</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0482</v>
+        <v>-0.0434</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.964</v>
+        <v>-0.868</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.89</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4208</v>
+        <v>-0.3822</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.416</v>
+        <v>-7.644</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0897</v>
+        <v>-0.0761</v>
       </c>
       <c r="J132" t="n">
-        <v>-1.794</v>
+        <v>-1.522</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.91</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1263</v>
+        <v>-0.1102</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.526</v>
+        <v>-2.204</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.89</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1488</v>
+        <v>-0.1315</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.976</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.85</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1903</v>
+        <v>-0.1715</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.806</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.26</v>
+        <v>-0.2408</v>
       </c>
       <c r="J136" t="n">
-        <v>-5.2</v>
+        <v>-4.816</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.69</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8032</v>
+        <v>0.7321</v>
       </c>
       <c r="J137" t="n">
-        <v>16.064</v>
+        <v>14.642</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.54</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6571</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>13.142</v>
+        <v>11.704</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.28</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3863</v>
+        <v>0.3269</v>
       </c>
       <c r="J139" t="n">
-        <v>7.726</v>
+        <v>6.538</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.97</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>-1.554</v>
+        <v>-1.274</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2823</v>
+        <v>-0.2658</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.646</v>
+        <v>-5.316</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.84</v>
       </c>
       <c r="I142" t="n">
-        <v>1.5886</v>
+        <v>1.6414</v>
       </c>
       <c r="J142" t="n">
-        <v>38.1264</v>
+        <v>39.3936</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.11</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3496</v>
+        <v>0.3115</v>
       </c>
       <c r="J143" t="n">
-        <v>8.3904</v>
+        <v>7.476</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.02</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0859</v>
+        <v>0.068</v>
       </c>
       <c r="J144" t="n">
-        <v>2.0616</v>
+        <v>1.632</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.78</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6524</v>
+        <v>-0.6178</v>
       </c>
       <c r="J145" t="n">
-        <v>-15.6576</v>
+        <v>-14.8272</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7631</v>
+        <v>-0.7366</v>
       </c>
       <c r="J146" t="n">
-        <v>-18.3144</v>
+        <v>-17.6784</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.43</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7832</v>
+        <v>0.729</v>
       </c>
       <c r="J147" t="n">
-        <v>18.7968</v>
+        <v>17.496</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.11</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2651</v>
+        <v>0.2182</v>
       </c>
       <c r="J148" t="n">
-        <v>6.3624</v>
+        <v>5.2368</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0964</v>
+        <v>0.0722</v>
       </c>
       <c r="J149" t="n">
-        <v>2.3136</v>
+        <v>1.7328</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.86</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1944</v>
+        <v>-0.1738</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.6656</v>
+        <v>-4.1712</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.77</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2853</v>
+        <v>-0.2669</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.8472</v>
+        <v>-6.4056</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.37</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9061</v>
+        <v>0.8887</v>
       </c>
       <c r="J152" t="n">
-        <v>20.8403</v>
+        <v>20.4401</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.1</v>
       </c>
       <c r="I153" t="n">
-        <v>0.319</v>
+        <v>0.2842</v>
       </c>
       <c r="J153" t="n">
-        <v>7.337</v>
+        <v>6.5366</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.1</v>
       </c>
       <c r="I154" t="n">
-        <v>0.319</v>
+        <v>0.2842</v>
       </c>
       <c r="J154" t="n">
-        <v>7.337</v>
+        <v>6.5366</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.08</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2658</v>
+        <v>0.2333</v>
       </c>
       <c r="J155" t="n">
-        <v>6.1134</v>
+        <v>5.3659</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.07</v>
       </c>
       <c r="I156" t="n">
-        <v>0.238</v>
+        <v>0.2069</v>
       </c>
       <c r="J156" t="n">
-        <v>5.474</v>
+        <v>4.7587</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.49</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9113</v>
+        <v>0.8737</v>
       </c>
       <c r="J157" t="n">
-        <v>20.9599</v>
+        <v>20.0951</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3251</v>
+        <v>0.273</v>
       </c>
       <c r="J158" t="n">
-        <v>7.4773</v>
+        <v>6.279</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0796</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.1781</v>
+        <v>-1.8308</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.58</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4489</v>
+        <v>-0.4432</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.3247</v>
+        <v>-10.1936</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.52</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5007</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.5161</v>
+        <v>-11.5345</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.73</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3892</v>
+        <v>1.414</v>
       </c>
       <c r="J162" t="n">
-        <v>27.784</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.54</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1424</v>
+        <v>1.1554</v>
       </c>
       <c r="J163" t="n">
-        <v>22.848</v>
+        <v>23.108</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.42</v>
       </c>
       <c r="I164" t="n">
-        <v>0.9678</v>
+        <v>0.9615</v>
       </c>
       <c r="J164" t="n">
-        <v>19.356</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.219</v>
+        <v>-0.186</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.38</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7497</v>
+        <v>-0.7272</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.994</v>
+        <v>-14.544</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.14</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3656</v>
+        <v>0.314</v>
       </c>
       <c r="J167" t="n">
-        <v>7.312</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0302</v>
+        <v>-0.0229</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.604</v>
+        <v>-0.458</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1894</v>
+        <v>-0.1709</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.788</v>
+        <v>-3.418</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3155</v>
+        <v>-0.2983</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.31</v>
+        <v>-5.966</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.61</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4155</v>
+        <v>-0.4056</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.31</v>
+        <v>-8.112</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.98</v>
       </c>
       <c r="I172" t="n">
-        <v>1.6424</v>
+        <v>1.6849</v>
       </c>
       <c r="J172" t="n">
-        <v>26.2784</v>
+        <v>26.9584</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.81</v>
       </c>
       <c r="I173" t="n">
-        <v>1.4424</v>
+        <v>1.4708</v>
       </c>
       <c r="J173" t="n">
-        <v>23.0784</v>
+        <v>23.5328</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.54</v>
       </c>
       <c r="I174" t="n">
-        <v>1.112</v>
+        <v>1.1304</v>
       </c>
       <c r="J174" t="n">
-        <v>17.792</v>
+        <v>18.0864</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.24</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5879</v>
+        <v>0.5631</v>
       </c>
       <c r="J175" t="n">
-        <v>9.4064</v>
+        <v>9.009600000000001</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.082</v>
+        <v>-0.0827</v>
       </c>
       <c r="J176" t="n">
-        <v>-1.312</v>
+        <v>-1.3232</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I177" t="n">
-        <v>0.265</v>
+        <v>0.2444</v>
       </c>
       <c r="J177" t="n">
-        <v>4.24</v>
+        <v>3.9104</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.75</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2654</v>
+        <v>-0.252</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.2464</v>
+        <v>-4.032</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.68</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3313</v>
+        <v>-0.3195</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.3008</v>
+        <v>-5.112</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.49</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4973</v>
+        <v>-0.4951</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.9568</v>
+        <v>-7.9216</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.32</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6456</v>
+        <v>-0.6659</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.3296</v>
+        <v>-10.6544</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.03</v>
       </c>
       <c r="I182" t="n">
-        <v>0.1246</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>2.6166</v>
+        <v>1.9803</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0658</v>
+        <v>0.0468</v>
       </c>
       <c r="J183" t="n">
-        <v>1.3818</v>
+        <v>0.9828</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.87</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1697</v>
+        <v>-0.1516</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.5637</v>
+        <v>-3.1836</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2304</v>
+        <v>-0.211</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.8384</v>
+        <v>-4.431</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.64</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.39</v>
+        <v>-0.3778</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.19</v>
+        <v>-7.9338</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.01</v>
       </c>
       <c r="I187" t="n">
-        <v>1.7431</v>
+        <v>1.8029</v>
       </c>
       <c r="J187" t="n">
-        <v>36.6051</v>
+        <v>37.8609</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.47</v>
       </c>
       <c r="I188" t="n">
-        <v>1.0512</v>
+        <v>1.0574</v>
       </c>
       <c r="J188" t="n">
-        <v>22.0752</v>
+        <v>22.2054</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.02</v>
       </c>
       <c r="I189" t="n">
-        <v>0.058</v>
+        <v>0.0417</v>
       </c>
       <c r="J189" t="n">
-        <v>1.218</v>
+        <v>0.8757</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1031</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.1651</v>
+        <v>-1.7346</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.79</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6572</v>
+        <v>-0.6269</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.8012</v>
+        <v>-13.1649</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.11</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2746</v>
+        <v>0.2259</v>
       </c>
       <c r="J192" t="n">
-        <v>9.611000000000001</v>
+        <v>7.9065</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2551</v>
+        <v>0.2081</v>
       </c>
       <c r="J193" t="n">
-        <v>8.9285</v>
+        <v>7.2835</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.03</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1018</v>
+        <v>0.075</v>
       </c>
       <c r="J194" t="n">
-        <v>3.563</v>
+        <v>2.625</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.97</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0573</v>
+        <v>-0.0451</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.0055</v>
+        <v>-1.5785</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3279</v>
+        <v>-0.3116</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.4765</v>
+        <v>-10.906</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.39</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9524</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>33.334</v>
+        <v>32.935</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.38</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9335</v>
+        <v>0.9193</v>
       </c>
       <c r="J198" t="n">
-        <v>32.6725</v>
+        <v>32.1755</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.11</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3479</v>
+        <v>0.3107</v>
       </c>
       <c r="J199" t="n">
-        <v>12.1765</v>
+        <v>10.8745</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3912</v>
+        <v>-0.3486</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.692</v>
+        <v>-12.201</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5874</v>
+        <v>-0.5495</v>
       </c>
       <c r="J201" t="n">
-        <v>-20.559</v>
+        <v>-19.2325</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.64</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8844</v>
+        <v>0.9802</v>
       </c>
       <c r="J202" t="n">
-        <v>17.688</v>
+        <v>19.604</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.29</v>
       </c>
       <c r="I203" t="n">
-        <v>0.472</v>
+        <v>0.4803</v>
       </c>
       <c r="J203" t="n">
-        <v>9.44</v>
+        <v>9.606</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3506</v>
+        <v>-0.3355</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.012</v>
+        <v>-6.71</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.62</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4137</v>
+        <v>-0.4042</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.273999999999999</v>
+        <v>-8.084</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.42</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5849</v>
+        <v>-0.5986</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.698</v>
+        <v>-11.972</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.29</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4076</v>
+        <v>0.3443</v>
       </c>
       <c r="J207" t="n">
-        <v>8.151999999999999</v>
+        <v>6.886</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.25</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3617</v>
+        <v>0.302</v>
       </c>
       <c r="J208" t="n">
-        <v>7.234</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.11</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1885</v>
+        <v>0.1488</v>
       </c>
       <c r="J209" t="n">
-        <v>3.77</v>
+        <v>2.976</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.06</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1142</v>
+        <v>0.0864</v>
       </c>
       <c r="J210" t="n">
-        <v>2.284</v>
+        <v>1.728</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.04</v>
       </c>
       <c r="I211" t="n">
-        <v>0.0803</v>
+        <v>0.0589</v>
       </c>
       <c r="J211" t="n">
-        <v>1.606</v>
+        <v>1.178</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>2.08</v>
       </c>
       <c r="I212" t="n">
-        <v>1.7498</v>
+        <v>1.8019</v>
       </c>
       <c r="J212" t="n">
-        <v>26.247</v>
+        <v>27.0285</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.87</v>
       </c>
       <c r="I213" t="n">
-        <v>1.5076</v>
+        <v>1.5403</v>
       </c>
       <c r="J213" t="n">
-        <v>22.614</v>
+        <v>23.1045</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.55</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1222</v>
+        <v>1.1419</v>
       </c>
       <c r="J214" t="n">
-        <v>16.833</v>
+        <v>17.1285</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.51</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0722</v>
+        <v>1.0902</v>
       </c>
       <c r="J215" t="n">
-        <v>16.083</v>
+        <v>16.353</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.75</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7834</v>
+        <v>-0.7721</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.751</v>
+        <v>-11.5815</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.65</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.3513</v>
+        <v>-0.342</v>
       </c>
       <c r="J217" t="n">
-        <v>-5.2695</v>
+        <v>-5.13</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.64</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3603</v>
+        <v>-0.3513</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.4045</v>
+        <v>-5.2695</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.62</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3779</v>
+        <v>-0.3692</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.6685</v>
+        <v>-5.538</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.59</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4027</v>
+        <v>-0.3946</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.0405</v>
+        <v>-5.919</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.53</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4546</v>
+        <v>-0.449</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.819</v>
+        <v>-6.735</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.66</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2739</v>
+        <v>1.2929</v>
       </c>
       <c r="J222" t="n">
-        <v>22.9302</v>
+        <v>23.2722</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.63</v>
       </c>
       <c r="I223" t="n">
-        <v>1.2362</v>
+        <v>1.2539</v>
       </c>
       <c r="J223" t="n">
-        <v>22.2516</v>
+        <v>22.5702</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.48</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0419</v>
+        <v>1.0518</v>
       </c>
       <c r="J224" t="n">
-        <v>18.7542</v>
+        <v>18.9324</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.43</v>
       </c>
       <c r="I225" t="n">
-        <v>0.9659</v>
+        <v>0.9656</v>
       </c>
       <c r="J225" t="n">
-        <v>17.3862</v>
+        <v>17.3808</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.89</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4404</v>
+        <v>-0.4061</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.9272</v>
+        <v>-7.3098</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.12</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3547</v>
+        <v>0.3093</v>
       </c>
       <c r="J227" t="n">
-        <v>6.3846</v>
+        <v>5.5674</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.86</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1723</v>
+        <v>-0.1562</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.1014</v>
+        <v>-2.8116</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.84</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1935</v>
+        <v>-0.1771</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.483</v>
+        <v>-3.1878</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.58</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4341</v>
+        <v>-0.4256</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.8138</v>
+        <v>-7.6608</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.53</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.478</v>
+        <v>-0.4742</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.603999999999999</v>
+        <v>-8.535600000000001</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.48</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0845</v>
+        <v>1.0945</v>
       </c>
       <c r="J232" t="n">
-        <v>24.9435</v>
+        <v>25.1735</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.26</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6776</v>
+        <v>0.6453</v>
       </c>
       <c r="J233" t="n">
-        <v>15.5848</v>
+        <v>14.8419</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.07</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2347</v>
+        <v>0.2042</v>
       </c>
       <c r="J234" t="n">
-        <v>5.3981</v>
+        <v>4.6966</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.05</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1757</v>
+        <v>0.1489</v>
       </c>
       <c r="J235" t="n">
-        <v>4.0411</v>
+        <v>3.4247</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.96</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1989</v>
+        <v>-0.1643</v>
       </c>
       <c r="J236" t="n">
-        <v>-4.5747</v>
+        <v>-3.7789</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.24</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5175</v>
+        <v>0.4599</v>
       </c>
       <c r="J237" t="n">
-        <v>11.9025</v>
+        <v>10.5777</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.04</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1346</v>
+        <v>0.1017</v>
       </c>
       <c r="J238" t="n">
-        <v>3.0958</v>
+        <v>2.3391</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1419</v>
+        <v>-0.1233</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.2637</v>
+        <v>-2.8359</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2369</v>
+        <v>-0.2167</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.4487</v>
+        <v>-4.9841</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.71</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3329</v>
+        <v>-0.3167</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.6567</v>
+        <v>-7.2841</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.09</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2184</v>
+        <v>0.2057</v>
       </c>
       <c r="J242" t="n">
-        <v>3.9312</v>
+        <v>3.7026</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.9</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1322</v>
+        <v>-0.1168</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.3796</v>
+        <v>-2.1024</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2261</v>
+        <v>-0.2081</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.0698</v>
+        <v>-3.7458</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.77</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2644</v>
+        <v>-0.2463</v>
       </c>
       <c r="J245" t="n">
-        <v>-4.7592</v>
+        <v>-4.4334</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.54</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4731</v>
+        <v>-0.4691</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.5158</v>
+        <v>-8.4438</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.94</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0027</v>
+        <v>0.9447</v>
       </c>
       <c r="J247" t="n">
-        <v>18.0486</v>
+        <v>17.0046</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>0.7551</v>
+        <v>0.6834</v>
       </c>
       <c r="J248" t="n">
-        <v>13.5918</v>
+        <v>12.3012</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.58</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6795</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="J249" t="n">
-        <v>12.231</v>
+        <v>10.9512</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.17</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2481</v>
+        <v>0.2034</v>
       </c>
       <c r="J250" t="n">
-        <v>4.4658</v>
+        <v>3.6612</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.57</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4861</v>
+        <v>-0.4908</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.7498</v>
+        <v>-8.8344</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.14</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4332</v>
+        <v>0.3913</v>
       </c>
       <c r="J252" t="n">
-        <v>9.9636</v>
+        <v>8.9999</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3324</v>
+        <v>0.2922</v>
       </c>
       <c r="J253" t="n">
-        <v>7.6452</v>
+        <v>6.7206</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.02</v>
       </c>
       <c r="I254" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="J254" t="n">
-        <v>2.1689</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.99</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0654</v>
+        <v>-0.047</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.5042</v>
+        <v>-1.081</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.97</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.143</v>
+        <v>-0.1131</v>
       </c>
       <c r="J256" t="n">
-        <v>-3.289</v>
+        <v>-2.6013</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.2</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4391</v>
+        <v>0.3816</v>
       </c>
       <c r="J257" t="n">
-        <v>10.0993</v>
+        <v>8.7768</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.4391</v>
+        <v>0.3816</v>
       </c>
       <c r="J258" t="n">
-        <v>10.0993</v>
+        <v>8.7768</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.95</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.0693</v>
       </c>
       <c r="J259" t="n">
-        <v>-1.9435</v>
+        <v>-1.5939</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.85</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1995</v>
+        <v>-0.1789</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.5885</v>
+        <v>-4.1147</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3549</v>
+        <v>-0.3405</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.162699999999999</v>
+        <v>-7.8315</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.63</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2678</v>
+        <v>1.2857</v>
       </c>
       <c r="J262" t="n">
-        <v>26.6238</v>
+        <v>26.9997</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.3</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7448</v>
+        <v>0.7194</v>
       </c>
       <c r="J263" t="n">
-        <v>15.6408</v>
+        <v>15.1074</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.23</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6039</v>
+        <v>0.5734</v>
       </c>
       <c r="J264" t="n">
-        <v>12.6819</v>
+        <v>12.0414</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.04</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1296</v>
+        <v>0.1061</v>
       </c>
       <c r="J265" t="n">
-        <v>2.7216</v>
+        <v>2.2281</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.04</v>
       </c>
       <c r="I266" t="n">
-        <v>0.1296</v>
+        <v>0.1061</v>
       </c>
       <c r="J266" t="n">
-        <v>2.7216</v>
+        <v>2.2281</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.3</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6513</v>
+        <v>0.6031</v>
       </c>
       <c r="J267" t="n">
-        <v>13.6773</v>
+        <v>12.6651</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.97</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0448</v>
+        <v>-0.0356</v>
       </c>
       <c r="J268" t="n">
-        <v>-0.9408</v>
+        <v>-0.7476</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.68</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3514</v>
+        <v>-0.3362</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.3794</v>
+        <v>-7.0602</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.66</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3696</v>
+        <v>-0.3557</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.7616</v>
+        <v>-7.4697</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3877</v>
+        <v>-0.3752</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.1417</v>
+        <v>-7.8792</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.15</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4242</v>
+        <v>0.3801</v>
       </c>
       <c r="J272" t="n">
-        <v>8.059799999999999</v>
+        <v>7.2219</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.98</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.0137</v>
+        <v>-0.0054</v>
       </c>
       <c r="J273" t="n">
-        <v>-0.2603</v>
+        <v>-0.1026</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.68</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3418</v>
+        <v>-0.3269</v>
       </c>
       <c r="J274" t="n">
-        <v>-6.4942</v>
+        <v>-6.2111</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.54</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4667</v>
+        <v>-0.4615</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.8673</v>
+        <v>-8.7685</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.47</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.5301</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.0263</v>
+        <v>-10.0719</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.77</v>
       </c>
       <c r="I277" t="n">
-        <v>1.4408</v>
+        <v>1.4693</v>
       </c>
       <c r="J277" t="n">
-        <v>27.3752</v>
+        <v>27.9167</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.38</v>
       </c>
       <c r="I278" t="n">
-        <v>0.8958</v>
+        <v>0.881</v>
       </c>
       <c r="J278" t="n">
-        <v>17.0202</v>
+        <v>16.739</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.26</v>
       </c>
       <c r="I279" t="n">
-        <v>0.6624</v>
+        <v>0.6352</v>
       </c>
       <c r="J279" t="n">
-        <v>12.5856</v>
+        <v>12.0688</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.09</v>
       </c>
       <c r="I280" t="n">
-        <v>0.2713</v>
+        <v>0.2403</v>
       </c>
       <c r="J280" t="n">
-        <v>5.1547</v>
+        <v>4.5657</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.88</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.445</v>
+        <v>-0.4064</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.455</v>
+        <v>-7.7216</v>
       </c>
     </row>
   </sheetData>
